--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>112.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-668.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.1%</t>
+          <t>448.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.8%</t>
+          <t>-614.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-267.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-178.5%</t>
+          <t>-181.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-184.5%</t>
+          <t>-183.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.4%</t>
+          <t>-178.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.9622078420698927</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.736089201185021</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>-0.9508186054150913</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>2.738469691966182</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.368572628961928</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.569294974052511</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9880615826826838</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.65870429556736</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.45310852400926</v>
       </c>
       <c r="F1848" t="n">
         <v>1.012143377422864</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.866708353920437</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.374799045221954</v>
       </c>
       <c r="F1849" t="n">
         <v>1.012143377422864</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.928886765081407</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.345009137095555</v>
       </c>
       <c r="F1850" t="n">
         <v>0.9499649662618935</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-2.29495549222606</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.191665945544142</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5838962391172409</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.503446273677744</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.128607922702237</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3754054576655564</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.750647458442966</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.037826199204717</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3955588111643689</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-3.243032486467063</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.84197858003881</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.09682621685972786</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.628212877397135</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.686448962479644</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.878083557411717</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.588269813928428</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-4.084595334298738</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.501771161829877</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.40393940937924</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.375806458497936</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.835745202529028</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.189417028705426</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-5.07043919666158</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.083824206054495</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.406101843892032</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>0.9481397388182793</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.482546174094904</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>0.9240495669713722</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.847673556733651</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.7772531289217053</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-6.256262333914329</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.6125791620641929</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.370022745937193</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.5622604297265075</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.786414620224191</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.3936977306205858</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-7.03068602095126</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.3062478609984369</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.133125570211944</v>
+        <v>-7.373944540594279</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2613716064398588</v>
+        <v>0.1650440182869248</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.181328387454288</v>
+        <v>-7.422147357836623</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2404953995979224</v>
+        <v>0.144167811444988</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.477989729264485</v>
+        <v>-7.718808699646821</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1256098388030513</v>
+        <v>0.02928225065011736</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.664709437573788</v>
+        <v>-7.905528407956123</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04689565094492743</v>
+        <v>-0.04943193720800698</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.047710826316418</v>
+        <v>-8.288529796698754</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.106407005873709</v>
+        <v>-0.202734594026643</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.052197271517807</v>
+        <v>-8.293016241900142</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1056300679828341</v>
+        <v>-0.2019576561357685</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.411727594021809</v>
+        <v>-8.652546564404144</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2440918936863845</v>
+        <v>-0.3404194818393189</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.462076657476031</v>
+        <v>-8.702895627858366</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.256315499110896</v>
+        <v>-0.35264308726383</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.559695934897427</v>
+        <v>-8.800514905279762</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2923214594576855</v>
+        <v>-0.3886490476106199</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.613767434405785</v>
+        <v>-8.854586404788121</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.311056502939457</v>
+        <v>-0.4073840910923909</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.818025609735649</v>
+        <v>-9.058844580117984</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3872465759527599</v>
+        <v>-0.4835741641056943</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.851678448244122</v>
+        <v>-9.092497418626458</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3962251568717132</v>
+        <v>-0.4925527450246476</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.778208616576674</v>
+        <v>-9.019027586959009</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3514655227113126</v>
+        <v>-0.4477931108642466</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.953333033963217</v>
+        <v>-9.194152004345552</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.406960068918413</v>
+        <v>-0.5032876570713474</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.187785127977707</v>
+        <v>-9.428604098360042</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.507960071425805</v>
+        <v>-0.604287659578739</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.292159859004153</v>
+        <v>-9.532978829386488</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5563821546103598</v>
+        <v>-0.6527097427632937</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.34494601460448</v>
+        <v>-9.585764984986815</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5763808270119339</v>
+        <v>-0.6727084151648683</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.470982807972769</v>
+        <v>-9.711801778355104</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.624101815730135</v>
+        <v>-0.7204294038830694</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.413911036076838</v>
+        <v>-9.654730006459173</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5972827712853621</v>
+        <v>-0.6936103594382961</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.555582877800958</v>
+        <v>-9.796401848183294</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6554267348737519</v>
+        <v>-0.7517543230266859</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.505992033376124</v>
+        <v>-9.746811003758459</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6205369869389457</v>
+        <v>-0.7168645750918801</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.357073698904268</v>
+        <v>-9.597892669286603</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5740207867968863</v>
+        <v>-0.6703483749498202</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.131228546184857</v>
+        <v>-9.372047516567193</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4741036526729134</v>
+        <v>-0.5704312408258478</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.006649889847266</v>
+        <v>-9.247468860229601</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4231330455818179</v>
+        <v>-0.5194606337347518</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.059545177891552</v>
+        <v>-9.300364148273887</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4416573866374249</v>
+        <v>-0.5379849747903589</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.987412002603671</v>
+        <v>-9.228230972986006</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4070704122836357</v>
+        <v>-0.5033980004365701</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.916045609994024</v>
+        <v>-9.156864580376359</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3882611176336423</v>
+        <v>-0.4845887057865763</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.822586576008799</v>
+        <v>-9.063405546391134</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.36076098535246</v>
+        <v>-0.457088573505394</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.555344775140401</v>
+        <v>-8.796163745522737</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2556988255044748</v>
+        <v>-0.3520264136574087</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.457437736463911</v>
+        <v>-8.698256706846246</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2168363250073391</v>
+        <v>-0.3131639131602735</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.433484195487953</v>
+        <v>-8.674303165870288</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2065864024714625</v>
+        <v>-0.3029139906243965</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.169424257165156</v>
+        <v>-8.410243227547491</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1142227433040959</v>
+        <v>-0.2105503314570298</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.462344633660318</v>
+        <v>-7.703163604042653</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1658220724375385</v>
+        <v>0.06949448428460459</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.422160335294127</v>
+        <v>-7.662979305676463</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1822394156718561</v>
+        <v>0.08591182751892212</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.258760464354765</v>
+        <v>-7.4995794347371</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.246966185268358</v>
+        <v>0.150638597115424</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-7.266098212507502</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.2519555148451156</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-7.116431821499987</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.3089298609351627</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-6.9841563478691</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.3572075371345442</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.828418015309358</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.4223179308460776</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.579418216625777</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.5348241915431688</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2472458891152278</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.685008206398882</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.3646122660347082</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3528358788883322</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.462924138135143</v>
+        <v>-6.703743108517479</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5019902352172902</v>
+        <v>0.4056626470643558</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3584318885484635</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.314984096727544</v>
+        <v>-6.555803067109879</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4412873290921624</v>
+        <v>0.344959740939228</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3381109726399059</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.262014574473556</v>
+        <v>-6.502833544855891</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4537611517402795</v>
+        <v>0.3574335635873451</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.285141450385917</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218466167702865</v>
+        <v>-6.459285138085201</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4642199023534626</v>
+        <v>0.3678923142005281</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.285141450385917</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185102961224096</v>
+        <v>-6.425921931606432</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4920275393261129</v>
+        <v>0.3956999511731789</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.285141450385917</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.076843824101575</v>
+        <v>-6.31766279448391</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5298633146343166</v>
+        <v>0.4335357264813826</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.285141450385917</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953552689284444</v>
+        <v>-6.194371659666779</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5766778625717461</v>
+        <v>0.4803502744188117</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1618503155687865</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.932403490381001</v>
+        <v>-6.173222460763336</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5928385203704485</v>
+        <v>0.4965109322175145</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1407011166653432</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.688638048397556</v>
+        <v>-5.929457018779892</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.686125405510877</v>
+        <v>0.589797817357943</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1407011166653432</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.586875228120261</v>
+        <v>-5.827694198502597</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7289548475418108</v>
+        <v>0.6326272593888769</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1274820482729145</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.337024834171187</v>
+        <v>-5.577843804553522</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8216370801051429</v>
+        <v>0.725309491952209</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1274820482729145</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.161132741703755</v>
+        <v>-5.40195171208609</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955930406127646</v>
+        <v>0.7992654524598302</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1274820482729145</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.989686278681291</v>
+        <v>-5.230505249063627</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9774991318763036</v>
+        <v>0.8811715437233696</v>
       </c>
       <c r="F1921" t="n">
         <v>0.04396441474954865</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.915396712942952</v>
+        <v>-5.156215683325287</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006235435787936</v>
+        <v>0.9099078476350022</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1182539804878879</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.851760970709018</v>
+        <v>-5.092579941091353</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036384533735827</v>
+        <v>0.9400569455828931</v>
       </c>
       <c r="F1923" t="n">
         <v>0.1818897227218225</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.740334211383098</v>
+        <v>-4.981153181765433</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062149496249991</v>
+        <v>0.9658219080970567</v>
       </c>
       <c r="F1924" t="n">
         <v>0.1818897227218225</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.499903714578237</v>
+        <v>-4.740722684960573</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.160064771596812</v>
+        <v>1.063737183443878</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4223202195266827</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.427661146407043</v>
+        <v>-4.668480116789378</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.192891112700111</v>
+        <v>1.096563524547176</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4223202195266827</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.409947459529177</v>
+        <v>-4.650766429911513</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200655171368597</v>
+        <v>1.104327583215662</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4255015484235996</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.30114257404945</v>
+        <v>-4.541961544431786</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241175196780481</v>
+        <v>1.144847608627547</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4255015484235996</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.321940746394775</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.234434964852965</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5667213934915798</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-4.189073057331497</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.3034762232801</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5667213934915798</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-4.068899973966999</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.352691301066201</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6868944768560787</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.924227828867261</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.420648261667536</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8315666219558162</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-3.984102656224954</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.382735822125885</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7716917945981241</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.864282425314116</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.445953083724428</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7716917945981241</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.866752131775922</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.352609400462147</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7692220881363179</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.935122318099932</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.244523187417845</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7784977871725328</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.948910370946979</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.229444674910917</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7784977871725328</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-4.004430446839568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.344267481246084</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7784977871725328</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.828956187047099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.419024417154859</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7784977871725328</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.939892439688347</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.350391944859567</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7784977871725328</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.906228894216066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.29239567644993</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8121613326448147</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.846376275012342</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.326509110563551</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8121613326448147</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.760132811985965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.355952766347962</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8121613326448147</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.805439631384945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.329605814032896</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7713511696355839</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.834472736087247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.318544445185077</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7713511696355839</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.741662254636387</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.284941329656786</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8641616510864433</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.786051723965815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.269059017849616</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8197721817570156</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.661774358688822</v>
+        <v>-3.902593329071158</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.313845672472136</v>
+        <v>1.217518084319202</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7032305766516729</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.549397357506149</v>
+        <v>-3.790216327888485</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.364287768775873</v>
+        <v>1.267960180622938</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7032305766516729</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.577177755407502</v>
+        <v>-3.817996725789838</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.36467281138387</v>
+        <v>1.268345223230936</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6754501787503198</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.695558428137641</v>
+        <v>-3.936377398519977</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.155676262292468</v>
+        <v>1.059348674139534</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6082323265993436</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.804172506580972</v>
+        <v>-4.044991476963308</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.232380291634342</v>
+        <v>1.136052703481407</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6082323265993436</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.768763468332829</v>
+        <v>-4.009582438715165</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.261056933035922</v>
+        <v>1.164729344882987</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6082323265993436</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.730379805774678</v>
+        <v>-3.971198776157014</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.273829839401551</v>
+        <v>1.177502251248617</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6466159891574947</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.553263475739512</v>
+        <v>-3.794082446121847</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.341405400260919</v>
+        <v>1.245077812107985</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6466159891574947</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.598355720573057</v>
+        <v>-3.839174690955393</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.324051894089414</v>
+        <v>1.22772430593648</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5847199459881049</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.418980299334289</v>
+        <v>-3.659799269716626</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.389589037891336</v>
+        <v>1.293261449738401</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7414967041588236</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.463994512854895</v>
+        <v>-3.704813483237232</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.352390807814683</v>
+        <v>1.256063219661748</v>
       </c>
       <c r="F1958" t="n">
         <v>0.711147808844219</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.730999023127331</v>
+        <v>-3.971817993509667</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.251280566044654</v>
+        <v>1.15495297789172</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5167847708012705</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.832196804564504</v>
+        <v>-4.07301577494684</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.210005375366287</v>
+        <v>1.113677787213352</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4483759572559513</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.825685837950191</v>
+        <v>-4.066504808332527</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.210209723566328</v>
+        <v>1.113882135413394</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4483759572559513</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.806647710242894</v>
+        <v>-4.04746668062523</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.214349693857492</v>
+        <v>1.118022105704558</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3901923459247568</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.837774341393512</v>
+        <v>-4.078593311775848</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.321193443031436</v>
+        <v>1.224865854878501</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3901923459247568</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.851641102727429</v>
+        <v>-4.092460073109766</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.316480067484002</v>
+        <v>1.220152479331067</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3523344291909338</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.806836931187499</v>
+        <v>-4.047655901569836</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.3404102664969</v>
+        <v>1.244082678343965</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3523344291909338</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.659093960952497</v>
+        <v>-3.899912931334834</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.2974576758681</v>
+        <v>1.201130087715166</v>
       </c>
       <c r="F1966" t="n">
         <v>0.520141786425817</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.761108643483718</v>
+        <v>-4.001927613866055</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.259445424387093</v>
+        <v>1.163117836234158</v>
       </c>
       <c r="F1967" t="n">
         <v>0.520141786425817</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.754955937430934</v>
+        <v>-3.995774907813271</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.262568855199865</v>
+        <v>1.16624126704693</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5262944924786013</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.771765235581435</v>
+        <v>-4.012584205963773</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.254925612679775</v>
+        <v>1.15859802452684</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5094851943280996</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.709467236805313</v>
+        <v>-3.950286207187651</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.346180365987044</v>
+        <v>1.249852777834109</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5094851943280996</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.507677039140155</v>
+        <v>-3.748496009522493</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.229188446767235</v>
+        <v>1.1328608586143</v>
       </c>
       <c r="F1971" t="n">
         <v>0.707503386497254</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.55856375182635</v>
+        <v>-3.799382722208688</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.279123994014932</v>
+        <v>1.182796405861997</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6566166738110595</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.656304296451324</v>
+        <v>-3.897123266833662</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.254655512280986</v>
+        <v>1.158327924128051</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6407273956780792</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.716513594456609</v>
+        <v>-3.957332564838946</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.229107773903544</v>
+        <v>1.132780185750609</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5805180976727947</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.640091548024682</v>
+        <v>-3.88091051840702</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.258168210516243</v>
+        <v>1.161840622363308</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5805180976727947</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.595718416386113</v>
+        <v>-3.836537386768451</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.275780330607107</v>
+        <v>1.179452742454172</v>
       </c>
       <c r="F1976" t="n">
         <v>0.6248912293113633</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.618198767244998</v>
+        <v>-3.859017737627336</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.261181984402143</v>
+        <v>1.164854396249208</v>
       </c>
       <c r="F1977" t="n">
         <v>0.6248912293113633</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.570543036683943</v>
+        <v>-3.81136200706628</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.28662603365437</v>
+        <v>1.190298445501435</v>
       </c>
       <c r="F1978" t="n">
         <v>0.672546959872419</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.470024878185188</v>
+        <v>-3.710843848567525</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.331725670428597</v>
+        <v>1.235398082275662</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7730651183711735</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.530691468587577</v>
+        <v>-3.771510438969914</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.294213706743513</v>
+        <v>1.197886118590578</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6913668016526399</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.485853066979179</v>
+        <v>-3.726672037361516</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.316246769997501</v>
+        <v>1.219919181844566</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6959102345975093</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.505351523221187</v>
+        <v>-3.746170493603524</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.312608327131776</v>
+        <v>1.216280738978841</v>
       </c>
       <c r="F1982" t="n">
         <v>0.647825593317605</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.461148686135287</v>
+        <v>-3.701967656517624</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.336169064493973</v>
+        <v>1.239841476341038</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6920284304035055</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.49812771379873</v>
+        <v>-3.738946684181067</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.319787453897844</v>
+        <v>1.223459865744909</v>
       </c>
       <c r="F1984" t="n">
         <v>0.729002332194836</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.339836296259458</v>
+        <v>-3.580655266641795</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.434351786096592</v>
+        <v>1.338024197943657</v>
       </c>
       <c r="F1985" t="n">
         <v>0.729002332194836</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.132194292624982</v>
+        <v>-3.373013263007319</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.515849292144636</v>
+        <v>1.419521703991701</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366443358293122</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.081162199902454</v>
+        <v>-3.321981170284791</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.531210357471917</v>
+        <v>1.434882769318982</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876764285518401</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.015938018775248</v>
+        <v>-3.256756989157585</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.574487434015504</v>
+        <v>1.478159845862569</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052900609679046</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.978510998704115</v>
+        <v>-3.219329969086452</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.585419214343238</v>
+        <v>1.489091626190303</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058152147708227</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.998622654738823</v>
+        <v>-3.23944162512116</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.578631344260595</v>
+        <v>1.48230375610766</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069179492705646</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.944877840311618</v>
+        <v>-3.185696810693955</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.760687041052688</v>
+        <v>1.664359452899753</v>
       </c>
       <c r="F1991" t="n">
         <v>1.079242802146108</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.870095579286605</v>
+        <v>-3.110914549668943</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.91071285468051</v>
+        <v>1.814385266527575</v>
       </c>
       <c r="F1992" t="n">
         <v>1.154025063171121</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.844011495022797</v>
+        <v>-3.084830465405135</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.912854464399892</v>
+        <v>1.816526876246957</v>
       </c>
       <c r="F1993" t="n">
         <v>1.154025063171121</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.765880314173851</v>
+        <v>-3.006699284556188</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.94230013232325</v>
+        <v>1.845972544170315</v>
       </c>
       <c r="F1994" t="n">
         <v>1.228201874054806</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.756987852780568</v>
+        <v>-2.997806823162905</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.963411522607355</v>
+        <v>1.86708393445442</v>
       </c>
       <c r="F1995" t="n">
         <v>1.228201874054806</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.925463969750445</v>
+        <v>-3.166282940132783</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.887876123223988</v>
+        <v>1.791548535071053</v>
       </c>
       <c r="F1996" t="n">
         <v>1.200254038338225</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.227664440888862</v>
+        <v>-2.468483411271199</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.148265631956483</v>
+        <v>2.051938043803548</v>
       </c>
       <c r="F1997" t="n">
         <v>1.129905978967814</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.20494333720571</v>
+        <v>-2.445762307588047</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.148018095926648</v>
+        <v>2.051690507773714</v>
       </c>
       <c r="F1998" t="n">
         <v>1.129905978967814</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.334145150499752</v>
+        <v>-2.574964120882089</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.2552434964602</v>
+        <v>2.158915908307265</v>
       </c>
       <c r="F1999" t="n">
         <v>1.000704165673772</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.488926157278008</v>
+        <v>-2.729745127660345</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.230408916242545</v>
+        <v>2.13408132808961</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9673364916192959</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.481871467062834</v>
+        <v>-2.722690437445171</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.229906148318159</v>
+        <v>2.133578560165224</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9743911818344697</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.454920242736346</v>
+        <v>-2.695739213118683</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.250692791693496</v>
+        <v>2.154365203540561</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9892715278621889</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.590873250792662</v>
+        <v>-2.831692221175</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.380414720615929</v>
+        <v>2.284087132462994</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9892715278621889</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.613281368597534</v>
+        <v>-2.854100338979872</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.363568168396974</v>
+        <v>2.267240580244039</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9892715278621889</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.761287136076934</v>
+        <v>-3.002106106459271</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.306419860954851</v>
+        <v>2.210092272801917</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9025445189986474</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.770728061965464</v>
+        <v>-3.011547032347801</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.358897208321286</v>
+        <v>2.262569620168351</v>
       </c>
       <c r="F2006" t="n">
         <v>1.024971636542039</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.823001669301105</v>
+        <v>-3.063820639683442</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.340878859932331</v>
+        <v>2.244551271779396</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9726980292063977</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.899331646902011</v>
+        <v>-3.140150617284348</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.308458681785743</v>
+        <v>2.212131093632808</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9726980292063977</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.101585367226364</v>
+        <v>-3.342404337608702</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.222377423258864</v>
+        <v>2.126049835105929</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7704443088820443</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.26315379275362</v>
+        <v>-3.503972763135957</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.156184063258115</v>
+        <v>2.05985647510518</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6436613850841649</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.7549119076471</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.395455084851173</v>
+        <v>-3.63627405523351</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.116336953285012</v>
+        <v>2.020009365132077</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6436613850841649</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.397016727666033</v>
+        <v>-3.63783569804837</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.115712296159068</v>
+        <v>2.019384708006133</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6436613850841649</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.424917514775506</v>
+        <v>-3.665736485157843</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.103076022442281</v>
+        <v>2.006748434289346</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6090644609412301</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.5474436174784</v>
+        <v>-3.788262587860737</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.050830025338322</v>
+        <v>1.954502437185387</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4865383582383362</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.777958113663988</v>
+        <v>-4.018777084046325</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.02533018645459</v>
+        <v>1.929002598301655</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2560238620527475</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.034678931658812</v>
+        <v>-4.275497902041149</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.062953578258508</v>
+        <v>1.966625990105573</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1476092879089327</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.188665349434952</v>
+        <v>-4.42948431981729</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.070339280293692</v>
+        <v>1.974011692140757</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1476092879089327</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.138143445607287</v>
+        <v>-4.378962415989624</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.076599243944879</v>
+        <v>1.980271655791944</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1476092879089327</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.390618599615011</v>
+        <v>-4.631437569997348</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.987479671397203</v>
+        <v>1.891152083244268</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1476092879089327</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.660091401536719</v>
+        <v>-4.900910371919056</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.880901085147463</v>
+        <v>1.784573496994529</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1476092879089327</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.817635473266161</v>
+        <v>-5.058454443648498</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.822005198683008</v>
+        <v>1.725677610530073</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08070748276865819</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.095599868849434</v>
+        <v>-5.336418839231771</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.705897293185888</v>
+        <v>1.609569705032953</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.008912251516826064</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.212567561488325</v>
+        <v>-5.453386531870662</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.821314272829376</v>
+        <v>1.724986684676441</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.008912251516826064</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.297285503709278</v>
+        <v>-5.538104474091615</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.782273733904809</v>
+        <v>1.685946145751874</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.09402828044487244</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.379220321978162</v>
+        <v>-5.620039292360499</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.759729224165747</v>
+        <v>1.663401636012812</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1039630260319526</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.325482148577899</v>
+        <v>-5.566301118960236</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.790150131981754</v>
+        <v>1.693822543828819</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.05022485263169052</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.215475865100678</v>
+        <v>-5.456294835483015</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.826305532616818</v>
+        <v>1.729977944463883</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02702028071441531</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.072416289359753</v>
+        <v>-5.31323525974209</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.887779373635162</v>
+        <v>1.791451785482228</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01900685412443603</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.770969563887915</v>
+        <v>-5.011788534270252</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.015618946706433</v>
+        <v>1.919291358553499</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2824398713474012</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.795559808123099</v>
+        <v>-5.036378778505436</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.00675402676507</v>
+        <v>1.910426438612135</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2824398713474012</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.744521432116579</v>
+        <v>-4.985340402498916</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.028012281547434</v>
+        <v>1.931684693394499</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2824398713474012</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.703382137249948</v>
+        <v>-4.944201107632285</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.063506098368231</v>
+        <v>1.967178510215296</v>
       </c>
       <c r="F2032" t="n">
         <v>0.323579166214032</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.592775997170346</v>
+        <v>-4.833594967552683</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.923932550524007</v>
+        <v>1.827604962371072</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4341853062936341</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.723356731701188</v>
+        <v>-4.964175702083526</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.875202300785634</v>
+        <v>1.778874712632699</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3036045717627915</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.558860397510227</v>
+        <v>-4.799679367892564</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.925427653538101</v>
+        <v>1.829100065385166</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3036045717627915</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.434379916786275</v>
+        <v>-4.675198887168612</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.974407556264111</v>
+        <v>1.878079968111176</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3036045717627915</v>
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.857260774640745</v>
+        <v>3.592633526050308</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.451858409062267</v>
+        <v>-4.524987088159608</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.977284938478787</v>
+        <v>1.94803346683985</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2861260794867997</v>
+        <v>0.4538163707717956</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.930060374109521</v>
+        <v>4.030674548880518</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.7%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-668.6%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.5%</t>
+          <t>451.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.1%</t>
+          <t>-629.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-267.8%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-187.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-178.6%</t>
+          <t>-194.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>-52.6%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.9622078420698927</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.736089201185021</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9508186054150913</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.738469691966182</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.368572628961928</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.569294974052511</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9880615826826838</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65870429556736</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.45310852400926</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
         <v>1.012143377422864</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.866708353920437</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.374799045221954</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
         <v>1.012143377422864</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.928886765081407</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.345009137095555</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
         <v>0.9499649662618935</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.29495549222606</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.191665945544142</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5838962391172409</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.503446273677744</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.128607922702237</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3754054576655564</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.750647458442966</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.037826199204717</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3955588111643689</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.243032486467063</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.84197858003881</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.09682621685972786</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.628212877397135</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.686448962479644</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.878083557411717</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.588269813928428</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.084595334298738</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.501771161829877</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.40393940937924</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.375806458497936</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.835745202529028</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.189417028705426</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.07043919666158</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.083824206054495</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.406101843892032</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9481397388182793</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.482546174094904</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9240495669713722</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.847673556733651</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7772531289217053</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.256262333914329</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6125791620641929</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.370022745937193</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5622604297265075</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.786414620224191</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3936977306205858</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.03068602095126</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3062478609984369</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.373944540594279</v>
+        <v>-7.133125570211944</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1650440182869248</v>
+        <v>0.2613716064398588</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.422147357836623</v>
+        <v>-7.181328387454288</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.144167811444988</v>
+        <v>0.2404953995979224</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.718808699646821</v>
+        <v>-7.477989729264485</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.02928225065011736</v>
+        <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.905528407956123</v>
+        <v>-7.664709437573788</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.04943193720800698</v>
+        <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.288529796698754</v>
+        <v>-8.047710826316418</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.202734594026643</v>
+        <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.293016241900142</v>
+        <v>-8.052197271517807</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2019576561357685</v>
+        <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.652546564404144</v>
+        <v>-8.411727594021809</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3404194818393189</v>
+        <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.702895627858366</v>
+        <v>-8.462076657476031</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.35264308726383</v>
+        <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.800514905279762</v>
+        <v>-8.559695934897427</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3886490476106199</v>
+        <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.854586404788121</v>
+        <v>-8.613767434405785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4073840910923909</v>
+        <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.058844580117984</v>
+        <v>-8.818025609735649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4835741641056943</v>
+        <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.092497418626458</v>
+        <v>-8.851678448244122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4925527450246476</v>
+        <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.019027586959009</v>
+        <v>-8.778208616576674</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4477931108642466</v>
+        <v>-0.3514655227113126</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.194152004345552</v>
+        <v>-8.953333033963217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5032876570713474</v>
+        <v>-0.406960068918413</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.428604098360042</v>
+        <v>-9.187785127977707</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.604287659578739</v>
+        <v>-0.507960071425805</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.532978829386488</v>
+        <v>-9.292159859004153</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6527097427632937</v>
+        <v>-0.5563821546103598</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.585764984986815</v>
+        <v>-9.34494601460448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6727084151648683</v>
+        <v>-0.5763808270119339</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.711801778355104</v>
+        <v>-9.470982807972769</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7204294038830694</v>
+        <v>-0.624101815730135</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.654730006459173</v>
+        <v>-9.413911036076838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6936103594382961</v>
+        <v>-0.5972827712853621</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.796401848183294</v>
+        <v>-9.555582877800958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7517543230266859</v>
+        <v>-0.6554267348737519</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.746811003758459</v>
+        <v>-9.505992033376124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7168645750918801</v>
+        <v>-0.6205369869389457</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.597892669286603</v>
+        <v>-9.357073698904268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6703483749498202</v>
+        <v>-0.5740207867968863</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.372047516567193</v>
+        <v>-9.131228546184857</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5704312408258478</v>
+        <v>-0.4741036526729134</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.247468860229601</v>
+        <v>-9.006649889847266</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5194606337347518</v>
+        <v>-0.4231330455818179</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.300364148273887</v>
+        <v>-9.059545177891552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5379849747903589</v>
+        <v>-0.4416573866374249</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.228230972986006</v>
+        <v>-8.987412002603671</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5033980004365701</v>
+        <v>-0.4070704122836357</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.156864580376359</v>
+        <v>-8.916045609994024</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4845887057865763</v>
+        <v>-0.3882611176336423</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.063405546391134</v>
+        <v>-8.822586576008799</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.457088573505394</v>
+        <v>-0.36076098535246</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.796163745522737</v>
+        <v>-8.555344775140401</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3520264136574087</v>
+        <v>-0.2556988255044748</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.698256706846246</v>
+        <v>-8.457437736463911</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3131639131602735</v>
+        <v>-0.2168363250073391</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.674303165870288</v>
+        <v>-8.433484195487953</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3029139906243965</v>
+        <v>-0.2065864024714625</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.410243227547491</v>
+        <v>-8.169424257165156</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2105503314570298</v>
+        <v>-0.1142227433040959</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.703163604042653</v>
+        <v>-7.462344633660318</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.06949448428460459</v>
+        <v>0.1658220724375385</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.662979305676463</v>
+        <v>-7.422160335294127</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.08591182751892212</v>
+        <v>0.1822394156718561</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.4995794347371</v>
+        <v>-7.258760464354765</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.150638597115424</v>
+        <v>0.246966185268358</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.266098212507502</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2519555148451156</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.116431821499987</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3089298609351627</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.9841563478691</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3572075371345442</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.828418015309358</v>
+        <v>-6.587599044927023</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4223179308460776</v>
+        <v>0.518645518999012</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.579418216625777</v>
+        <v>-6.338599246243442</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5348241915431688</v>
+        <v>0.6311517796961028</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2472458891152278</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.685008206398882</v>
+        <v>-6.444189236016546</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3646122660347082</v>
+        <v>0.4609398541876426</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3528358788883322</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.703743108517479</v>
+        <v>-6.462924138135143</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4056626470643558</v>
+        <v>0.5019902352172902</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3584318885484635</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.555803067109879</v>
+        <v>-6.314984096727544</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.344959740939228</v>
+        <v>0.4412873290921624</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3381109726399059</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.502833544855891</v>
+        <v>-6.262014574473556</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3574335635873451</v>
+        <v>0.4537611517402795</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.285141450385917</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.459285138085201</v>
+        <v>-6.218466167702865</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3678923142005281</v>
+        <v>0.4642199023534626</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.285141450385917</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.425921931606432</v>
+        <v>-6.185102961224096</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3956999511731789</v>
+        <v>0.4920275393261129</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.285141450385917</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.31766279448391</v>
+        <v>-6.076843824101575</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4335357264813826</v>
+        <v>0.5298633146343166</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.285141450385917</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.194371659666779</v>
+        <v>-5.953552689284444</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4803502744188117</v>
+        <v>0.5766778625717461</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1618503155687865</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.173222460763336</v>
+        <v>-5.932403490381001</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4965109322175145</v>
+        <v>0.5928385203704485</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1407011166653432</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.929457018779892</v>
+        <v>-5.688638048397556</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.589797817357943</v>
+        <v>0.686125405510877</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1407011166653432</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.827694198502597</v>
+        <v>-5.586875228120261</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6326272593888769</v>
+        <v>0.7289548475418108</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1274820482729145</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.577843804553522</v>
+        <v>-5.337024834171187</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.725309491952209</v>
+        <v>0.8216370801051429</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1274820482729145</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.40195171208609</v>
+        <v>-5.161132741703755</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7992654524598302</v>
+        <v>0.8955930406127646</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1274820482729145</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.230505249063627</v>
+        <v>-4.989686278681291</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8811715437233696</v>
+        <v>0.9774991318763036</v>
       </c>
       <c r="F1921" t="n">
         <v>0.04396441474954865</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.156215683325287</v>
+        <v>-4.915396712942952</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9099078476350022</v>
+        <v>1.006235435787936</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1182539804878879</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.092579941091353</v>
+        <v>-4.851760970709018</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9400569455828931</v>
+        <v>1.036384533735827</v>
       </c>
       <c r="F1923" t="n">
         <v>0.1818897227218225</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.981153181765433</v>
+        <v>-4.740334211383098</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9658219080970567</v>
+        <v>1.062149496249991</v>
       </c>
       <c r="F1924" t="n">
         <v>0.1818897227218225</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.740722684960573</v>
+        <v>-4.499903714578237</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.063737183443878</v>
+        <v>1.160064771596812</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4223202195266827</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.668480116789378</v>
+        <v>-4.427661146407043</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.096563524547176</v>
+        <v>1.192891112700111</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4223202195266827</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.650766429911513</v>
+        <v>-4.409947459529177</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.104327583215662</v>
+        <v>1.200655171368597</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4255015484235996</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.541961544431786</v>
+        <v>-4.30114257404945</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.144847608627547</v>
+        <v>1.241175196780481</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4255015484235996</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.321940746394775</v>
+        <v>-4.08112177601244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.234434964852965</v>
+        <v>1.330762553005899</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5667213934915798</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.189073057331497</v>
+        <v>-3.948254086949162</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.3034762232801</v>
+        <v>1.399803811433034</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5667213934915798</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.068899973966999</v>
+        <v>-3.828081003584662</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.352691301066201</v>
+        <v>1.449018889219135</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6868944768560787</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.924227828867261</v>
+        <v>-3.683408858484925</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.420648261667536</v>
+        <v>1.51697584982047</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8315666219558162</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.984102656224954</v>
+        <v>-3.743283685842617</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.382735822125885</v>
+        <v>1.479063410278819</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7716917945981241</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.864282425314116</v>
+        <v>-3.62346345493178</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.445953083724428</v>
+        <v>1.542280671877363</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7716917945981241</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.866752131775922</v>
+        <v>-3.625933161393586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.352609400462147</v>
+        <v>1.448936988615082</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7692220881363179</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.935122318099932</v>
+        <v>-3.694303347717596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.244523187417845</v>
+        <v>1.340850775570779</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7784977871725328</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.948910370946979</v>
+        <v>-3.708091400564642</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.229444674910917</v>
+        <v>1.325772263063852</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7784977871725328</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.004430446839568</v>
+        <v>-3.763611476457232</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.344267481246084</v>
+        <v>1.440595069399018</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7784977871725328</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.828956187047099</v>
+        <v>-3.588137216664763</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.419024417154859</v>
+        <v>1.515352005307794</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7784977871725328</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.939892439688347</v>
+        <v>-3.699073469306011</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.350391944859567</v>
+        <v>1.446719533012502</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7784977871725328</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.906228894216066</v>
+        <v>-3.665409923833729</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.29239567644993</v>
+        <v>1.388723264602864</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8121613326448147</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.846376275012342</v>
+        <v>-3.605557304630006</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.326509110563551</v>
+        <v>1.422836698716486</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8121613326448147</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.760132811985965</v>
+        <v>-3.519313841603629</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.355952766347962</v>
+        <v>1.452280354500897</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8121613326448147</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.805439631384945</v>
+        <v>-3.564620661002609</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.329605814032896</v>
+        <v>1.425933402185831</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7713511696355839</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.834472736087247</v>
+        <v>-3.59365376570491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.318544445185077</v>
+        <v>1.414872033338011</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7713511696355839</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.741662254636387</v>
+        <v>-3.500843284254051</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.284941329656786</v>
+        <v>1.381268917809721</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8641616510864433</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.786051723965815</v>
+        <v>-3.545232753583479</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.269059017849616</v>
+        <v>1.365386606002551</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8197721817570156</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.902593329071158</v>
+        <v>-3.661774358688822</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.217518084319202</v>
+        <v>1.313845672472136</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7032305766516729</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.790216327888485</v>
+        <v>-3.778808689329874</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.267960180622938</v>
+        <v>1.272523236046383</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7032305766516729</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.817996725789838</v>
+        <v>-3.806589087231227</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.268345223230936</v>
+        <v>1.27290827865438</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6754501787503198</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.936377398519977</v>
+        <v>-3.924969759961366</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.059348674139534</v>
+        <v>1.063911729562978</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6082323265993436</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.044991476963308</v>
+        <v>-4.033583838404697</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.136052703481407</v>
+        <v>1.140615758904852</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6082323265993436</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.009582438715165</v>
+        <v>-3.998174800156554</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.164729344882987</v>
+        <v>1.169292400306432</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6082323265993436</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.971198776157014</v>
+        <v>-3.959791137598403</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.177502251248617</v>
+        <v>1.182065306672061</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6466159891574947</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.794082446121847</v>
+        <v>-3.782674807563237</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.245077812107985</v>
+        <v>1.249640867531429</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6466159891574947</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.839174690955393</v>
+        <v>-3.827767052396783</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.22772430593648</v>
+        <v>1.232287361359924</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5847199459881049</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.659799269716626</v>
+        <v>-3.648391631158015</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.293261449738401</v>
+        <v>1.297824505161845</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7414967041588236</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.704813483237232</v>
+        <v>-3.693405844678621</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.256063219661748</v>
+        <v>1.260626275085193</v>
       </c>
       <c r="F1958" t="n">
         <v>0.711147808844219</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.971817993509667</v>
+        <v>-3.960410354951057</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.15495297789172</v>
+        <v>1.159516033315164</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5167847708012705</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.07301577494684</v>
+        <v>-4.061608136388229</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.113677787213352</v>
+        <v>1.118240842636796</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4483759572559513</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.066504808332527</v>
+        <v>-4.055097169773917</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.113882135413394</v>
+        <v>1.118445190836838</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4483759572559513</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.04746668062523</v>
+        <v>-4.036059042066619</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.118022105704558</v>
+        <v>1.122585161128002</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3901923459247568</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.078593311775848</v>
+        <v>-4.067185673217238</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.224865854878501</v>
+        <v>1.229428910301945</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3901923459247568</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.092460073109766</v>
+        <v>-4.081052434551156</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.220152479331067</v>
+        <v>1.224715534754512</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3523344291909338</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.047655901569836</v>
+        <v>-4.036248263011226</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.244082678343965</v>
+        <v>1.24864573376741</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3523344291909338</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.899912931334834</v>
+        <v>-3.888505292776224</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.201130087715166</v>
+        <v>1.20569314313861</v>
       </c>
       <c r="F1966" t="n">
         <v>0.520141786425817</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.001927613866055</v>
+        <v>-3.990519975307445</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.163117836234158</v>
+        <v>1.167680891657602</v>
       </c>
       <c r="F1967" t="n">
         <v>0.520141786425817</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.995774907813271</v>
+        <v>-3.98436726925466</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.16624126704693</v>
+        <v>1.170804322470375</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5262944924786013</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.012584205963773</v>
+        <v>-4.001176567405162</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.15859802452684</v>
+        <v>1.163161079950284</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5094851943280996</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.950286207187651</v>
+        <v>-3.93887856862904</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.249852777834109</v>
+        <v>1.254415833257554</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5094851943280996</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.748496009522493</v>
+        <v>-3.737088370963882</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.1328608586143</v>
+        <v>1.137423914037744</v>
       </c>
       <c r="F1971" t="n">
         <v>0.707503386497254</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.799382722208688</v>
+        <v>-3.787975083650077</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.182796405861997</v>
+        <v>1.187359461285441</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6566166738110595</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.897123266833662</v>
+        <v>-3.885715628275051</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.158327924128051</v>
+        <v>1.162890979551495</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6407273956780792</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.957332564838946</v>
+        <v>-3.945924926280336</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.132780185750609</v>
+        <v>1.137343241174053</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5805180976727947</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.88091051840702</v>
+        <v>-3.869502879848409</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.161840622363308</v>
+        <v>1.166403677786752</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5805180976727947</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.836537386768451</v>
+        <v>-3.82512974820984</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.179452742454172</v>
+        <v>1.184015797877616</v>
       </c>
       <c r="F1976" t="n">
         <v>0.6248912293113633</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.859017737627336</v>
+        <v>-3.847610099068725</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.164854396249208</v>
+        <v>1.169417451672653</v>
       </c>
       <c r="F1977" t="n">
         <v>0.6248912293113633</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.81136200706628</v>
+        <v>-3.79995436850767</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.190298445501435</v>
+        <v>1.19486150092488</v>
       </c>
       <c r="F1978" t="n">
         <v>0.672546959872419</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.710843848567525</v>
+        <v>-3.699436210008915</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.235398082275662</v>
+        <v>1.239961137699106</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7730651183711735</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.771510438969914</v>
+        <v>-3.760102800411304</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.197886118590578</v>
+        <v>1.202449174014023</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6913668016526399</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.726672037361516</v>
+        <v>-3.715264398802906</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.219919181844566</v>
+        <v>1.224482237268011</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6959102345975093</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.746170493603524</v>
+        <v>-3.734762855044914</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.216280738978841</v>
+        <v>1.220843794402285</v>
       </c>
       <c r="F1982" t="n">
         <v>0.647825593317605</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.701967656517624</v>
+        <v>-3.690560017959014</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.239841476341038</v>
+        <v>1.244404531764483</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6920284304035055</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.738946684181067</v>
+        <v>-3.727539045622457</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.223459865744909</v>
+        <v>1.228022921168353</v>
       </c>
       <c r="F1984" t="n">
         <v>0.729002332194836</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.580655266641795</v>
+        <v>-3.569247628083185</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.338024197943657</v>
+        <v>1.342587253367101</v>
       </c>
       <c r="F1985" t="n">
         <v>0.729002332194836</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.373013263007319</v>
+        <v>-3.361605624448709</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.419521703991701</v>
+        <v>1.424084759415145</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366443358293122</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.321981170284791</v>
+        <v>-3.310573531726181</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.434882769318982</v>
+        <v>1.439445824742426</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876764285518401</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.256756989157585</v>
+        <v>-3.245349350598975</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.478159845862569</v>
+        <v>1.482722901286013</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052900609679046</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.219329969086452</v>
+        <v>-3.207922330527841</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.489091626190303</v>
+        <v>1.493654681613747</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058152147708227</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.23944162512116</v>
+        <v>-3.22803398656255</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.48230375610766</v>
+        <v>1.486866811531104</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069179492705646</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.185696810693955</v>
+        <v>-3.174289172135345</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.664359452899753</v>
+        <v>1.668922508323197</v>
       </c>
       <c r="F1991" t="n">
         <v>1.079242802146108</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.110914549668943</v>
+        <v>-3.099506911110332</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.814385266527575</v>
+        <v>1.818948321951019</v>
       </c>
       <c r="F1992" t="n">
         <v>1.154025063171121</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.084830465405135</v>
+        <v>-3.073422826846524</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.816526876246957</v>
+        <v>1.821089931670401</v>
       </c>
       <c r="F1993" t="n">
         <v>1.154025063171121</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.006699284556188</v>
+        <v>-2.995291645997578</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.845972544170315</v>
+        <v>1.85053559959376</v>
       </c>
       <c r="F1994" t="n">
         <v>1.228201874054806</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.997806823162905</v>
+        <v>-2.986399184604295</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.86708393445442</v>
+        <v>1.871646989877864</v>
       </c>
       <c r="F1995" t="n">
         <v>1.228201874054806</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.166282940132783</v>
+        <v>-3.154875301574172</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.791548535071053</v>
+        <v>1.796111590494497</v>
       </c>
       <c r="F1996" t="n">
         <v>1.200254038338225</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.468483411271199</v>
+        <v>-2.457075772712589</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.051938043803548</v>
+        <v>2.056501099226992</v>
       </c>
       <c r="F1997" t="n">
         <v>1.129905978967814</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.445762307588047</v>
+        <v>-2.434354669029437</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.051690507773714</v>
+        <v>2.056253563197158</v>
       </c>
       <c r="F1998" t="n">
         <v>1.129905978967814</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.574964120882089</v>
+        <v>-2.563556482323479</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.158915908307265</v>
+        <v>2.16347896373071</v>
       </c>
       <c r="F1999" t="n">
         <v>1.000704165673772</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.729745127660345</v>
+        <v>-2.718337489101735</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.13408132808961</v>
+        <v>2.138644383513054</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9673364916192959</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.722690437445171</v>
+        <v>-2.711282798886561</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.133578560165224</v>
+        <v>2.138141615588669</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9743911818344697</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.695739213118683</v>
+        <v>-2.684331574560073</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.154365203540561</v>
+        <v>2.158928258964005</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9892715278621889</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.831692221175</v>
+        <v>-2.820284582616389</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.284087132462994</v>
+        <v>2.288650187886438</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9892715278621889</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.854100338979872</v>
+        <v>-2.842692700421261</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.267240580244039</v>
+        <v>2.271803635667483</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9892715278621889</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.002106106459271</v>
+        <v>-2.990698467900661</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.210092272801917</v>
+        <v>2.21465532822536</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9025445189986474</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.011547032347801</v>
+        <v>-3.000139393789191</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.262569620168351</v>
+        <v>2.267132675591796</v>
       </c>
       <c r="F2006" t="n">
         <v>1.024971636542039</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.063820639683442</v>
+        <v>-3.052413001124832</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.244551271779396</v>
+        <v>2.24911432720284</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9726980292063977</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.140150617284348</v>
+        <v>-3.128742978725738</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.212131093632808</v>
+        <v>2.216694149056253</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9726980292063977</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.342404337608702</v>
+        <v>-3.330996699050091</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.126049835105929</v>
+        <v>2.130612890529374</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7704443088820443</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.503972763135957</v>
+        <v>-3.492565124577347</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.05985647510518</v>
+        <v>2.064419530528624</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6436613850841649</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.63627405523351</v>
+        <v>-3.6248664166749</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.020009365132077</v>
+        <v>2.024572420555521</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6436613850841649</v>
@@ -47827,10 +47827,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.63783569804837</v>
+        <v>-3.62642805948976</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.019384708006133</v>
+        <v>2.023947763429577</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6436613850841649</v>
@@ -47850,10 +47850,10 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.665736485157843</v>
+        <v>-3.654328846599233</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.006748434289346</v>
+        <v>2.01131148971279</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6090644609412301</v>
@@ -47873,10 +47873,10 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.788262587860737</v>
+        <v>-3.776854949302127</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.954502437185387</v>
+        <v>1.959065492608831</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4865383582383362</v>
@@ -47896,10 +47896,10 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.018777084046325</v>
+        <v>-4.007369445487715</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.929002598301655</v>
+        <v>1.9335656537251</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2560238620527475</v>
@@ -47919,10 +47919,10 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.275497902041149</v>
+        <v>-4.264090263482538</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.966625990105573</v>
+        <v>1.971189045529017</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1476092879089327</v>
@@ -47942,10 +47942,10 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.42948431981729</v>
+        <v>-4.418076681258679</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.974011692140757</v>
+        <v>1.978574747564201</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1476092879089327</v>
@@ -47965,10 +47965,10 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.378962415989624</v>
+        <v>-4.367554777431013</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.980271655791944</v>
+        <v>1.984834711215388</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1476092879089327</v>
@@ -47988,10 +47988,10 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.631437569997348</v>
+        <v>-4.620029931438737</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.891152083244268</v>
+        <v>1.895715138667712</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1476092879089327</v>
@@ -48011,10 +48011,10 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.900910371919056</v>
+        <v>-4.889502733360445</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.784573496994529</v>
+        <v>1.789136552417973</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1476092879089327</v>
@@ -48034,10 +48034,10 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.058454443648498</v>
+        <v>-5.047046805089887</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.725677610530073</v>
+        <v>1.730240665953517</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08070748276865819</v>
@@ -48057,10 +48057,10 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.336418839231771</v>
+        <v>-5.325011200673161</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.609569705032953</v>
+        <v>1.614132760456398</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.008912251516826064</v>
@@ -48080,10 +48080,10 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.453386531870662</v>
+        <v>-5.441978893312052</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.724986684676441</v>
+        <v>1.729549740099885</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.008912251516826064</v>
@@ -48103,10 +48103,10 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.538104474091615</v>
+        <v>-5.526696835533005</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.685946145751874</v>
+        <v>1.690509201175318</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.09402828044487244</v>
@@ -48126,10 +48126,10 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.620039292360499</v>
+        <v>-5.608631653801888</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.663401636012812</v>
+        <v>1.667964691436256</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1039630260319526</v>
@@ -48149,10 +48149,10 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.566301118960236</v>
+        <v>-5.554893480401626</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.693822543828819</v>
+        <v>1.698385599252263</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.05022485263169052</v>
@@ -48172,10 +48172,10 @@
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.456294835483015</v>
+        <v>-5.444887196924404</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.729977944463883</v>
+        <v>1.734540999887328</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02702028071441531</v>
@@ -48195,10 +48195,10 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.31323525974209</v>
+        <v>-5.301827621183479</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.791451785482228</v>
+        <v>1.796014840905672</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01900685412443603</v>
@@ -48218,10 +48218,10 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.011788534270252</v>
+        <v>-5.000380895711642</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.919291358553499</v>
+        <v>1.923854413976943</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2824398713474012</v>
@@ -48241,10 +48241,10 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.036378778505436</v>
+        <v>-5.024971139946826</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.910426438612135</v>
+        <v>1.914989494035579</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2824398713474012</v>
@@ -48264,10 +48264,10 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.985340402498916</v>
+        <v>-4.973932763940305</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.931684693394499</v>
+        <v>1.936247748817943</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2824398713474012</v>
@@ -48287,10 +48287,10 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.944201107632285</v>
+        <v>-4.932793469073674</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.967178510215296</v>
+        <v>1.971741565638741</v>
       </c>
       <c r="F2032" t="n">
         <v>0.323579166214032</v>
@@ -48310,10 +48310,10 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.833594967552683</v>
+        <v>-4.822187328994072</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.827604962371072</v>
+        <v>1.832168017794516</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4341853062936341</v>
@@ -48333,10 +48333,10 @@
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.964175702083526</v>
+        <v>-4.952768063524915</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.778874712632699</v>
+        <v>1.783437768056143</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3036045717627915</v>
@@ -48356,10 +48356,10 @@
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.799679367892564</v>
+        <v>-4.788271729333953</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.829100065385166</v>
+        <v>1.83366312080861</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3036045717627915</v>
@@ -48379,10 +48379,10 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.675198887168612</v>
+        <v>-4.663791248610002</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.878079968111176</v>
+        <v>1.88264302353462</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3036045717627915</v>
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.592633526050308</v>
+        <v>3.459093953841843</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.524987088159608</v>
+        <v>-4.674176443499891</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.94803346683985</v>
+        <v>1.888357724703737</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4538163707717956</v>
+        <v>0.2932193768729022</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.030674548880518</v>
+        <v>3.934316352541183</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-639.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.1%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-629.0%</t>
+          <t>-600.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-256.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-187.4%</t>
+          <t>-176.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-258.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-183.7%</t>
+          <t>-209.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-194.7%</t>
+          <t>-189.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-155.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-52.6%</t>
+          <t>-49.3%</t>
         </is>
       </c>
     </row>
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.073588152288091</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.687288764722045</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>1.042227088974184</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.74241670333554</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.363719818893523</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.571102314678795</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>1.066308883714364</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.75673199677857</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.5717238772466</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.492792835891489</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>1.066308883714364</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.761624141332495</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.63390228840757</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.463002927765089</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>1.004130472553394</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.719398550973901</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-1.999971015552223</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.309659736213677</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.6380617454087415</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.492841613993559</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.208461797003907</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.246601713371772</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.4295709639570571</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.388085434861317</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.455662981769129</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.155819989874252</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.4497243174558695</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.408276197369172</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-2.948048009793226</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.959972370708345</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.04266071056822723</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.113951572598447</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.333228400723298</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.804442753149179</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.04266071056822723</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.11249411141131</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.58309908073788</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.706263604597963</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.006397990737763981</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.136020866764204</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-3.789610857624901</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.619764952499412</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.2129097676247855</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>3.008219859288249</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.108954932705403</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.493800249167471</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.2129097676247855</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>3.009992785988509</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.540760725855191</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.30741081937496</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.3493272640660525</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.914475175591153</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.775454719987743</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.20181799672403</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.3429909968367973</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.906561710930796</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.111117367218196</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.066133529487814</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.4109219823257021</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.864383711293419</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.187561697421067</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>1.042043357640907</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.3304764732320402</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.919138576983857</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.552689080059814</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.8952469195912398</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.6267872575310527</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.740606621410281</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.961277857240493</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7305729527337275</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.494214899116633</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.075038269263358</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.680254220396042</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.489400331588094</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.491430143550355</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.5116915212901203</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.487394382196971</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.735701544277425</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4242416516679715</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.49765307286565</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.133125570211944</v>
+        <v>-7.078960063920444</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2613716064398588</v>
+        <v>0.2830378089564589</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.493752638011346</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.181328387454288</v>
+        <v>-7.127162881162787</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2404953995979224</v>
+        <v>0.2621616021145226</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.492157558066347</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.477989729264485</v>
+        <v>-7.423824222972985</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1256098388030513</v>
+        <v>0.1472760413196519</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.10411917044561</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.454690652555227</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.664709437573788</v>
+        <v>-7.610543931282288</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04689565094492743</v>
+        <v>0.06856185346152754</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.10411917044561</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.450664348020824</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.047710826316418</v>
+        <v>-7.993545320024919</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.106407005873709</v>
+        <v>-0.08474080335710887</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.10411917044561</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.45056224669924</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.052197271517807</v>
+        <v>-7.998031765226307</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1056300679828341</v>
+        <v>-0.08396386546623447</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.108605615646998</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.450441895549837</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.411727594021809</v>
+        <v>-8.35756208773031</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2440918936863845</v>
+        <v>-0.2224256911697853</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.108605615646998</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.455792198847887</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.462076657476031</v>
+        <v>-8.407911151184532</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.256315499110896</v>
+        <v>-0.2346492965942963</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.15895467910122</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.433498780732532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.559695934897427</v>
+        <v>-8.505530428605928</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2923214594576855</v>
+        <v>-0.2706552569410863</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.256573956522617</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.377968964901462</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.613767434405785</v>
+        <v>-8.559601928114287</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.311056502939457</v>
+        <v>-0.2893903004228573</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.310645456030977</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.348419621518019</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.818025609735649</v>
+        <v>-8.76386010344415</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3872465759527599</v>
+        <v>-0.3655803734361607</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.438284400644966</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.277349451868268</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.851678448244122</v>
+        <v>-8.797512941952624</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3962251568717132</v>
+        <v>-0.374558954355114</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.538697768562003</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.221583985602482</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.778208616576674</v>
+        <v>-8.724043110285175</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3514655227113126</v>
+        <v>-0.3297993201947129</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.465227936894554</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.281037586096372</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.953333033963217</v>
+        <v>-8.899167527671718</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.406960068918413</v>
+        <v>-0.3852938664018137</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.640352354281098</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.190518156411962</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.187785127977707</v>
+        <v>-9.133619621686208</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.507960071425805</v>
+        <v>-0.4862938689092053</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.640352354281098</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.183298991510366</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.292159859004153</v>
+        <v>-9.237994352712654</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5563821546103598</v>
+        <v>-0.5347159520937601</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.744727085307544</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.114001962120523</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.34494601460448</v>
+        <v>-9.290780508312981</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5763808270119339</v>
+        <v>-0.5547146244953347</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.840402571889941</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.057712460009641</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.470982807972769</v>
+        <v>-9.41681730168127</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.624101815730135</v>
+        <v>-0.6024356132135358</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815150949080199</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.075557162324601</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.413911036076838</v>
+        <v>-9.359745529785339</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5972827712853621</v>
+        <v>-0.5756165687687624</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815150949080199</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.079547498011002</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.555582877800958</v>
+        <v>-9.50141737150946</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6554267348737519</v>
+        <v>-0.6337605323571522</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815150949080199</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.07807227111226</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.505992033376124</v>
+        <v>-9.451826527084625</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6205369869389457</v>
+        <v>-0.5988707844223464</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.765560104655365</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.122880187932032</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.357073698904268</v>
+        <v>-9.302908192612769</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5740207867968863</v>
+        <v>-0.5523545842802866</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.734310513920192</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.128578808726453</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.131228546184857</v>
+        <v>-9.077063039893357</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4741036526729134</v>
+        <v>-0.4524374501563133</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.692383838333028</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.16331388711496</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.006649889847266</v>
+        <v>-8.952484383555765</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4231330455818179</v>
+        <v>-0.4014668430652177</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.692383838333028</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.164453031671019</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.059545177891552</v>
+        <v>-9.005379671600052</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4416573866374249</v>
+        <v>-0.4199911841208248</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.687428492244582</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.170060013486195</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.987412002603671</v>
+        <v>-8.93324649631217</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4070704122836357</v>
+        <v>-0.3854042097670356</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.687428492244582</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.175793717724831</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.916045609994024</v>
+        <v>-8.861880103702523</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3882611176336423</v>
+        <v>-0.3665949151170418</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.616062099634934</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.208876290896755</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.822586576008799</v>
+        <v>-8.768421069717299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.36076098535246</v>
+        <v>-0.3390947828358599</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.616062099634934</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.198992809583847</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.555344775140401</v>
+        <v>-8.501179268848901</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2556988255044748</v>
+        <v>-0.2340326229878742</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.616062099634934</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.197158249084473</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.457437736463911</v>
+        <v>-8.40327223017241</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2168363250073391</v>
+        <v>-0.195170122490739</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.548076349774378</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.237649384027346</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.433484195487953</v>
+        <v>-8.379318689196452</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2065864024714625</v>
+        <v>-0.184920199954862</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.52412280879842</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.252690014758414</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.169424257165156</v>
+        <v>-8.115258750873656</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1142227433040959</v>
+        <v>-0.09255654078749576</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.260062870475624</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.39786566159034</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.462344633660318</v>
+        <v>-7.408179127368817</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1658220724375385</v>
+        <v>0.1874882749541387</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.260062870475624</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.395078627930039</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.422160335294127</v>
+        <v>-7.367994829002627</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1822394156718561</v>
+        <v>0.2039056181884562</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.219878572109433</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.419532830837595</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.258760464354765</v>
+        <v>-7.204594958063264</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.246966185268358</v>
+        <v>0.2686323877849581</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.056478701170071</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.516939574621969</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-6.971113735833666</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.3699493055146501</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8229974789404721</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.664952736797581</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-6.821447344826151</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.4269236516046968</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7300939876979362</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.717802621230143</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-6.689171871195264</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.4752013278040788</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.5978185140670496</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.792535392155702</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.533433538635522</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.5403117215156121</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.442080181507308</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.888793452379184</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.284433739951941</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.6528179822127034</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2472458891152278</v>
+        <v>-0.1930803828237273</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.018600369038091</v>
+        <v>3.051099672812991</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.390023729725046</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.4826060567042427</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3528358788883322</v>
+        <v>-0.2986703725968317</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.827270445575009</v>
+        <v>2.85976974934991</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.462924138135143</v>
+        <v>-6.408758631843643</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5019902352172902</v>
+        <v>0.5236564377338904</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3584318885484635</v>
+        <v>-0.304266382256963</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.872457181656017</v>
+        <v>2.904956485430917</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.314984096727544</v>
+        <v>-6.260818590436044</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4412873290921624</v>
+        <v>0.4629535316087625</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3381109726399059</v>
+        <v>-0.2839454663484054</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.764770808512984</v>
+        <v>2.797270112287884</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.262014574473556</v>
+        <v>-6.207849068182055</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4537611517402795</v>
+        <v>0.4754273542568797</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.787838535611899</v>
+        <v>2.820337839386799</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218466167702865</v>
+        <v>-6.164300661411365</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4642199023534626</v>
+        <v>0.4858861048700627</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.780877923516806</v>
+        <v>2.813377227291706</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185102961224096</v>
+        <v>-6.130937454932596</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4920275393261129</v>
+        <v>0.5136937418427134</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.795340277897949</v>
+        <v>2.827839581672849</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.076843824101575</v>
+        <v>-6.022678317810074</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5298633146343166</v>
+        <v>0.5515295171509171</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.789872398357144</v>
+        <v>2.822371702132044</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953552689284444</v>
+        <v>-5.899387182992943</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5766778625717461</v>
+        <v>0.5983440650883463</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1618503155687865</v>
+        <v>-0.107684809277286</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.861345173257999</v>
+        <v>2.893844477032899</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.932403490381001</v>
+        <v>-5.8782379840895</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5928385203704485</v>
+        <v>0.6145047228870486</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.08653561037384266</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88173567083739</v>
+        <v>2.914234974612291</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.688638048397556</v>
+        <v>-5.634472542106056</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.686125405510877</v>
+        <v>0.7077916080274771</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.08653561037384266</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.877516379184441</v>
+        <v>2.910015682959342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.586875228120261</v>
+        <v>-5.532709721828761</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7289548475418108</v>
+        <v>0.750621050058411</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.07331654198141396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.887572134139914</v>
+        <v>2.920071437914815</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.337024834171187</v>
+        <v>-5.282859327879686</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8216370801051429</v>
+        <v>0.843303282621743</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.07331654198141396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.880314209123616</v>
+        <v>2.912813512898517</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.161132741703755</v>
+        <v>-5.106967235412254</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955930406127646</v>
+        <v>0.9172592431293647</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.07331654198141396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.883913332644265</v>
+        <v>2.916412636419166</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.989686278681291</v>
+        <v>-4.935520772389791</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9774991318763036</v>
+        <v>0.9991653343929037</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04396441474954865</v>
+        <v>0.09812992104104917</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.000108716512297</v>
+        <v>3.032608020287197</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.915396712942952</v>
+        <v>-4.861231206651452</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006235435787936</v>
+        <v>1.027901638304536</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1182539804878879</v>
+        <v>0.1724194867793885</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.043702933571597</v>
+        <v>3.076202237346497</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.851760970709018</v>
+        <v>-4.797595464417517</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036384533735827</v>
+        <v>1.058050736252427</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.236055229013323</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.086579179966275</v>
+        <v>3.119078483741176</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.740334211383098</v>
+        <v>-4.686168705091597</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062149496249991</v>
+        <v>1.083815698766591</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.236055229013323</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.067773438750071</v>
+        <v>3.100272742524971</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.499903714578237</v>
+        <v>-4.445738208286737</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.160064771596812</v>
+        <v>1.181730974113413</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4223202195266827</v>
+        <v>0.4764857258181833</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.213774813457865</v>
+        <v>3.246274117232765</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.427661146407043</v>
+        <v>-4.373495640115542</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.192891112700111</v>
+        <v>1.214557315216711</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4223202195266827</v>
+        <v>0.4764857258181833</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.217704127292685</v>
+        <v>3.250203431067585</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.409947459529177</v>
+        <v>-4.355781953237677</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200655171368597</v>
+        <v>1.222321373885197</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4255015484235996</v>
+        <v>0.4796670547151001</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.220291508548175</v>
+        <v>3.252790812323075</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.30114257404945</v>
+        <v>-4.24697706775795</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241175196780481</v>
+        <v>1.262841399297081</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4255015484235996</v>
+        <v>0.4796670547151001</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.217289579768168</v>
+        <v>3.249788883543069</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.026956269720939</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.352428755522499</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5667213934915798</v>
+        <v>0.6208868997830803</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.303600523819571</v>
+        <v>3.336099827594471</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-3.894088580657661</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.421470013949634</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5667213934915798</v>
+        <v>0.6208868997830803</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.319494706621394</v>
+        <v>3.351994010396294</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-3.773915497293162</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.470685091735735</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6868944768560787</v>
+        <v>0.7410599831475793</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.392744401080395</v>
+        <v>3.425243704855296</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.629243352193424</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.538642052337071</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8315666219558162</v>
+        <v>0.8857321282473167</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.489635790701677</v>
+        <v>3.522135094476578</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-3.689118179551117</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.500729612795419</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7716917945981241</v>
+        <v>0.8258573008896246</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.439748385688488</v>
+        <v>3.472247689463388</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.569297948640279</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.563946874393963</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7716917945981241</v>
+        <v>0.8258573008896246</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.455037554922697</v>
+        <v>3.487536858697597</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.571767655102085</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.470603191131682</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7692220881363179</v>
+        <v>0.8233875944278184</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.361199930368054</v>
+        <v>3.393699234142955</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.640137841426095</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.362516978087379</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.286027211275085</v>
+        <v>3.318526515049985</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.653925894273142</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.347438465580452</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.276463919906976</v>
+        <v>3.308963223681876</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-3.709445970165731</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.462261271915619</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.413494756599178</v>
+        <v>3.445994060374079</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.533971710373262</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.537018207824394</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.418061988590966</v>
+        <v>3.450561292365867</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.644907963014511</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.468385735529102</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.393804017352173</v>
+        <v>3.426303321127074</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.611244417542229</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.410389467119464</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8121613326448147</v>
+        <v>0.8663268389363152</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.342540458036992</v>
+        <v>3.375039761811892</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.551391798338506</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.444502901233086</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8121613326448147</v>
+        <v>0.8663268389363152</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.352712844469124</v>
+        <v>3.385212148244025</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.465148335312128</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.473946557017497</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8121613326448147</v>
+        <v>0.8663268389363152</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.347659115042985</v>
+        <v>3.380158418817885</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.510455154711108</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.447599604702431</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7713511696355839</v>
+        <v>0.8255166759270844</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.314948792681972</v>
+        <v>3.347448096456872</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.53948825941341</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.436538235854612</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7713511696355839</v>
+        <v>0.8255166759270844</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.315500665715073</v>
+        <v>3.347999969489974</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.446677777962551</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.402935120326321</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8641616510864433</v>
+        <v>0.9183271573779438</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.300459646476955</v>
+        <v>3.332958950251855</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.491067247291978</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.387052808519151</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8197721817570156</v>
+        <v>0.8739376880485161</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.275699440803899</v>
+        <v>3.308198744578799</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.661774358688822</v>
+        <v>-3.607608852397321</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.313845672472136</v>
+        <v>1.335511874988737</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7032305766516729</v>
+        <v>0.7573960829431734</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.200850186252416</v>
+        <v>3.233349490027317</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.778808689329874</v>
+        <v>-3.495231851214649</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.272523236046383</v>
+        <v>1.385953971292473</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7032305766516729</v>
+        <v>0.7573960829431734</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.206341482083084</v>
+        <v>3.238840785857984</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.806589087231227</v>
+        <v>-3.523012249116002</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.27290827865438</v>
+        <v>1.386339013900471</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6754501787503198</v>
+        <v>0.7296156850418203</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.201170445110811</v>
+        <v>3.233669748885711</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.924969759961366</v>
+        <v>-3.64139292184614</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.063911729562978</v>
+        <v>1.177342464809069</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6082323265993436</v>
+        <v>0.6623978328908441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.999195453820878</v>
+        <v>3.031694757595778</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.033583838404697</v>
+        <v>-3.750007000289471</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.140615758904852</v>
+        <v>1.254046494150942</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6082323265993436</v>
+        <v>0.6623978328908441</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.119345114540084</v>
+        <v>3.151844418314984</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.998174800156554</v>
+        <v>-3.714597962041328</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.169292400306432</v>
+        <v>1.282723135552522</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6082323265993436</v>
+        <v>0.6623978328908441</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.133858140642407</v>
+        <v>3.166357444417307</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.959791137598403</v>
+        <v>-3.676214299483177</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.182065306672061</v>
+        <v>1.295496041918151</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6466159891574947</v>
+        <v>0.7007814954489953</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.154307779519666</v>
+        <v>3.186807083294567</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.782674807563237</v>
+        <v>-3.499097969448011</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.249640867531429</v>
+        <v>1.363071602777519</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6466159891574947</v>
+        <v>0.7007814954489953</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.151036808364968</v>
+        <v>3.183536112139869</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.827767052396783</v>
+        <v>-3.544190214281556</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.232287361359924</v>
+        <v>1.345718096606014</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5847199459881049</v>
+        <v>0.6388854522796055</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.114582574225247</v>
+        <v>3.147081878000148</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.648391631158015</v>
+        <v>-3.364814793042789</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.297824505161845</v>
+        <v>1.411255240407936</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7414967041588236</v>
+        <v>0.7956622104503241</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.202435604434093</v>
+        <v>3.234934908208993</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.693405844678621</v>
+        <v>-3.409829006563395</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.260626275085193</v>
+        <v>1.374057010331283</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.711147808844219</v>
+        <v>0.7653133151357195</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.16503372257692</v>
+        <v>3.19753302635182</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.960410354951057</v>
+        <v>-3.67683351683583</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.159516033315164</v>
+        <v>1.272946768561255</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5167847708012705</v>
+        <v>0.570950277092771</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.054107462090097</v>
+        <v>3.086606765864997</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.061608136388229</v>
+        <v>-3.778031298273003</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.118240842636796</v>
+        <v>1.231671577882887</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4483759572559513</v>
+        <v>0.5025414635474519</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.012266095859407</v>
+        <v>3.044765399634307</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.055097169773917</v>
+        <v>-3.77152033165869</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.118445190836838</v>
+        <v>1.231875926082929</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4483759572559513</v>
+        <v>0.5025414635474519</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.009866057413723</v>
+        <v>3.042365361188624</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.036059042066619</v>
+        <v>-3.752482203951393</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.122585161128002</v>
+        <v>1.236015896374093</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3901923459247568</v>
+        <v>0.4443578522162573</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.971480609823252</v>
+        <v>3.003979913598152</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.067185673217238</v>
+        <v>-3.783608835102011</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.229428910301945</v>
+        <v>1.342859645548036</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3901923459247568</v>
+        <v>0.4443578522162573</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.090775011457442</v>
+        <v>3.123274315232342</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.081052434551156</v>
+        <v>-3.797475596435929</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.224715534754512</v>
+        <v>1.338146270000602</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3523344291909338</v>
+        <v>0.4064999354824344</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.068893590403281</v>
+        <v>3.101392894178182</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.036248263011226</v>
+        <v>-3.752671424895999</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.24864573376741</v>
+        <v>1.3620764690135</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3523344291909338</v>
+        <v>0.4064999354824344</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.074902120800207</v>
+        <v>3.107401424575108</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.888505292776224</v>
+        <v>-3.604928454660997</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.20569314313861</v>
+        <v>1.319123878384701</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.520141786425817</v>
+        <v>0.5743072927173176</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.073536756418337</v>
+        <v>3.106036060193238</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.990519975307445</v>
+        <v>-3.706943137192217</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.167680891657602</v>
+        <v>1.281111626903693</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.520141786425817</v>
+        <v>0.5743072927173176</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.076330377949818</v>
+        <v>3.108829681724719</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.98436726925466</v>
+        <v>-3.700790431139433</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.170804322470375</v>
+        <v>1.284235057716465</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5262944924786013</v>
+        <v>0.5804599987701019</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.080684349973147</v>
+        <v>3.113183653748047</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.001176567405162</v>
+        <v>-3.717599729289935</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.163161079950284</v>
+        <v>1.276591815196375</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5094851943280996</v>
+        <v>0.5636507006196003</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.069679247822956</v>
+        <v>3.102178551597857</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.93887856862904</v>
+        <v>-3.655301730513813</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.254415833257554</v>
+        <v>1.367846568503645</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5094851943280996</v>
+        <v>0.5636507006196003</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.136014801619777</v>
+        <v>3.168514105394677</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.737088370963882</v>
+        <v>-3.453511532848655</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.137423914037744</v>
+        <v>1.250854649283835</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.707503386497254</v>
+        <v>0.7616688927887547</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.057117718635397</v>
+        <v>3.089617022410297</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.787975083650077</v>
+        <v>-3.504398245534849</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.187359461285441</v>
+        <v>1.300790196531532</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6566166738110595</v>
+        <v>0.7107821801025602</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.096875923345855</v>
+        <v>3.129375227120756</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.885715628275051</v>
+        <v>-3.602138790159824</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.162890979551495</v>
+        <v>1.276321714797586</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6407273956780792</v>
+        <v>0.69489290196958</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.101970092582111</v>
+        <v>3.134469396357011</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.945924926280336</v>
+        <v>-3.662348088165108</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.137343241174053</v>
+        <v>1.250773976420144</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5805180976727947</v>
+        <v>0.6346836039642955</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.064380494603612</v>
+        <v>3.096879798378512</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.869502879848409</v>
+        <v>-3.585926041733182</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.166403677786752</v>
+        <v>1.279834413032843</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5805180976727947</v>
+        <v>0.6346836039642955</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.06287211264354</v>
+        <v>3.095371416418441</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.82512974820984</v>
+        <v>-3.541552910094613</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.184015797877616</v>
+        <v>1.297446533123707</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6248912293113633</v>
+        <v>0.6790567356028641</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.089358859062118</v>
+        <v>3.121858162837018</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.847610099068725</v>
+        <v>-3.564033260953498</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.169417451672653</v>
+        <v>1.282848186918744</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6248912293113633</v>
+        <v>0.6790567356028641</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.083752653200708</v>
+        <v>3.116251956975609</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.79995436850767</v>
+        <v>-3.516377530392442</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.19486150092488</v>
+        <v>1.30829223617097</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.672546959872419</v>
+        <v>0.7267124661639197</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.118727848565146</v>
+        <v>3.151227152340047</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.699436210008915</v>
+        <v>-3.415859371893688</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.239961137699106</v>
+        <v>1.353391872945197</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7730651183711735</v>
+        <v>0.8272306246626743</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.183931117039124</v>
+        <v>3.216430420814024</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.760102800411304</v>
+        <v>-3.476525962296077</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.202449174014023</v>
+        <v>1.315879909260114</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6913668016526399</v>
+        <v>0.7455323079441406</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.121666799483876</v>
+        <v>3.154166103258776</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.715264398802906</v>
+        <v>-3.431687560687679</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.224482237268011</v>
+        <v>1.337912972514101</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6959102345975093</v>
+        <v>0.7500757408890101</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.128490561861426</v>
+        <v>3.160989865636326</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.734762855044914</v>
+        <v>-3.451186016929687</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.220843794402285</v>
+        <v>1.334274529648376</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.647825593317605</v>
+        <v>0.7019910996091058</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.103800716724561</v>
+        <v>3.136300020499462</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.690560017959014</v>
+        <v>-3.406983179843786</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.244404531764483</v>
+        <v>1.357835267010573</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6920284304035055</v>
+        <v>0.7461939366950062</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.136202021503939</v>
+        <v>3.168701325278839</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.727539045622457</v>
+        <v>-3.44396220750723</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.228022921168353</v>
+        <v>1.341453656414444</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.729002332194836</v>
+        <v>0.7831678384863368</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.156796363047984</v>
+        <v>3.189295666822885</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.569247628083185</v>
+        <v>-3.285670789967957</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.342587253367101</v>
+        <v>1.456017988613192</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.729002332194836</v>
+        <v>0.7831678384863368</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.208044128231024</v>
+        <v>3.240543432005925</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.361605624448709</v>
+        <v>-3.078028786333481</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.424084759415145</v>
+        <v>1.537515494661236</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366443358293122</v>
+        <v>0.9908098421208129</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.331070035005963</v>
+        <v>3.363569338780864</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.310573531726181</v>
+        <v>-3.026996693610953</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.439445824742426</v>
+        <v>1.552876559988517</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876764285518401</v>
+        <v>1.041841934843341</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.35663751887775</v>
+        <v>3.38913682265265</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.245349350598975</v>
+        <v>-2.961772512483748</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.482722901286013</v>
+        <v>1.596153636532104</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052900609679046</v>
+        <v>1.107066115970546</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.412959431646778</v>
+        <v>3.445458735421679</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.207922330527841</v>
+        <v>-2.924345492412614</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.493654681613747</v>
+        <v>1.607085416859838</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058152147708227</v>
+        <v>1.112317653999728</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.412071326763567</v>
+        <v>3.444570630538468</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.22803398656255</v>
+        <v>-2.944457148447322</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.486866811531104</v>
+        <v>1.600297546777195</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069179492705646</v>
+        <v>1.123344998997147</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.419944526093259</v>
+        <v>3.45244382986816</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.174289172135345</v>
+        <v>-2.890712334020118</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.668922508323197</v>
+        <v>1.782353243569288</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.079242802146108</v>
+        <v>1.133408308437609</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.586540282778747</v>
+        <v>3.619039586553648</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.099506911110332</v>
+        <v>-2.815930072995105</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.818948321951019</v>
+        <v>1.93237905719711</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.154025063171121</v>
+        <v>1.208190569462622</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.751522548611572</v>
+        <v>3.784021852386473</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.073422826846524</v>
+        <v>-2.789845988731297</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.821089931670401</v>
+        <v>1.934520666916492</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.154025063171121</v>
+        <v>1.208190569462622</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.743230524625431</v>
+        <v>3.775729828400332</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.995291645997578</v>
+        <v>-2.71171480788235</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.85053559959376</v>
+        <v>1.96396633483985</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.228201874054806</v>
+        <v>1.282367380346307</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.785929806739421</v>
+        <v>3.818429110514322</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.986399184604295</v>
+        <v>-2.702822346489067</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.871646989877864</v>
+        <v>1.985077725123955</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.228201874054806</v>
+        <v>1.282367380346307</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.803484212466213</v>
+        <v>3.835983516241113</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.154875301574172</v>
+        <v>-2.871298463458945</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.796111590494497</v>
+        <v>1.909542325740588</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.200254038338225</v>
+        <v>1.254419544629726</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.778570558440848</v>
+        <v>3.811069862215749</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.457075772712589</v>
+        <v>-2.173498934597362</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.056501099226992</v>
+        <v>2.169931834473083</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.129905978967814</v>
+        <v>1.184071485259315</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.717631420006464</v>
+        <v>3.750130723781364</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.434354669029437</v>
+        <v>-2.150777830914209</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.056253563197158</v>
+        <v>2.169684298443249</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.129905978967814</v>
+        <v>1.184071485259315</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.708295442503368</v>
+        <v>3.740794746278269</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.563556482323479</v>
+        <v>-2.279979644208252</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.16347896373071</v>
+        <v>2.276909698976801</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.000704165673772</v>
+        <v>1.054869671965273</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.789680480378112</v>
+        <v>3.822179784153013</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.718337489101735</v>
+        <v>-2.434760650986507</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.138644383513054</v>
+        <v>2.252075118759145</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9673364916192959</v>
+        <v>1.021501997910797</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.806737698439073</v>
+        <v>3.839237002213973</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.711282798886561</v>
+        <v>-2.427705960771334</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.138141615588669</v>
+        <v>2.251572350834759</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9743911818344697</v>
+        <v>1.028556688125971</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.807645868557722</v>
+        <v>3.840145172332623</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.684331574560073</v>
+        <v>-2.400754736444846</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.158928258964005</v>
+        <v>2.272358994210096</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9892715278621889</v>
+        <v>1.04343703415369</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.826580229819095</v>
+        <v>3.859079533593996</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.820284582616389</v>
+        <v>-2.536707744501162</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.288650187886438</v>
+        <v>2.402080923132529</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9892715278621889</v>
+        <v>1.04343703415369</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.010683361964055</v>
+        <v>4.043182665738955</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714428</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.842692700421261</v>
+        <v>-2.559115862306034</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.271803635667483</v>
+        <v>2.385234370913574</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9892715278621889</v>
+        <v>1.04343703415369</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.002800056867049</v>
+        <v>4.035299360641948</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.990698467900661</v>
+        <v>-2.707121629785433</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.21465532822536</v>
+        <v>2.328086063471451</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9025445189986474</v>
+        <v>0.9567100252901484</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.952817851098561</v>
+        <v>3.985317154873461</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.000139393789191</v>
+        <v>-2.716562555673963</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.267132675591796</v>
+        <v>2.380563410837887</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.024971636542039</v>
+        <v>1.07913714283354</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.082527839346443</v>
+        <v>4.115027143121344</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.052413001124832</v>
+        <v>-2.768836163009605</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.24911432720284</v>
+        <v>2.362545062448931</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9726980292063977</v>
+        <v>1.026863535497899</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.054054769490358</v>
+        <v>4.086554073265259</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.128742978725738</v>
+        <v>-2.845166140610511</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.216694149056253</v>
+        <v>2.330124884302344</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9726980292063977</v>
+        <v>1.026863535497899</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.052166582384134</v>
+        <v>4.084665886159034</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.330996699050091</v>
+        <v>-3.047419860934864</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.130612890529374</v>
+        <v>2.244043625775465</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7704443088820443</v>
+        <v>0.824609815173545</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.925634579792384</v>
+        <v>3.958133883567284</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.492565124577347</v>
+        <v>-3.208988286462119</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.064419530528624</v>
+        <v>2.177850265774715</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6436613850841649</v>
+        <v>0.6978268913756657</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.847998835723809</v>
+        <v>3.880498139498709</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.7549119076471</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.6248664166749</v>
+        <v>-3.341289578559672</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.024572420555521</v>
+        <v>2.138003155801612</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6436613850841649</v>
+        <v>0.6978268913756657</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.861072242589727</v>
+        <v>3.893571546364628</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.749896851763535</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.62642805948976</v>
+        <v>-3.342851221374532</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.023947763429577</v>
+        <v>2.137378498675668</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6436613850841649</v>
+        <v>0.6978268913756657</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.861072242589727</v>
+        <v>3.893571546364628</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392112</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.654328846599233</v>
+        <v>-3.370752008484005</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.01131148971279</v>
+        <v>2.124742224958881</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6090644609412301</v>
+        <v>0.6632299672327309</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.838838129230969</v>
+        <v>3.871337433005869</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172529</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.776854949302127</v>
+        <v>-3.493278111186899</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.959065492608831</v>
+        <v>2.072496227854922</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4865383582383362</v>
+        <v>0.540703864529837</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.762086911586431</v>
+        <v>3.794586215361332</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.007369445487715</v>
+        <v>-3.723792607372488</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.9335656537251</v>
+        <v>2.04699638897119</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2560238620527475</v>
+        <v>0.3101893683442483</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.690484173465582</v>
+        <v>3.722983477240482</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.264090263482538</v>
+        <v>-3.980513425367312</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.971189045529017</v>
+        <v>2.084619780775108</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.2017747942004334</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.76574714798114</v>
+        <v>3.79824645175604</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.418076681258679</v>
+        <v>-4.134499843143452</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.978574747564201</v>
+        <v>2.092005482810292</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.2017747942004334</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.83472741712678</v>
+        <v>3.86722672090168</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.367554777431013</v>
+        <v>-4.083977939315786</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.984834711215388</v>
+        <v>2.098265446461479</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.2017747942004334</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.820778619246901</v>
+        <v>3.853277923021801</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994895</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.620029931438737</v>
+        <v>-4.33645309332351</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.895715138667712</v>
+        <v>2.009145873913803</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.2017747942004334</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.832649108302315</v>
+        <v>3.865148412077215</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.889502733360445</v>
+        <v>-4.605925895245218</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.789136552417973</v>
+        <v>1.902567287664064</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.2017747942004334</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.833859642821258</v>
+        <v>3.866358946596159</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.047046805089887</v>
+        <v>-4.76346996697466</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.730240665953517</v>
+        <v>1.843671401199608</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08070748276865819</v>
+        <v>0.1348729890601589</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.797840301964415</v>
+        <v>3.830339605739316</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.325011200673161</v>
+        <v>-5.041434362557934</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.614132760456398</v>
+        <v>1.727563495702488</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.008912251516826064</v>
+        <v>0.04525325477467468</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.739146314129314</v>
+        <v>3.771645617904214</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.66797646721547</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.441978893312052</v>
+        <v>-5.158402055196825</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.729549740099885</v>
+        <v>1.842980475345976</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.008912251516826064</v>
+        <v>0.04525325477467468</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.901350370828358</v>
+        <v>3.933849674603258</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.696553628456693</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.526696835533005</v>
+        <v>-5.243119997417778</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.690509201175318</v>
+        <v>1.803939936421409</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.09402828044487244</v>
+        <v>-0.03986277415337169</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.845127391435344</v>
+        <v>3.877626695210245</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.608631653801888</v>
+        <v>-5.325054815686661</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.667964691436256</v>
+        <v>1.781395426682347</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1039630260319526</v>
+        <v>-0.04979751974045188</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.849395961651587</v>
+        <v>3.881895265426488</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.783647027717833</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.554893480401626</v>
+        <v>-5.271316642286399</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.698385599252263</v>
+        <v>1.811816334498354</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.05022485263169052</v>
+        <v>0.003940653659810223</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.890564504147647</v>
+        <v>3.923063807922547</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.79831094461695</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.444887196924404</v>
+        <v>-5.161310358809177</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.734540999887328</v>
+        <v>1.847971735133418</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02702028071441531</v>
+        <v>0.02714522557708543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.896640134542188</v>
+        <v>3.929139438317088</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203666</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.301827621183479</v>
+        <v>-5.018250783068252</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.796014840905672</v>
+        <v>1.909445576151763</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01900685412443603</v>
+        <v>0.03515865216706471</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.905698201218149</v>
+        <v>3.93819750499305</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436931</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.000380895711642</v>
+        <v>-4.716804057596415</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.923854413976943</v>
+        <v>2.037285149223034</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2824398713474012</v>
+        <v>0.336605377638902</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.093827119383787</v>
+        <v>4.126326423158688</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064768</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.024971139946826</v>
+        <v>-4.741394301831598</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.914989494035579</v>
+        <v>2.02842022928167</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2824398713474012</v>
+        <v>0.336605377638902</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.094798297136498</v>
+        <v>4.127297600911398</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859302</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.973932763940305</v>
+        <v>-4.690355925825078</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.936247748817943</v>
+        <v>2.049678484064034</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2824398713474012</v>
+        <v>0.336605377638902</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.095641201516253</v>
+        <v>4.128140505291154</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354681</v>
+        <v>3.831748677354685</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.932793469073674</v>
+        <v>-4.649216630958447</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.971741565638741</v>
+        <v>2.085172300884832</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.323579166214032</v>
+        <v>0.3777446725055328</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.139362877310377</v>
+        <v>4.171862181085277</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085621</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.822187328994072</v>
+        <v>-4.538610490878845</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.832168017794516</v>
+        <v>1.945598753040607</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4341853062936341</v>
+        <v>0.4883508125851348</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.021910557482073</v>
+        <v>4.054409861256974</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.804703121462783</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.952768063524915</v>
+        <v>-4.669191225409688</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.783437768056143</v>
+        <v>1.896868503302234</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3036045717627915</v>
+        <v>0.3577700780542923</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.947064160837531</v>
+        <v>3.979563464612432</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218596</v>
+        <v>3.7750430212186</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.788271729333953</v>
+        <v>-4.504694891218726</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.83366312080861</v>
+        <v>1.947093856054701</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3036045717627915</v>
+        <v>0.3577700780542923</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.931490979913614</v>
+        <v>3.963990283688514</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.821044820462772</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.663791248610002</v>
+        <v>-4.380214410494775</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.88264302353462</v>
+        <v>1.996073758780711</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3036045717627915</v>
+        <v>0.3577700780542923</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.930678690350043</v>
+        <v>3.963177994124944</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.459093953841843</v>
+        <v>3.87680986327176</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.674176443499891</v>
+        <v>-4.390599605384664</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.888357724703737</v>
+        <v>2.001788459949828</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2932193768729022</v>
+        <v>0.347384883164403</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.934316352541183</v>
+        <v>3.966815656316083</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-639.1%</t>
+          <t>-668.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.1%</t>
+          <t>446.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-600.6%</t>
+          <t>-654.3%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-256.0%</t>
+          <t>-267.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.0%</t>
+          <t>-197.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-258.3%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-209.9%</t>
+          <t>-183.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-189.3%</t>
+          <t>-194.7%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,31 +1447,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-92.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2037"/>
+  <dimension ref="A1:G2038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.9622078420698927</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.736089201185021</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>-0.9508186054150913</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>2.738469691966182</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.073588152288091</v>
+        <v>-1.368572628961928</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.687288764722045</v>
+        <v>2.569294974052511</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.042227088974184</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.74241670333554</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.363719818893523</v>
+        <v>-1.65870429556736</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.571102314678795</v>
+        <v>2.45310852400926</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.066308883714364</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.75673199677857</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.5717238772466</v>
+        <v>-1.866708353920437</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.492792835891489</v>
+        <v>2.374799045221954</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.066308883714364</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.761624141332495</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.63390228840757</v>
+        <v>-1.928886765081407</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.463002927765089</v>
+        <v>2.345009137095555</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.004130472553394</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.719398550973901</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.999971015552223</v>
+        <v>-2.29495549222606</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.309659736213677</v>
+        <v>2.191665945544142</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6380617454087415</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.492841613993559</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.208461797003907</v>
+        <v>-2.503446273677744</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.246601713371772</v>
+        <v>2.128607922702237</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4295709639570571</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.388085434861317</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.455662981769129</v>
+        <v>-2.750647458442966</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.155819989874252</v>
+        <v>2.037826199204717</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4497243174558695</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.408276197369172</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.948048009793226</v>
+        <v>-3.243032486467063</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.959972370708345</v>
+        <v>1.84197858003881</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.04266071056822723</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.113951572598447</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.333228400723298</v>
+        <v>-3.628212877397135</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.804442753149179</v>
+        <v>1.686448962479644</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.04266071056822723</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.11249411141131</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.58309908073788</v>
+        <v>-3.878083557411717</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.706263604597963</v>
+        <v>1.588269813928428</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.006397990737763981</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.136020866764204</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.789610857624901</v>
+        <v>-4.084595334298738</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.619764952499412</v>
+        <v>1.501771161829877</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2129097676247855</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.008219859288249</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.108954932705403</v>
+        <v>-4.40393940937924</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.493800249167471</v>
+        <v>1.375806458497936</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2129097676247855</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.009992785988509</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.540760725855191</v>
+        <v>-4.835745202529028</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.30741081937496</v>
+        <v>1.189417028705426</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.3493272640660525</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.914475175591153</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.775454719987743</v>
+        <v>-5.07043919666158</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.20181799672403</v>
+        <v>1.083824206054495</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3429909968367973</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.906561710930796</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.111117367218196</v>
+        <v>-5.406101843892032</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.066133529487814</v>
+        <v>0.9481397388182793</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4109219823257021</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.864383711293419</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.187561697421067</v>
+        <v>-5.482546174094904</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.042043357640907</v>
+        <v>0.9240495669713722</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3304764732320402</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.919138576983857</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.552689080059814</v>
+        <v>-5.847673556733651</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8952469195912398</v>
+        <v>0.7772531289217053</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6267872575310527</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.740606621410281</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.961277857240493</v>
+        <v>-6.256262333914329</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7305729527337275</v>
+        <v>0.6125791620641929</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.494214899116633</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.075038269263358</v>
+        <v>-6.370022745937193</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.680254220396042</v>
+        <v>0.5622604297265075</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.489400331588094</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.491430143550355</v>
+        <v>-6.786414620224191</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5116915212901203</v>
+        <v>0.3936977306205858</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.487394382196971</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.735701544277425</v>
+        <v>-7.03068602095126</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4242416516679715</v>
+        <v>0.3062478609984369</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.49765307286565</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.078960063920444</v>
+        <v>-7.373944540594279</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2830378089564589</v>
+        <v>0.1650440182869248</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.493752638011346</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.127162881162787</v>
+        <v>-7.422147357836623</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2621616021145226</v>
+        <v>0.144167811444988</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.492157558066347</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.423824222972985</v>
+        <v>-7.718808699646821</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1472760413196519</v>
+        <v>0.02928225065011736</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.10411917044561</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.454690652555227</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.610543931282288</v>
+        <v>-7.905528407956123</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.06856185346152754</v>
+        <v>-0.04943193720800698</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.10411917044561</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.450664348020824</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.993545320024919</v>
+        <v>-8.288529796698754</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.08474080335710887</v>
+        <v>-0.202734594026643</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.10411917044561</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.45056224669924</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.998031765226307</v>
+        <v>-8.293016241900142</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.08396386546623447</v>
+        <v>-0.2019576561357685</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.108605615646998</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.450441895549837</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.35756208773031</v>
+        <v>-8.652546564404144</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2224256911697853</v>
+        <v>-0.3404194818393189</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.108605615646998</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.455792198847887</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.407911151184532</v>
+        <v>-8.702895627858366</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2346492965942963</v>
+        <v>-0.35264308726383</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.15895467910122</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.433498780732532</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.505530428605928</v>
+        <v>-8.800514905279762</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2706552569410863</v>
+        <v>-0.3886490476106199</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.256573956522617</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.377968964901462</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.559601928114287</v>
+        <v>-8.854586404788121</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2893903004228573</v>
+        <v>-0.4073840910923909</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.310645456030977</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.348419621518019</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.76386010344415</v>
+        <v>-9.058844580117984</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3655803734361607</v>
+        <v>-0.4835741641056943</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.438284400644966</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.277349451868268</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.797512941952624</v>
+        <v>-9.092497418626458</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.374558954355114</v>
+        <v>-0.4925527450246476</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.538697768562003</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.221583985602482</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.724043110285175</v>
+        <v>-9.019027586959009</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3297993201947129</v>
+        <v>-0.4477931108642466</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.465227936894554</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.281037586096372</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.899167527671718</v>
+        <v>-9.194152004345552</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3852938664018137</v>
+        <v>-0.5032876570713474</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.640352354281098</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.190518156411962</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.133619621686208</v>
+        <v>-9.428604098360042</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4862938689092053</v>
+        <v>-0.604287659578739</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.640352354281098</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.183298991510366</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.237994352712654</v>
+        <v>-9.532978829386488</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5347159520937601</v>
+        <v>-0.6527097427632937</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.744727085307544</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.114001962120523</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.290780508312981</v>
+        <v>-9.585764984986815</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5547146244953347</v>
+        <v>-0.6727084151648683</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.840402571889941</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.057712460009641</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.41681730168127</v>
+        <v>-9.711801778355104</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6024356132135358</v>
+        <v>-0.7204294038830694</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.815150949080199</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.075557162324601</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.359745529785339</v>
+        <v>-9.654730006459173</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5756165687687624</v>
+        <v>-0.6936103594382961</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.815150949080199</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.079547498011002</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.50141737150946</v>
+        <v>-9.796401848183294</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6337605323571522</v>
+        <v>-0.7517543230266859</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.815150949080199</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.07807227111226</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.451826527084625</v>
+        <v>-9.746811003758459</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5988707844223464</v>
+        <v>-0.7168645750918801</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.765560104655365</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.122880187932032</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.302908192612769</v>
+        <v>-9.597892669286603</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5523545842802866</v>
+        <v>-0.6703483749498202</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.734310513920192</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.128578808726453</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.077063039893357</v>
+        <v>-9.372047516567193</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4524374501563133</v>
+        <v>-0.5704312408258478</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.692383838333028</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.16331388711496</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.952484383555765</v>
+        <v>-9.247468860229601</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4014668430652177</v>
+        <v>-0.5194606337347518</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.692383838333028</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.164453031671019</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.005379671600052</v>
+        <v>-9.300364148273887</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4199911841208248</v>
+        <v>-0.5379849747903589</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.687428492244582</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.170060013486195</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.93324649631217</v>
+        <v>-9.228230972986006</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3854042097670356</v>
+        <v>-0.5033980004365701</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.687428492244582</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.175793717724831</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.861880103702523</v>
+        <v>-9.156864580376359</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3665949151170418</v>
+        <v>-0.4845887057865763</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.616062099634934</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.208876290896755</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.768421069717299</v>
+        <v>-9.063405546391134</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3390947828358599</v>
+        <v>-0.457088573505394</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.616062099634934</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.198992809583847</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.501179268848901</v>
+        <v>-8.796163745522737</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2340326229878742</v>
+        <v>-0.3520264136574087</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.616062099634934</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.197158249084473</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.40327223017241</v>
+        <v>-8.698256706846246</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.195170122490739</v>
+        <v>-0.3131639131602735</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.548076349774378</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.237649384027346</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.379318689196452</v>
+        <v>-8.674303165870288</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.184920199954862</v>
+        <v>-0.3029139906243965</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.52412280879842</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.252690014758414</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.115258750873656</v>
+        <v>-8.410243227547491</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09255654078749576</v>
+        <v>-0.2105503314570298</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.260062870475624</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.39786566159034</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.408179127368817</v>
+        <v>-7.703163604042653</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1874882749541387</v>
+        <v>0.06949448428460459</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.260062870475624</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.395078627930039</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.367994829002627</v>
+        <v>-7.662979305676463</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2039056181884562</v>
+        <v>0.08591182751892212</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.219878572109433</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.419532830837595</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.204594958063264</v>
+        <v>-7.4995794347371</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2686323877849581</v>
+        <v>0.150638597115424</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.056478701170071</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.516939574621969</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.971113735833666</v>
+        <v>-7.266098212507502</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3699493055146501</v>
+        <v>0.2519555148451156</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8229974789404721</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.664952736797581</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.821447344826151</v>
+        <v>-7.116431821499987</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4269236516046968</v>
+        <v>0.3089298609351627</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7300939876979362</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.717802621230143</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.689171871195264</v>
+        <v>-6.9841563478691</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4752013278040788</v>
+        <v>0.3572075371345442</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5978185140670496</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.792535392155702</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.533433538635522</v>
+        <v>-6.828418015309358</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5403117215156121</v>
+        <v>0.4223179308460776</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.442080181507308</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.888793452379184</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.284433739951941</v>
+        <v>-6.579418216625777</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6528179822127034</v>
+        <v>0.5348241915431688</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1930803828237273</v>
+        <v>-0.2472458891152278</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.051099672812991</v>
+        <v>3.018600369038091</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.390023729725046</v>
+        <v>-6.685008206398882</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4826060567042427</v>
+        <v>0.3646122660347082</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2986703725968317</v>
+        <v>-0.3528358788883322</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.85976974934991</v>
+        <v>2.827270445575009</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.408758631843643</v>
+        <v>-6.703743108517479</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5236564377338904</v>
+        <v>0.4056626470643558</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.304266382256963</v>
+        <v>-0.3584318885484635</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.904956485430917</v>
+        <v>2.872457181656017</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.260818590436044</v>
+        <v>-6.555803067109879</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4629535316087625</v>
+        <v>0.344959740939228</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2839454663484054</v>
+        <v>-0.3381109726399059</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.797270112287884</v>
+        <v>2.764770808512984</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.207849068182055</v>
+        <v>-6.502833544855891</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4754273542568797</v>
+        <v>0.3574335635873451</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.820337839386799</v>
+        <v>2.787838535611899</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.164300661411365</v>
+        <v>-6.459285138085201</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4858861048700627</v>
+        <v>0.3678923142005281</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.813377227291706</v>
+        <v>2.780877923516806</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.130937454932596</v>
+        <v>-6.425921931606432</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5136937418427134</v>
+        <v>0.3956999511731789</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.827839581672849</v>
+        <v>2.795340277897949</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.022678317810074</v>
+        <v>-6.31766279448391</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5515295171509171</v>
+        <v>0.4335357264813826</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.822371702132044</v>
+        <v>2.789872398357144</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.899387182992943</v>
+        <v>-6.194371659666779</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5983440650883463</v>
+        <v>0.4803502744188117</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.107684809277286</v>
+        <v>-0.1618503155687865</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.893844477032899</v>
+        <v>2.861345173257999</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.8782379840895</v>
+        <v>-6.173222460763336</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6145047228870486</v>
+        <v>0.4965109322175145</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.08653561037384266</v>
+        <v>-0.1407011166653432</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.914234974612291</v>
+        <v>2.88173567083739</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.634472542106056</v>
+        <v>-5.929457018779892</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7077916080274771</v>
+        <v>0.589797817357943</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.08653561037384266</v>
+        <v>-0.1407011166653432</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.910015682959342</v>
+        <v>2.877516379184441</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532709721828761</v>
+        <v>-5.827694198502597</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.750621050058411</v>
+        <v>0.6326272593888769</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.07331654198141396</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.920071437914815</v>
+        <v>2.887572134139914</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282859327879686</v>
+        <v>-5.577843804553522</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.843303282621743</v>
+        <v>0.725309491952209</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.07331654198141396</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.912813512898517</v>
+        <v>2.880314209123616</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.106967235412254</v>
+        <v>-5.40195171208609</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9172592431293647</v>
+        <v>0.7992654524598302</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.07331654198141396</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.916412636419166</v>
+        <v>2.883913332644265</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935520772389791</v>
+        <v>-5.230505249063627</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9991653343929037</v>
+        <v>0.8811715437233696</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.09812992104104917</v>
+        <v>0.04396441474954865</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.032608020287197</v>
+        <v>3.000108716512297</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.861231206651452</v>
+        <v>-5.156215683325287</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.027901638304536</v>
+        <v>0.9099078476350022</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1724194867793885</v>
+        <v>0.1182539804878879</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.076202237346497</v>
+        <v>3.043702933571597</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.797595464417517</v>
+        <v>-5.092579941091353</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.058050736252427</v>
+        <v>0.9400569455828931</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.236055229013323</v>
+        <v>0.1818897227218225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.119078483741176</v>
+        <v>3.086579179966275</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.686168705091597</v>
+        <v>-4.981153181765433</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.083815698766591</v>
+        <v>0.9658219080970567</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.236055229013323</v>
+        <v>0.1818897227218225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.100272742524971</v>
+        <v>3.067773438750071</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.445738208286737</v>
+        <v>-4.740722684960573</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.181730974113413</v>
+        <v>1.063737183443878</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4764857258181833</v>
+        <v>0.4223202195266827</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.246274117232765</v>
+        <v>3.213774813457865</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.373495640115542</v>
+        <v>-4.668480116789378</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.214557315216711</v>
+        <v>1.096563524547176</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4764857258181833</v>
+        <v>0.4223202195266827</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.250203431067585</v>
+        <v>3.217704127292685</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.355781953237677</v>
+        <v>-4.650766429911513</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.222321373885197</v>
+        <v>1.104327583215662</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4796670547151001</v>
+        <v>0.4255015484235996</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.252790812323075</v>
+        <v>3.220291508548175</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.24697706775795</v>
+        <v>-4.541961544431786</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.262841399297081</v>
+        <v>1.144847608627547</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4796670547151001</v>
+        <v>0.4255015484235996</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.249788883543069</v>
+        <v>3.217289579768168</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.026956269720939</v>
+        <v>-4.321940746394775</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.352428755522499</v>
+        <v>1.234434964852965</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6208868997830803</v>
+        <v>0.5667213934915798</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.336099827594471</v>
+        <v>3.303600523819571</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.894088580657661</v>
+        <v>-4.189073057331497</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.421470013949634</v>
+        <v>1.3034762232801</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6208868997830803</v>
+        <v>0.5667213934915798</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.351994010396294</v>
+        <v>3.319494706621394</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.773915497293162</v>
+        <v>-4.068899973966999</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.470685091735735</v>
+        <v>1.352691301066201</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7410599831475793</v>
+        <v>0.6868944768560787</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.425243704855296</v>
+        <v>3.392744401080395</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.629243352193424</v>
+        <v>-3.924227828867261</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.538642052337071</v>
+        <v>1.420648261667536</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8857321282473167</v>
+        <v>0.8315666219558162</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.522135094476578</v>
+        <v>3.489635790701677</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.689118179551117</v>
+        <v>-3.984102656224954</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.500729612795419</v>
+        <v>1.382735822125885</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8258573008896246</v>
+        <v>0.7716917945981241</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.472247689463388</v>
+        <v>3.439748385688488</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.569297948640279</v>
+        <v>-3.864282425314116</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.563946874393963</v>
+        <v>1.445953083724428</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8258573008896246</v>
+        <v>0.7716917945981241</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.487536858697597</v>
+        <v>3.455037554922697</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.571767655102085</v>
+        <v>-3.866752131775922</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.470603191131682</v>
+        <v>1.352609400462147</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8233875944278184</v>
+        <v>0.7692220881363179</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.393699234142955</v>
+        <v>3.361199930368054</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.640137841426095</v>
+        <v>-3.935122318099932</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.362516978087379</v>
+        <v>1.244523187417845</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.318526515049985</v>
+        <v>3.286027211275085</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.653925894273142</v>
+        <v>-3.948910370946979</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.347438465580452</v>
+        <v>1.229444674910917</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.308963223681876</v>
+        <v>3.276463919906976</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.709445970165731</v>
+        <v>-4.004430446839568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.462261271915619</v>
+        <v>1.344267481246084</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.445994060374079</v>
+        <v>3.413494756599178</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.533971710373262</v>
+        <v>-3.828956187047099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.537018207824394</v>
+        <v>1.419024417154859</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.450561292365867</v>
+        <v>3.418061988590966</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.644907963014511</v>
+        <v>-3.939892439688347</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.468385735529102</v>
+        <v>1.350391944859567</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.426303321127074</v>
+        <v>3.393804017352173</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.611244417542229</v>
+        <v>-3.906228894216066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.410389467119464</v>
+        <v>1.29239567644993</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8663268389363152</v>
+        <v>0.8121613326448147</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.375039761811892</v>
+        <v>3.342540458036992</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.551391798338506</v>
+        <v>-3.846376275012342</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.444502901233086</v>
+        <v>1.326509110563551</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8663268389363152</v>
+        <v>0.8121613326448147</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.385212148244025</v>
+        <v>3.352712844469124</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.465148335312128</v>
+        <v>-3.760132811985965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.473946557017497</v>
+        <v>1.355952766347962</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8663268389363152</v>
+        <v>0.8121613326448147</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.380158418817885</v>
+        <v>3.347659115042985</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.510455154711108</v>
+        <v>-3.805439631384945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.447599604702431</v>
+        <v>1.329605814032896</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8255166759270844</v>
+        <v>0.7713511696355839</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.347448096456872</v>
+        <v>3.314948792681972</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.53948825941341</v>
+        <v>-3.834472736087247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.436538235854612</v>
+        <v>1.318544445185077</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8255166759270844</v>
+        <v>0.7713511696355839</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.347999969489974</v>
+        <v>3.315500665715073</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.446677777962551</v>
+        <v>-3.741662254636387</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.402935120326321</v>
+        <v>1.284941329656786</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9183271573779438</v>
+        <v>0.8641616510864433</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.332958950251855</v>
+        <v>3.300459646476955</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.491067247291978</v>
+        <v>-3.786051723965815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.387052808519151</v>
+        <v>1.269059017849616</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8739376880485161</v>
+        <v>0.8197721817570156</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.308198744578799</v>
+        <v>3.275699440803899</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.607608852397321</v>
+        <v>-3.902593329071158</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.335511874988737</v>
+        <v>1.217518084319202</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7573960829431734</v>
+        <v>0.7032305766516729</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.233349490027317</v>
+        <v>3.200850186252416</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.495231851214649</v>
+        <v>-4.031924558465223</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.385953971292473</v>
+        <v>1.171276888392243</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7573960829431734</v>
+        <v>0.7032305766516729</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.238840785857984</v>
+        <v>3.206341482083084</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.523012249116002</v>
+        <v>-4.059704956366575</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.386339013900471</v>
+        <v>1.171661931000241</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7296156850418203</v>
+        <v>0.6754501787503198</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.233669748885711</v>
+        <v>3.201170445110811</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.64139292184614</v>
+        <v>-4.178085629096714</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.177342464809069</v>
+        <v>0.9626653819088391</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6623978328908441</v>
+        <v>0.6082323265993436</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.031694757595778</v>
+        <v>2.999195453820878</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.750007000289471</v>
+        <v>-4.286699707540045</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.254046494150942</v>
+        <v>1.039369411250712</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6623978328908441</v>
+        <v>0.6082323265993436</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.151844418314984</v>
+        <v>3.119345114540084</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.714597962041328</v>
+        <v>-4.251290669291902</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.282723135552522</v>
+        <v>1.068046052652293</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6623978328908441</v>
+        <v>0.6082323265993436</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.166357444417307</v>
+        <v>3.133858140642407</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.676214299483177</v>
+        <v>-4.212907006733751</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.295496041918151</v>
+        <v>1.080818959017922</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7007814954489953</v>
+        <v>0.6466159891574947</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.186807083294567</v>
+        <v>3.154307779519666</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.499097969448011</v>
+        <v>-4.035790676698585</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.363071602777519</v>
+        <v>1.14839451987729</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7007814954489953</v>
+        <v>0.6466159891574947</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.183536112139869</v>
+        <v>3.151036808364968</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.544190214281556</v>
+        <v>-4.080882921532131</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.345718096606014</v>
+        <v>1.131041013705785</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6388854522796055</v>
+        <v>0.5847199459881049</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.147081878000148</v>
+        <v>3.114582574225247</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.364814793042789</v>
+        <v>-3.901507500293363</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.411255240407936</v>
+        <v>1.196578157507706</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7956622104503241</v>
+        <v>0.7414967041588236</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.234934908208993</v>
+        <v>3.202435604434093</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.409829006563395</v>
+        <v>-3.946521713813969</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.374057010331283</v>
+        <v>1.159379927431053</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7653133151357195</v>
+        <v>0.711147808844219</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.19753302635182</v>
+        <v>3.16503372257692</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.67683351683583</v>
+        <v>-4.213526224086404</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.272946768561255</v>
+        <v>1.058269685661025</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.570950277092771</v>
+        <v>0.5167847708012705</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.086606765864997</v>
+        <v>3.054107462090097</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.778031298273003</v>
+        <v>-4.314724005523577</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.231671577882887</v>
+        <v>1.016994494982657</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5025414635474519</v>
+        <v>0.4483759572559513</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.044765399634307</v>
+        <v>3.012266095859407</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.77152033165869</v>
+        <v>-4.308213038909265</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.231875926082929</v>
+        <v>1.017198843182699</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5025414635474519</v>
+        <v>0.4483759572559513</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.042365361188624</v>
+        <v>3.009866057413723</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.752482203951393</v>
+        <v>-4.289174911201967</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.236015896374093</v>
+        <v>1.021338813473863</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4443578522162573</v>
+        <v>0.3901923459247568</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.003979913598152</v>
+        <v>2.971480609823252</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.783608835102011</v>
+        <v>-4.320301542352586</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.342859645548036</v>
+        <v>1.128182562647806</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4443578522162573</v>
+        <v>0.3901923459247568</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.123274315232342</v>
+        <v>3.090775011457442</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.797475596435929</v>
+        <v>-4.334168303686504</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.338146270000602</v>
+        <v>1.123469187100372</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4064999354824344</v>
+        <v>0.3523344291909338</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.101392894178182</v>
+        <v>3.068893590403281</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.752671424895999</v>
+        <v>-4.289364132146574</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.3620764690135</v>
+        <v>1.14739938611327</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4064999354824344</v>
+        <v>0.3523344291909338</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.107401424575108</v>
+        <v>3.074902120800207</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.604928454660997</v>
+        <v>-4.141621161911571</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.319123878384701</v>
+        <v>1.104446795484471</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5743072927173176</v>
+        <v>0.520141786425817</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.106036060193238</v>
+        <v>3.073536756418337</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.706943137192217</v>
+        <v>-4.243635844442792</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.281111626903693</v>
+        <v>1.066434544003463</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5743072927173176</v>
+        <v>0.520141786425817</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.108829681724719</v>
+        <v>3.076330377949818</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.700790431139433</v>
+        <v>-4.237483138390008</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.284235057716465</v>
+        <v>1.069557974816235</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5804599987701019</v>
+        <v>0.5262944924786013</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.113183653748047</v>
+        <v>3.080684349973147</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.717599729289935</v>
+        <v>-4.25429243654051</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.276591815196375</v>
+        <v>1.061914732296145</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5636507006196003</v>
+        <v>0.5094851943280996</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.102178551597857</v>
+        <v>3.069679247822956</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.655301730513813</v>
+        <v>-4.191994437764388</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.367846568503645</v>
+        <v>1.153169485603415</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5636507006196003</v>
+        <v>0.5094851943280996</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.168514105394677</v>
+        <v>3.136014801619777</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.453511532848655</v>
+        <v>-3.99020424009923</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.250854649283835</v>
+        <v>1.036177566383605</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7616688927887547</v>
+        <v>0.707503386497254</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.089617022410297</v>
+        <v>3.057117718635397</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.504398245534849</v>
+        <v>-4.041090952785424</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.300790196531532</v>
+        <v>1.086113113631302</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7107821801025602</v>
+        <v>0.6566166738110595</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.129375227120756</v>
+        <v>3.096875923345855</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.602138790159824</v>
+        <v>-4.138831497410399</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.276321714797586</v>
+        <v>1.061644631897356</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.69489290196958</v>
+        <v>0.6407273956780792</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.134469396357011</v>
+        <v>3.101970092582111</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.662348088165108</v>
+        <v>-4.199040795415684</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.250773976420144</v>
+        <v>1.036096893519914</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6346836039642955</v>
+        <v>0.5805180976727947</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.096879798378512</v>
+        <v>3.064380494603612</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.585926041733182</v>
+        <v>-4.122618748983757</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.279834413032843</v>
+        <v>1.065157330132613</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6346836039642955</v>
+        <v>0.5805180976727947</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.095371416418441</v>
+        <v>3.06287211264354</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.541552910094613</v>
+        <v>-4.078245617345188</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.297446533123707</v>
+        <v>1.082769450223477</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6790567356028641</v>
+        <v>0.6248912293113633</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.121858162837018</v>
+        <v>3.089358859062118</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.564033260953498</v>
+        <v>-4.100725968204073</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.282848186918744</v>
+        <v>1.068171104018513</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6790567356028641</v>
+        <v>0.6248912293113633</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.116251956975609</v>
+        <v>3.083752653200708</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.516377530392442</v>
+        <v>-4.053070237643017</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.30829223617097</v>
+        <v>1.09361515327074</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7267124661639197</v>
+        <v>0.672546959872419</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.151227152340047</v>
+        <v>3.118727848565146</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.415859371893688</v>
+        <v>-3.952552079144263</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.353391872945197</v>
+        <v>1.138714790044967</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8272306246626743</v>
+        <v>0.7730651183711735</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.216430420814024</v>
+        <v>3.183931117039124</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.476525962296077</v>
+        <v>-4.013218669546651</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.315879909260114</v>
+        <v>1.101202826359884</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7455323079441406</v>
+        <v>0.6913668016526399</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.154166103258776</v>
+        <v>3.121666799483876</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.431687560687679</v>
+        <v>-3.968380267938253</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.337912972514101</v>
+        <v>1.123235889613872</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7500757408890101</v>
+        <v>0.6959102345975093</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.160989865636326</v>
+        <v>3.128490561861426</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.451186016929687</v>
+        <v>-3.987878724180261</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.334274529648376</v>
+        <v>1.119597446748146</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7019910996091058</v>
+        <v>0.647825593317605</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.136300020499462</v>
+        <v>3.103800716724561</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.406983179843786</v>
+        <v>-3.943675887094361</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.357835267010573</v>
+        <v>1.143158184110344</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7461939366950062</v>
+        <v>0.6920284304035055</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.168701325278839</v>
+        <v>3.136202021503939</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.44396220750723</v>
+        <v>-3.980654914757804</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.341453656414444</v>
+        <v>1.126776573514214</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7831678384863368</v>
+        <v>0.729002332194836</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.189295666822885</v>
+        <v>3.156796363047984</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.285670789967957</v>
+        <v>-3.822363497218532</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.456017988613192</v>
+        <v>1.241340905712963</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7831678384863368</v>
+        <v>0.729002332194836</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.240543432005925</v>
+        <v>3.208044128231024</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.078028786333481</v>
+        <v>-3.614721493584056</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.537515494661236</v>
+        <v>1.322838411761006</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9908098421208129</v>
+        <v>0.9366443358293122</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.363569338780864</v>
+        <v>3.331070035005963</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.026996693610953</v>
+        <v>-3.563689400861528</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.552876559988517</v>
+        <v>1.338199477088287</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.041841934843341</v>
+        <v>0.9876764285518401</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.38913682265265</v>
+        <v>3.35663751887775</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.961772512483748</v>
+        <v>-3.498465219734322</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.596153636532104</v>
+        <v>1.381476553631874</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.107066115970546</v>
+        <v>1.052900609679046</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.445458735421679</v>
+        <v>3.412959431646778</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.924345492412614</v>
+        <v>-3.461038199663188</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.607085416859838</v>
+        <v>1.392408333959609</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.112317653999728</v>
+        <v>1.058152147708227</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.444570630538468</v>
+        <v>3.412071326763567</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.944457148447322</v>
+        <v>-3.481149855697896</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.600297546777195</v>
+        <v>1.385620463876965</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.123344998997147</v>
+        <v>1.069179492705646</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.45244382986816</v>
+        <v>3.419944526093259</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.890712334020118</v>
+        <v>-3.427405041270692</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.782353243569288</v>
+        <v>1.567676160669058</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.133408308437609</v>
+        <v>1.079242802146108</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.619039586553648</v>
+        <v>3.586540282778747</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.815930072995105</v>
+        <v>-3.352622780245679</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.93237905719711</v>
+        <v>1.71770197429688</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.208190569462622</v>
+        <v>1.154025063171121</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.784021852386473</v>
+        <v>3.751522548611572</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.789845988731297</v>
+        <v>-3.326538695981871</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.934520666916492</v>
+        <v>1.719843584016262</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.208190569462622</v>
+        <v>1.154025063171121</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.775729828400332</v>
+        <v>3.743230524625431</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.71171480788235</v>
+        <v>-3.248407515132924</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.96396633483985</v>
+        <v>1.749289251939621</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.282367380346307</v>
+        <v>1.228201874054806</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.818429110514322</v>
+        <v>3.785929806739421</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.702822346489067</v>
+        <v>-3.239515053739641</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.985077725123955</v>
+        <v>1.770400642223725</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.282367380346307</v>
+        <v>1.228201874054806</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.835983516241113</v>
+        <v>3.803484212466213</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.871298463458945</v>
+        <v>-3.407991170709519</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.909542325740588</v>
+        <v>1.694865242840358</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.254419544629726</v>
+        <v>1.200254038338225</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.811069862215749</v>
+        <v>3.778570558440848</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.173498934597362</v>
+        <v>-2.710191641847936</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.169931834473083</v>
+        <v>1.955254751572853</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.184071485259315</v>
+        <v>1.129905978967814</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.750130723781364</v>
+        <v>3.717631420006464</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.150777830914209</v>
+        <v>-2.687470538164783</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.169684298443249</v>
+        <v>1.955007215543019</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.184071485259315</v>
+        <v>1.129905978967814</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.740794746278269</v>
+        <v>3.708295442503368</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.279979644208252</v>
+        <v>-2.816672351458826</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.276909698976801</v>
+        <v>2.062232616076571</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.054869671965273</v>
+        <v>1.000704165673772</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.822179784153013</v>
+        <v>3.789680480378112</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.434760650986507</v>
+        <v>-2.971453358237081</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.252075118759145</v>
+        <v>2.037398035858915</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.021501997910797</v>
+        <v>0.9673364916192959</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.839237002213973</v>
+        <v>3.806737698439073</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.427705960771334</v>
+        <v>-2.964398668021908</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.251572350834759</v>
+        <v>2.03689526793453</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.028556688125971</v>
+        <v>0.9743911818344697</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.840145172332623</v>
+        <v>3.807645868557722</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.400754736444846</v>
+        <v>-2.93744744369542</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.272358994210096</v>
+        <v>2.057681911309866</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.04343703415369</v>
+        <v>0.9892715278621889</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.859079533593996</v>
+        <v>3.826580229819095</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.536707744501162</v>
+        <v>-3.073400451751736</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.402080923132529</v>
+        <v>2.1874038402323</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.04343703415369</v>
+        <v>0.9892715278621889</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.043182665738955</v>
+        <v>4.010683361964055</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714428</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.559115862306034</v>
+        <v>-3.095808569556608</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.385234370913574</v>
+        <v>2.170557288013344</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.04343703415369</v>
+        <v>0.9892715278621889</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.035299360641948</v>
+        <v>4.002800056867049</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.707121629785433</v>
+        <v>-3.243814337036008</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.328086063471451</v>
+        <v>2.113408980571222</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9567100252901484</v>
+        <v>0.9025445189986474</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.985317154873461</v>
+        <v>3.952817851098561</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.716562555673963</v>
+        <v>-3.253255262924537</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.380563410837887</v>
+        <v>2.165886327937657</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.07913714283354</v>
+        <v>1.024971636542039</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.115027143121344</v>
+        <v>4.082527839346443</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.768836163009605</v>
+        <v>-3.305528870260179</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.362545062448931</v>
+        <v>2.147867979548701</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.026863535497899</v>
+        <v>0.9726980292063977</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.086554073265259</v>
+        <v>4.054054769490358</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.845166140610511</v>
+        <v>-3.381858847861085</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.330124884302344</v>
+        <v>2.115447801402114</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.026863535497899</v>
+        <v>0.9726980292063977</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.084665886159034</v>
+        <v>4.052166582384134</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.047419860934864</v>
+        <v>-3.584112568185438</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.244043625775465</v>
+        <v>2.029366542875235</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.824609815173545</v>
+        <v>0.7704443088820443</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.958133883567284</v>
+        <v>3.925634579792384</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.208988286462119</v>
+        <v>-3.745680993712693</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.177850265774715</v>
+        <v>1.963173182874485</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6978268913756657</v>
+        <v>0.6436613850841649</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.880498139498709</v>
+        <v>3.847998835723809</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.7549119076471</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.341289578559672</v>
+        <v>-3.877982285810246</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.138003155801612</v>
+        <v>1.923326072901383</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6978268913756657</v>
+        <v>0.6436613850841649</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.893571546364628</v>
+        <v>3.861072242589727</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763535</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.342851221374532</v>
+        <v>-3.879543928625107</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.137378498675668</v>
+        <v>1.922701415775439</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6978268913756657</v>
+        <v>0.6436613850841649</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.893571546364628</v>
+        <v>3.861072242589727</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392119</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.370752008484005</v>
+        <v>-3.90744471573458</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.124742224958881</v>
+        <v>1.910065142058651</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6632299672327309</v>
+        <v>0.6090644609412301</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.871337433005869</v>
+        <v>3.838838129230969</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172529</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.493278111186899</v>
+        <v>-4.029970818437473</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.072496227854922</v>
+        <v>1.857819144954693</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.540703864529837</v>
+        <v>0.4865383582383362</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.794586215361332</v>
+        <v>3.762086911586431</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.723792607372488</v>
+        <v>-4.260485314623062</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.04699638897119</v>
+        <v>1.832319306070961</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3101893683442483</v>
+        <v>0.2560238620527475</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.722983477240482</v>
+        <v>3.690484173465582</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.980513425367312</v>
+        <v>-4.517206132617886</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.084619780775108</v>
+        <v>1.869942697874878</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2017747942004334</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.79824645175604</v>
+        <v>3.76574714798114</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.134499843143452</v>
+        <v>-4.671192550394027</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.092005482810292</v>
+        <v>1.877328399910062</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2017747942004334</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.86722672090168</v>
+        <v>3.83472741712678</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.083977939315786</v>
+        <v>-4.620670646566361</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.098265446461479</v>
+        <v>1.883588363561249</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2017747942004334</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.853277923021801</v>
+        <v>3.820778619246901</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994895</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.33645309332351</v>
+        <v>-4.873145800574085</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.009145873913803</v>
+        <v>1.794468791013573</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2017747942004334</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.865148412077215</v>
+        <v>3.832649108302315</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.605925895245218</v>
+        <v>-5.142618602495793</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.902567287664064</v>
+        <v>1.687890204763834</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2017747942004334</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.866358946596159</v>
+        <v>3.833859642821258</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.76346996697466</v>
+        <v>-5.300162674225235</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.843671401199608</v>
+        <v>1.628994318299378</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1348729890601589</v>
+        <v>0.08070748276865819</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.830339605739316</v>
+        <v>3.797840301964415</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.041434362557934</v>
+        <v>-5.578127069808509</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.727563495702488</v>
+        <v>1.512886412802259</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.04525325477467468</v>
+        <v>-0.008912251516826064</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.771645617904214</v>
+        <v>3.739146314129314</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66797646721547</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.158402055196825</v>
+        <v>-5.6950947624474</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.842980475345976</v>
+        <v>1.628303392445746</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.04525325477467468</v>
+        <v>-0.008912251516826064</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.933849674603258</v>
+        <v>3.901350370828358</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456693</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.243119997417778</v>
+        <v>-5.779812704668353</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.803939936421409</v>
+        <v>1.589262853521179</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.03986277415337169</v>
+        <v>-0.09402828044487244</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.877626695210245</v>
+        <v>3.845127391435344</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.325054815686661</v>
+        <v>-5.861747522937236</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.781395426682347</v>
+        <v>1.566718343782117</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.04979751974045188</v>
+        <v>-0.1039630260319526</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.881895265426488</v>
+        <v>3.849395961651587</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717833</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.271316642286399</v>
+        <v>-5.808009349536974</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.811816334498354</v>
+        <v>1.597139251598124</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.003940653659810223</v>
+        <v>-0.05022485263169052</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.923063807922547</v>
+        <v>3.890564504147647</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79831094461695</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.161310358809177</v>
+        <v>-5.698003066059752</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.847971735133418</v>
+        <v>1.633294652233188</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02714522557708543</v>
+        <v>-0.02702028071441531</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.929139438317088</v>
+        <v>3.896640134542188</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203666</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.018250783068252</v>
+        <v>-5.554943490318827</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.909445576151763</v>
+        <v>1.694768493251533</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.03515865216706471</v>
+        <v>-0.01900685412443603</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.93819750499305</v>
+        <v>3.905698201218149</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436931</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.716804057596415</v>
+        <v>-5.253496764846989</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.037285149223034</v>
+        <v>1.822608066322803</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.336605377638902</v>
+        <v>0.2824398713474012</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.126326423158688</v>
+        <v>4.093827119383787</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064768</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.741394301831598</v>
+        <v>-5.278087009082173</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.02842022928167</v>
+        <v>1.81374314638144</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.336605377638902</v>
+        <v>0.2824398713474012</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.127297600911398</v>
+        <v>4.094798297136498</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859302</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.690355925825078</v>
+        <v>-5.227048633075653</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.049678484064034</v>
+        <v>1.835001401163804</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.336605377638902</v>
+        <v>0.2824398713474012</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.128140505291154</v>
+        <v>4.095641201516253</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354685</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.649216630958447</v>
+        <v>-5.185909338209022</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.085172300884832</v>
+        <v>1.870495217984601</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3777446725055328</v>
+        <v>0.323579166214032</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.171862181085277</v>
+        <v>4.139362877310377</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085621</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.538610490878845</v>
+        <v>-5.07530319812942</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.945598753040607</v>
+        <v>1.730921670140377</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4883508125851348</v>
+        <v>0.4341853062936341</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.054409861256974</v>
+        <v>4.021910557482073</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462783</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.669191225409688</v>
+        <v>-5.205883932660263</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.896868503302234</v>
+        <v>1.682191420402004</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3577700780542923</v>
+        <v>0.3036045717627915</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.979563464612432</v>
+        <v>3.947064160837531</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.7750430212186</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.504694891218726</v>
+        <v>-5.041387598469301</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.947093856054701</v>
+        <v>1.732416773154471</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3577700780542923</v>
+        <v>0.3036045717627915</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.963990283688514</v>
+        <v>3.931490979913614</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462772</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.380214410494775</v>
+        <v>-4.91690711774535</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.996073758780711</v>
+        <v>1.781396675880481</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3577700780542923</v>
+        <v>0.3036045717627915</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.963177994124944</v>
+        <v>3.930678690350043</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,45 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.87680986327176</v>
+        <v>3.83232118453305</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.390599605384664</v>
+        <v>-4.927292312635239</v>
       </c>
       <c r="E2037" t="n">
-        <v>2.001788459949828</v>
+        <v>1.787111377049598</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.347384883164403</v>
+        <v>0.2932193768729022</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.966815656316083</v>
+        <v>3.934316352541183</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="2" t="n">
+        <v>45500</v>
+      </c>
+      <c r="B2038" t="n">
+        <v>3.463255670938917</v>
+      </c>
+      <c r="C2038" t="n">
+        <v>3.540046617474293</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>-4.927292312635239</v>
+      </c>
+      <c r="E2038" t="n">
+        <v>1.787111377049598</v>
+      </c>
+      <c r="F2038" t="n">
+        <v>0.2932193768729022</v>
+      </c>
+      <c r="G2038" t="n">
+        <v>3.533110414460661</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>30.9%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>58.7%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.4%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-668.6%</t>
+          <t>-639.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.6%</t>
+          <t>456.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.3%</t>
+          <t>-614.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-267.8%</t>
+          <t>-256.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.5%</t>
+          <t>-181.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-258.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-183.7%</t>
+          <t>-194.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-194.7%</t>
+          <t>-190.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-155.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-92.7%</t>
+          <t>-77.0%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.9622078420698927</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.736089201185021</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9508186054150913</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.738469691966182</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.368572628961928</v>
+        <v>-1.073588152288091</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.569294974052511</v>
+        <v>2.687288764722045</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>1.042227088974184</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.74241670333554</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65870429556736</v>
+        <v>-1.363719818893523</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.45310852400926</v>
+        <v>2.571102314678795</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>1.066308883714364</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.75673199677857</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.866708353920437</v>
+        <v>-1.5717238772466</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.374799045221954</v>
+        <v>2.492792835891489</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>1.066308883714364</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.761624141332495</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.928886765081407</v>
+        <v>-1.63390228840757</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.345009137095555</v>
+        <v>2.463002927765089</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>1.004130472553394</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.719398550973901</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.29495549222606</v>
+        <v>-1.999971015552223</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.191665945544142</v>
+        <v>2.309659736213677</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.6380617454087415</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.492841613993559</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.503446273677744</v>
+        <v>-2.208461797003907</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.128607922702237</v>
+        <v>2.246601713371772</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.4295709639570571</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.388085434861317</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.750647458442966</v>
+        <v>-2.455662981769129</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.037826199204717</v>
+        <v>2.155819989874252</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.4497243174558695</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.408276197369172</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.243032486467063</v>
+        <v>-2.948048009793226</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.84197858003881</v>
+        <v>1.959972370708345</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.04266071056822723</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.113951572598447</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.628212877397135</v>
+        <v>-3.333228400723298</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.686448962479644</v>
+        <v>1.804442753149179</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.04266071056822723</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.11249411141131</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.878083557411717</v>
+        <v>-3.58309908073788</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.588269813928428</v>
+        <v>1.706263604597963</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.006397990737763981</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.136020866764204</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.084595334298738</v>
+        <v>-3.789610857624901</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.501771161829877</v>
+        <v>1.619764952499412</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.2129097676247855</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>3.008219859288249</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.40393940937924</v>
+        <v>-4.108954932705403</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.375806458497936</v>
+        <v>1.493800249167471</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.2129097676247855</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>3.009992785988509</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.835745202529028</v>
+        <v>-4.540760725855191</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.189417028705426</v>
+        <v>1.30741081937496</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.3493272640660525</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.914475175591153</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.07043919666158</v>
+        <v>-4.775454719987743</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.083824206054495</v>
+        <v>1.20181799672403</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.3429909968367973</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.906561710930796</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.406101843892032</v>
+        <v>-5.111117367218196</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9481397388182793</v>
+        <v>1.066133529487814</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.4109219823257021</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.864383711293419</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.482546174094904</v>
+        <v>-5.187561697421067</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9240495669713722</v>
+        <v>1.042043357640907</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.3304764732320402</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.919138576983857</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.847673556733651</v>
+        <v>-5.552689080059814</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7772531289217053</v>
+        <v>0.8952469195912398</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.6267872575310527</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.740606621410281</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.256262333914329</v>
+        <v>-5.961277857240493</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6125791620641929</v>
+        <v>0.7305729527337275</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.494214899116633</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.370022745937193</v>
+        <v>-6.075038269263358</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5622604297265075</v>
+        <v>0.680254220396042</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.489400331588094</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.786414620224191</v>
+        <v>-6.491430143550355</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3936977306205858</v>
+        <v>0.5116915212901203</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.487394382196971</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.03068602095126</v>
+        <v>-6.735701544277425</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3062478609984369</v>
+        <v>0.4242416516679715</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.49765307286565</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.373944540594279</v>
+        <v>-7.078960063920444</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1650440182869248</v>
+        <v>0.2830378089564589</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.493752638011346</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.422147357836623</v>
+        <v>-7.127162881162787</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.144167811444988</v>
+        <v>0.2621616021145226</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.035376034711731</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.492157558066347</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.718808699646821</v>
+        <v>-7.423824222972985</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.02928225065011736</v>
+        <v>0.1472760413196519</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.10411917044561</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.454690652555227</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.905528407956123</v>
+        <v>-7.610543931282288</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.04943193720800698</v>
+        <v>0.06856185346152754</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.10411917044561</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.450664348020824</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.288529796698754</v>
+        <v>-7.993545320024919</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.202734594026643</v>
+        <v>-0.08474080335710887</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.10411917044561</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.45056224669924</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.293016241900142</v>
+        <v>-7.998031765226307</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2019576561357685</v>
+        <v>-0.08396386546623447</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.108605615646998</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.450441895549837</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.652546564404144</v>
+        <v>-8.35756208773031</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3404194818393189</v>
+        <v>-0.2224256911697853</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.108605615646998</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.455792198847887</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.702895627858366</v>
+        <v>-8.407911151184532</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.35264308726383</v>
+        <v>-0.2346492965942963</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.15895467910122</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.433498780732532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.800514905279762</v>
+        <v>-8.505530428605928</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3886490476106199</v>
+        <v>-0.2706552569410863</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.256573956522617</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.377968964901462</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.854586404788121</v>
+        <v>-8.559601928114287</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4073840910923909</v>
+        <v>-0.2893903004228573</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.310645456030977</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.348419621518019</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.058844580117984</v>
+        <v>-8.76386010344415</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4835741641056943</v>
+        <v>-0.3655803734361607</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.438284400644966</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.277349451868268</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.092497418626458</v>
+        <v>-8.797512941952624</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4925527450246476</v>
+        <v>-0.374558954355114</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.538697768562003</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.221583985602482</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.019027586959009</v>
+        <v>-8.724043110285175</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4477931108642466</v>
+        <v>-0.3297993201947129</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.465227936894554</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.281037586096372</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.194152004345552</v>
+        <v>-8.899167527671718</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5032876570713474</v>
+        <v>-0.3852938664018137</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.640352354281098</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.190518156411962</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.428604098360042</v>
+        <v>-9.133619621686208</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.604287659578739</v>
+        <v>-0.4862938689092053</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.640352354281098</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.183298991510366</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.532978829386488</v>
+        <v>-9.237994352712654</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6527097427632937</v>
+        <v>-0.5347159520937601</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.744727085307544</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.114001962120523</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.585764984986815</v>
+        <v>-9.290780508312981</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6727084151648683</v>
+        <v>-0.5547146244953347</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.840402571889941</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.057712460009641</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.711801778355104</v>
+        <v>-9.41681730168127</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7204294038830694</v>
+        <v>-0.6024356132135358</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815150949080199</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.075557162324601</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.654730006459173</v>
+        <v>-9.359745529785339</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6936103594382961</v>
+        <v>-0.5756165687687624</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815150949080199</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.079547498011002</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.796401848183294</v>
+        <v>-9.50141737150946</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7517543230266859</v>
+        <v>-0.6337605323571522</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815150949080199</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.07807227111226</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.746811003758459</v>
+        <v>-9.451826527084625</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7168645750918801</v>
+        <v>-0.5988707844223464</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.765560104655365</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.122880187932032</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.597892669286603</v>
+        <v>-9.302908192612769</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6703483749498202</v>
+        <v>-0.5523545842802866</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.734310513920192</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.128578808726453</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.372047516567193</v>
+        <v>-9.077063039893357</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5704312408258478</v>
+        <v>-0.4524374501563133</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.692383838333028</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.16331388711496</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.247468860229601</v>
+        <v>-8.952484383555765</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5194606337347518</v>
+        <v>-0.4014668430652177</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.692383838333028</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.164453031671019</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.300364148273887</v>
+        <v>-9.005379671600052</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5379849747903589</v>
+        <v>-0.4199911841208248</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.687428492244582</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.170060013486195</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.228230972986006</v>
+        <v>-8.93324649631217</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5033980004365701</v>
+        <v>-0.3854042097670356</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.687428492244582</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.175793717724831</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.156864580376359</v>
+        <v>-8.861880103702523</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4845887057865763</v>
+        <v>-0.3665949151170418</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.616062099634934</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.208876290896755</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.063405546391134</v>
+        <v>-8.768421069717299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.457088573505394</v>
+        <v>-0.3390947828358599</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.616062099634934</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.198992809583847</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.796163745522737</v>
+        <v>-8.501179268848901</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3520264136574087</v>
+        <v>-0.2340326229878742</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.616062099634934</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.197158249084473</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.698256706846246</v>
+        <v>-8.40327223017241</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3131639131602735</v>
+        <v>-0.195170122490739</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.548076349774378</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.237649384027346</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.674303165870288</v>
+        <v>-8.379318689196452</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3029139906243965</v>
+        <v>-0.184920199954862</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.52412280879842</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.252690014758414</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.410243227547491</v>
+        <v>-8.115258750873656</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2105503314570298</v>
+        <v>-0.09255654078749576</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.260062870475624</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.39786566159034</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.703163604042653</v>
+        <v>-7.408179127368817</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.06949448428460459</v>
+        <v>0.1874882749541387</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.260062870475624</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.395078627930039</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.662979305676463</v>
+        <v>-7.367994829002627</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.08591182751892212</v>
+        <v>0.2039056181884562</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.219878572109433</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.419532830837595</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.4995794347371</v>
+        <v>-7.204594958063264</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.150638597115424</v>
+        <v>0.2686323877849581</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.056478701170071</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.516939574621969</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.266098212507502</v>
+        <v>-6.971113735833666</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2519555148451156</v>
+        <v>0.3699493055146501</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8229974789404721</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.664952736797581</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.116431821499987</v>
+        <v>-6.821447344826151</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3089298609351627</v>
+        <v>0.4269236516046968</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7300939876979362</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.717802621230143</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.9841563478691</v>
+        <v>-6.689171871195264</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3572075371345442</v>
+        <v>0.4752013278040788</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.5978185140670496</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.792535392155702</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.828418015309358</v>
+        <v>-6.533433538635522</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4223179308460776</v>
+        <v>0.5403117215156121</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.442080181507308</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.888793452379184</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.579418216625777</v>
+        <v>-6.284433739951941</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5348241915431688</v>
+        <v>0.6528179822127034</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2472458891152278</v>
+        <v>-0.1930803828237273</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.018600369038091</v>
+        <v>3.051099672812991</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.685008206398882</v>
+        <v>-6.390023729725046</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3646122660347082</v>
+        <v>0.4826060567042427</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3528358788883322</v>
+        <v>-0.2986703725968317</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.827270445575009</v>
+        <v>2.85976974934991</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.703743108517479</v>
+        <v>-6.408758631843643</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4056626470643558</v>
+        <v>0.5236564377338904</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3584318885484635</v>
+        <v>-0.304266382256963</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.872457181656017</v>
+        <v>2.904956485430917</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.555803067109879</v>
+        <v>-6.260818590436044</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.344959740939228</v>
+        <v>0.4629535316087625</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3381109726399059</v>
+        <v>-0.2839454663484054</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.764770808512984</v>
+        <v>2.797270112287884</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.502833544855891</v>
+        <v>-6.207849068182055</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3574335635873451</v>
+        <v>0.4754273542568797</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.787838535611899</v>
+        <v>2.820337839386799</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.459285138085201</v>
+        <v>-6.164300661411365</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3678923142005281</v>
+        <v>0.4858861048700627</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.780877923516806</v>
+        <v>2.813377227291706</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.425921931606432</v>
+        <v>-6.130937454932596</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3956999511731789</v>
+        <v>0.5136937418427134</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.795340277897949</v>
+        <v>2.827839581672849</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.31766279448391</v>
+        <v>-6.022678317810074</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4335357264813826</v>
+        <v>0.5515295171509171</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2309759440944165</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.789872398357144</v>
+        <v>2.822371702132044</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.194371659666779</v>
+        <v>-5.899387182992943</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4803502744188117</v>
+        <v>0.5983440650883463</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1618503155687865</v>
+        <v>-0.107684809277286</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.861345173257999</v>
+        <v>2.893844477032899</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.173222460763336</v>
+        <v>-5.8782379840895</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4965109322175145</v>
+        <v>0.6145047228870486</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.08653561037384266</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88173567083739</v>
+        <v>2.914234974612291</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.929457018779892</v>
+        <v>-5.634472542106056</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.589797817357943</v>
+        <v>0.7077916080274771</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.08653561037384266</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.877516379184441</v>
+        <v>2.910015682959342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.827694198502597</v>
+        <v>-5.532709721828761</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6326272593888769</v>
+        <v>0.750621050058411</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.07331654198141396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.887572134139914</v>
+        <v>2.920071437914815</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.577843804553522</v>
+        <v>-5.282859327879686</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.725309491952209</v>
+        <v>0.843303282621743</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.07331654198141396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.880314209123616</v>
+        <v>2.912813512898517</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.40195171208609</v>
+        <v>-5.106967235412254</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7992654524598302</v>
+        <v>0.9172592431293647</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.07331654198141396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.883913332644265</v>
+        <v>2.916412636419166</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.230505249063627</v>
+        <v>-4.935520772389791</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8811715437233696</v>
+        <v>0.9991653343929037</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04396441474954865</v>
+        <v>0.09812992104104917</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.000108716512297</v>
+        <v>3.032608020287197</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.156215683325287</v>
+        <v>-4.861231206651452</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9099078476350022</v>
+        <v>1.027901638304536</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1182539804878879</v>
+        <v>0.1724194867793885</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.043702933571597</v>
+        <v>3.076202237346497</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.092579941091353</v>
+        <v>-4.797595464417517</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9400569455828931</v>
+        <v>1.058050736252427</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.236055229013323</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.086579179966275</v>
+        <v>3.119078483741176</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.981153181765433</v>
+        <v>-4.686168705091597</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9658219080970567</v>
+        <v>1.083815698766591</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.236055229013323</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.067773438750071</v>
+        <v>3.100272742524971</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.740722684960573</v>
+        <v>-4.445738208286737</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.063737183443878</v>
+        <v>1.181730974113413</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4223202195266827</v>
+        <v>0.4764857258181833</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.213774813457865</v>
+        <v>3.246274117232765</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.668480116789378</v>
+        <v>-4.373495640115542</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.096563524547176</v>
+        <v>1.214557315216711</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4223202195266827</v>
+        <v>0.4764857258181833</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.217704127292685</v>
+        <v>3.250203431067585</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.650766429911513</v>
+        <v>-4.355781953237677</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.104327583215662</v>
+        <v>1.222321373885197</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4255015484235996</v>
+        <v>0.4796670547151001</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.220291508548175</v>
+        <v>3.252790812323075</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.541961544431786</v>
+        <v>-4.24697706775795</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.144847608627547</v>
+        <v>1.262841399297081</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4255015484235996</v>
+        <v>0.4796670547151001</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.217289579768168</v>
+        <v>3.249788883543069</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.321940746394775</v>
+        <v>-4.026956269720939</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.234434964852965</v>
+        <v>1.352428755522499</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5667213934915798</v>
+        <v>0.6208868997830803</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.303600523819571</v>
+        <v>3.336099827594471</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.189073057331497</v>
+        <v>-3.894088580657661</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.3034762232801</v>
+        <v>1.421470013949634</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5667213934915798</v>
+        <v>0.6208868997830803</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.319494706621394</v>
+        <v>3.351994010396294</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.068899973966999</v>
+        <v>-3.773915497293162</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.352691301066201</v>
+        <v>1.470685091735735</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6868944768560787</v>
+        <v>0.7410599831475793</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.392744401080395</v>
+        <v>3.425243704855296</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.924227828867261</v>
+        <v>-3.629243352193424</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.420648261667536</v>
+        <v>1.538642052337071</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8315666219558162</v>
+        <v>0.8857321282473167</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.489635790701677</v>
+        <v>3.522135094476578</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.984102656224954</v>
+        <v>-3.689118179551117</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.382735822125885</v>
+        <v>1.500729612795419</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7716917945981241</v>
+        <v>0.8258573008896246</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.439748385688488</v>
+        <v>3.472247689463388</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.864282425314116</v>
+        <v>-3.569297948640279</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.445953083724428</v>
+        <v>1.563946874393963</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7716917945981241</v>
+        <v>0.8258573008896246</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.455037554922697</v>
+        <v>3.487536858697597</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.866752131775922</v>
+        <v>-3.571767655102085</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.352609400462147</v>
+        <v>1.470603191131682</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7692220881363179</v>
+        <v>0.8233875944278184</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.361199930368054</v>
+        <v>3.393699234142955</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.935122318099932</v>
+        <v>-3.640137841426095</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.244523187417845</v>
+        <v>1.362516978087379</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.286027211275085</v>
+        <v>3.318526515049985</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.948910370946979</v>
+        <v>-3.653925894273142</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.229444674910917</v>
+        <v>1.347438465580452</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.276463919906976</v>
+        <v>3.308963223681876</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.004430446839568</v>
+        <v>-3.709445970165731</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.344267481246084</v>
+        <v>1.462261271915619</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.413494756599178</v>
+        <v>3.445994060374079</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.828956187047099</v>
+        <v>-3.533971710373262</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.419024417154859</v>
+        <v>1.537018207824394</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.418061988590966</v>
+        <v>3.450561292365867</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.939892439688347</v>
+        <v>-3.644907963014511</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.350391944859567</v>
+        <v>1.468385735529102</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7784977871725328</v>
+        <v>0.8326632934640333</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.393804017352173</v>
+        <v>3.426303321127074</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.906228894216066</v>
+        <v>-3.611244417542229</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.29239567644993</v>
+        <v>1.410389467119464</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8121613326448147</v>
+        <v>0.8663268389363152</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.342540458036992</v>
+        <v>3.375039761811892</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.846376275012342</v>
+        <v>-3.551391798338506</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.326509110563551</v>
+        <v>1.444502901233086</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8121613326448147</v>
+        <v>0.8663268389363152</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.352712844469124</v>
+        <v>3.385212148244025</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.760132811985965</v>
+        <v>-3.465148335312128</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.355952766347962</v>
+        <v>1.473946557017497</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8121613326448147</v>
+        <v>0.8663268389363152</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.347659115042985</v>
+        <v>3.380158418817885</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.805439631384945</v>
+        <v>-3.510455154711108</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.329605814032896</v>
+        <v>1.447599604702431</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7713511696355839</v>
+        <v>0.8255166759270844</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.314948792681972</v>
+        <v>3.347448096456872</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.834472736087247</v>
+        <v>-3.53948825941341</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.318544445185077</v>
+        <v>1.436538235854612</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7713511696355839</v>
+        <v>0.8255166759270844</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.315500665715073</v>
+        <v>3.347999969489974</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.741662254636387</v>
+        <v>-3.446677777962551</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.284941329656786</v>
+        <v>1.402935120326321</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8641616510864433</v>
+        <v>0.9183271573779438</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.300459646476955</v>
+        <v>3.332958950251855</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.786051723965815</v>
+        <v>-3.491067247291978</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.269059017849616</v>
+        <v>1.387052808519151</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8197721817570156</v>
+        <v>0.8739376880485161</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.275699440803899</v>
+        <v>3.308198744578799</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.902593329071158</v>
+        <v>-3.607608852397321</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.217518084319202</v>
+        <v>1.335511874988737</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7032305766516729</v>
+        <v>0.7573960829431734</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.200850186252416</v>
+        <v>3.233349490027317</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.031924558465223</v>
+        <v>-3.495231851214649</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.171276888392243</v>
+        <v>1.385953971292473</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7032305766516729</v>
+        <v>0.7573960829431734</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.206341482083084</v>
+        <v>3.238840785857984</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.059704956366575</v>
+        <v>-3.523012249116002</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.171661931000241</v>
+        <v>1.386339013900471</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6754501787503198</v>
+        <v>0.7296156850418203</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.201170445110811</v>
+        <v>3.233669748885711</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.178085629096714</v>
+        <v>-3.64139292184614</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9626653819088391</v>
+        <v>1.177342464809069</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6082323265993436</v>
+        <v>0.6623978328908441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.999195453820878</v>
+        <v>3.031694757595778</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.286699707540045</v>
+        <v>-3.750007000289471</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.039369411250712</v>
+        <v>1.254046494150942</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6082323265993436</v>
+        <v>0.6623978328908441</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.119345114540084</v>
+        <v>3.151844418314984</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.251290669291902</v>
+        <v>-3.714597962041328</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.068046052652293</v>
+        <v>1.282723135552522</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6082323265993436</v>
+        <v>0.6623978328908441</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.133858140642407</v>
+        <v>3.166357444417307</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.212907006733751</v>
+        <v>-3.676214299483177</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.080818959017922</v>
+        <v>1.295496041918151</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6466159891574947</v>
+        <v>0.7007814954489953</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.154307779519666</v>
+        <v>3.186807083294567</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.035790676698585</v>
+        <v>-3.499097969448011</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.14839451987729</v>
+        <v>1.363071602777519</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6466159891574947</v>
+        <v>0.7007814954489953</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.151036808364968</v>
+        <v>3.183536112139869</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.080882921532131</v>
+        <v>-3.544190214281556</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.131041013705785</v>
+        <v>1.345718096606014</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5847199459881049</v>
+        <v>0.6388854522796055</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.114582574225247</v>
+        <v>3.147081878000148</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.901507500293363</v>
+        <v>-3.364814793042789</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.196578157507706</v>
+        <v>1.411255240407936</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7414967041588236</v>
+        <v>0.7956622104503241</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.202435604434093</v>
+        <v>3.234934908208993</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.946521713813969</v>
+        <v>-3.409829006563395</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.159379927431053</v>
+        <v>1.374057010331283</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.711147808844219</v>
+        <v>0.7653133151357195</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.16503372257692</v>
+        <v>3.19753302635182</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.213526224086404</v>
+        <v>-3.67683351683583</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.058269685661025</v>
+        <v>1.272946768561255</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5167847708012705</v>
+        <v>0.570950277092771</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.054107462090097</v>
+        <v>3.086606765864997</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.314724005523577</v>
+        <v>-3.778031298273003</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.016994494982657</v>
+        <v>1.231671577882887</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4483759572559513</v>
+        <v>0.5025414635474519</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.012266095859407</v>
+        <v>3.044765399634307</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.308213038909265</v>
+        <v>-3.77152033165869</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.017198843182699</v>
+        <v>1.231875926082929</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4483759572559513</v>
+        <v>0.5025414635474519</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.009866057413723</v>
+        <v>3.042365361188624</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.289174911201967</v>
+        <v>-3.752482203951393</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.021338813473863</v>
+        <v>1.236015896374093</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3901923459247568</v>
+        <v>0.4443578522162573</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.971480609823252</v>
+        <v>3.003979913598152</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.320301542352586</v>
+        <v>-3.783608835102011</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.128182562647806</v>
+        <v>1.342859645548036</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3901923459247568</v>
+        <v>0.4443578522162573</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.090775011457442</v>
+        <v>3.123274315232342</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.334168303686504</v>
+        <v>-3.937917782735934</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.123469187100372</v>
+        <v>1.2819693954806</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3523344291909338</v>
+        <v>0.3899772709027647</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.068893590403281</v>
+        <v>3.09147929543038</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.289364132146574</v>
+        <v>-3.893113611196004</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.14739938611327</v>
+        <v>1.305899594493498</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3523344291909338</v>
+        <v>0.3899772709027647</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.074902120800207</v>
+        <v>3.097487825827306</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.141621161911571</v>
+        <v>-3.745370640961001</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.104446795484471</v>
+        <v>1.262947003864699</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.520141786425817</v>
+        <v>0.5577846281376478</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.073536756418337</v>
+        <v>3.096122461445435</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.243635844442792</v>
+        <v>-3.847385323492222</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.066434544003463</v>
+        <v>1.224934752383691</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.520141786425817</v>
+        <v>0.5577846281376478</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.076330377949818</v>
+        <v>3.098916082976916</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.237483138390008</v>
+        <v>-3.841232617439438</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.069557974816235</v>
+        <v>1.228058183196463</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5262944924786013</v>
+        <v>0.5639373341904321</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.080684349973147</v>
+        <v>3.103270055000245</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.25429243654051</v>
+        <v>-3.858041915589939</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.061914732296145</v>
+        <v>1.220414940676373</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5094851943280996</v>
+        <v>0.5471280360399304</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.069679247822956</v>
+        <v>3.092264952850055</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.191994437764388</v>
+        <v>-3.795743916813818</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.153169485603415</v>
+        <v>1.311669693983643</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5094851943280996</v>
+        <v>0.5471280360399304</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.136014801619777</v>
+        <v>3.158600506646875</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.99020424009923</v>
+        <v>-3.59395371914866</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.036177566383605</v>
+        <v>1.194677774763833</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.707503386497254</v>
+        <v>0.7451462282090848</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.057117718635397</v>
+        <v>3.079703423662495</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.041090952785424</v>
+        <v>-3.644840431834854</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.086113113631302</v>
+        <v>1.24461332201153</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6566166738110595</v>
+        <v>0.6942595155228903</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.096875923345855</v>
+        <v>3.119461628372954</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.138831497410399</v>
+        <v>-3.742580976459829</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.061644631897356</v>
+        <v>1.220144840277584</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6407273956780792</v>
+        <v>0.6783702373899101</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.101970092582111</v>
+        <v>3.124555797609209</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.199040795415684</v>
+        <v>-3.802790274465113</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.036096893519914</v>
+        <v>1.194597101900142</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5805180976727947</v>
+        <v>0.6181609393846256</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.064380494603612</v>
+        <v>3.08696619963071</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.122618748983757</v>
+        <v>-3.726368228033186</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.065157330132613</v>
+        <v>1.223657538512841</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5805180976727947</v>
+        <v>0.6181609393846256</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.06287211264354</v>
+        <v>3.085457817670639</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.078245617345188</v>
+        <v>-3.681995096394618</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.082769450223477</v>
+        <v>1.241269658603705</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6248912293113633</v>
+        <v>0.6625340710231942</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.089358859062118</v>
+        <v>3.111944564089216</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.100725968204073</v>
+        <v>-3.704475447253503</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.068171104018513</v>
+        <v>1.226671312398742</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6248912293113633</v>
+        <v>0.6625340710231942</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.083752653200708</v>
+        <v>3.106338358227807</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.053070237643017</v>
+        <v>-3.656819716692447</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.09361515327074</v>
+        <v>1.252115361650968</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.672546959872419</v>
+        <v>0.7101898015842498</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.118727848565146</v>
+        <v>3.141313553592245</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.952552079144263</v>
+        <v>-3.556301558193693</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.138714790044967</v>
+        <v>1.297214998425195</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7730651183711735</v>
+        <v>0.8107079600830044</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.183931117039124</v>
+        <v>3.206516822066222</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.013218669546651</v>
+        <v>-3.616968148596082</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.101202826359884</v>
+        <v>1.259703034740112</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6913668016526399</v>
+        <v>0.7290096433644707</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.121666799483876</v>
+        <v>3.144252504510974</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.968380267938253</v>
+        <v>-3.572129746987684</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.123235889613872</v>
+        <v>1.281736097994099</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6959102345975093</v>
+        <v>0.7335530763093402</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.128490561861426</v>
+        <v>3.151076266888524</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.987878724180261</v>
+        <v>-3.591628203229692</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.119597446748146</v>
+        <v>1.278097655128374</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.647825593317605</v>
+        <v>0.6854684350294359</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.103800716724561</v>
+        <v>3.12638642175166</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.943675887094361</v>
+        <v>-3.547425366143791</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.143158184110344</v>
+        <v>1.301658392490571</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6920284304035055</v>
+        <v>0.7296712721153363</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.136202021503939</v>
+        <v>3.158787726531037</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.980654914757804</v>
+        <v>-3.584404393807235</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.126776573514214</v>
+        <v>1.285276781894442</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.729002332194836</v>
+        <v>0.7666451739066669</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.156796363047984</v>
+        <v>3.179382068075083</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.822363497218532</v>
+        <v>-3.426112976267962</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.241340905712963</v>
+        <v>1.39984111409319</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.729002332194836</v>
+        <v>0.7666451739066669</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.208044128231024</v>
+        <v>3.230629833258123</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.865338681321016</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.614721493584056</v>
+        <v>-3.218470972633486</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.322838411761006</v>
+        <v>1.481338620141234</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366443358293122</v>
+        <v>0.974287177541143</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.331070035005963</v>
+        <v>3.353655740033062</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.563689400861528</v>
+        <v>-3.167438879910958</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.338199477088287</v>
+        <v>1.496699685468515</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876764285518401</v>
+        <v>1.025319270263671</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.35663751887775</v>
+        <v>3.379223223904849</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.498465219734322</v>
+        <v>-3.102214698783753</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.381476553631874</v>
+        <v>1.539976762012102</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052900609679046</v>
+        <v>1.090543451390877</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.412959431646778</v>
+        <v>3.435545136673877</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.461038199663188</v>
+        <v>-3.064787678712619</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.392408333959609</v>
+        <v>1.550908542339836</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058152147708227</v>
+        <v>1.095794989420058</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.412071326763567</v>
+        <v>3.434657031790666</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.481149855697896</v>
+        <v>-3.084899334747327</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.385620463876965</v>
+        <v>1.544120672257193</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069179492705646</v>
+        <v>1.106822334417478</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.419944526093259</v>
+        <v>3.442530231120358</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.82866144563628</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.427405041270692</v>
+        <v>-3.031154520320122</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.567676160669058</v>
+        <v>1.726176369049286</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.079242802146108</v>
+        <v>1.11688564385794</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.586540282778747</v>
+        <v>3.609125987805846</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.352622780245679</v>
+        <v>-2.95637225929511</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.71770197429688</v>
+        <v>1.876202182677108</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.154025063171121</v>
+        <v>1.191667904882952</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.751522548611572</v>
+        <v>3.774108253638671</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.326538695981871</v>
+        <v>-2.930288175031302</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.719843584016262</v>
+        <v>1.87834379239649</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.154025063171121</v>
+        <v>1.191667904882952</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.743230524625431</v>
+        <v>3.76581622965253</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896923</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.248407515132924</v>
+        <v>-2.852156994182355</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.749289251939621</v>
+        <v>1.907789460319848</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.228201874054806</v>
+        <v>1.265844715766637</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.785929806739421</v>
+        <v>3.80851551176652</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.239515053739641</v>
+        <v>-2.843264532789072</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.770400642223725</v>
+        <v>1.928900850603953</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.228201874054806</v>
+        <v>1.265844715766637</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.803484212466213</v>
+        <v>3.826069917493311</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.407991170709519</v>
+        <v>-3.01174064975895</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.694865242840358</v>
+        <v>1.853365451220586</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.200254038338225</v>
+        <v>1.237896880050056</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.778570558440848</v>
+        <v>3.801156263467947</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782701</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.710191641847936</v>
+        <v>-2.313941120897367</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.955254751572853</v>
+        <v>2.113754959953081</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.129905978967814</v>
+        <v>1.167548820679646</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.717631420006464</v>
+        <v>3.740217125033563</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.687470538164783</v>
+        <v>-2.291220017214214</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.955007215543019</v>
+        <v>2.113507423923247</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.129905978967814</v>
+        <v>1.167548820679646</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.708295442503368</v>
+        <v>3.730881147530467</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.816672351458826</v>
+        <v>-2.420421830508257</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.062232616076571</v>
+        <v>2.220732824456799</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.000704165673772</v>
+        <v>1.038347007385603</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.789680480378112</v>
+        <v>3.81226618540521</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.971453358237081</v>
+        <v>-2.575202837286512</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.037398035858915</v>
+        <v>2.195898244239143</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9673364916192959</v>
+        <v>1.004979333331127</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.806737698439073</v>
+        <v>3.829323403466172</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799958</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.964398668021908</v>
+        <v>-2.568148147071339</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.03689526793453</v>
+        <v>2.195395476314757</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9743911818344697</v>
+        <v>1.012034023546301</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.807645868557722</v>
+        <v>3.830231573584821</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.93744744369542</v>
+        <v>-2.541196922744851</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.057681911309866</v>
+        <v>2.216182119690094</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9892715278621889</v>
+        <v>1.02691436957402</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.826580229819095</v>
+        <v>3.849165934846194</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.073400451751736</v>
+        <v>-2.677149930801167</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.1874038402323</v>
+        <v>2.345904048612527</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9892715278621889</v>
+        <v>1.02691436957402</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.010683361964055</v>
+        <v>4.033269066991154</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.095808569556608</v>
+        <v>-2.699558048606039</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.170557288013344</v>
+        <v>2.329057496393572</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9892715278621889</v>
+        <v>1.02691436957402</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.002800056867049</v>
+        <v>4.025385761894147</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.243814337036008</v>
+        <v>-2.847563816085438</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.113408980571222</v>
+        <v>2.271909188951449</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9025445189986474</v>
+        <v>0.9401873607104787</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.952817851098561</v>
+        <v>3.975403556125659</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.253255262924537</v>
+        <v>-2.857004741973968</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.165886327937657</v>
+        <v>2.324386536317885</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.024971636542039</v>
+        <v>1.06261447825387</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.082527839346443</v>
+        <v>4.105113544373541</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.305528870260179</v>
+        <v>-2.90927834930961</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.147867979548701</v>
+        <v>2.306368187928929</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9726980292063977</v>
+        <v>1.010340870918229</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.054054769490358</v>
+        <v>4.076640474517458</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.381858847861085</v>
+        <v>-2.985608326910516</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.115447801402114</v>
+        <v>2.273948009782342</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9726980292063977</v>
+        <v>1.010340870918229</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.052166582384134</v>
+        <v>4.074752287411233</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.584112568185438</v>
+        <v>-3.187862047234869</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.029366542875235</v>
+        <v>2.187866751255463</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7704443088820443</v>
+        <v>0.8080871505938754</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.925634579792384</v>
+        <v>3.948220284819483</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343059</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.745680993712693</v>
+        <v>-3.349430472762124</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.963173182874485</v>
+        <v>2.121673391254713</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6436613850841649</v>
+        <v>0.681304226795996</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.847998835723809</v>
+        <v>3.870584540750908</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.7549119076471</v>
+        <v>3.754911907647099</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.877982285810246</v>
+        <v>-3.481731764859677</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.923326072901383</v>
+        <v>2.08182628128161</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6436613850841649</v>
+        <v>0.681304226795996</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.861072242589727</v>
+        <v>3.883657947616826</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.749896851763527</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.879543928625107</v>
+        <v>-3.483293407674537</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.922701415775439</v>
+        <v>2.081201624155666</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6436613850841649</v>
+        <v>0.681304226795996</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.861072242589727</v>
+        <v>3.883657947616826</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392112</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.90744471573458</v>
+        <v>-3.51119419478401</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.910065142058651</v>
+        <v>2.068565350438879</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6090644609412301</v>
+        <v>0.6467073026530612</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.838838129230969</v>
+        <v>3.861423834258067</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172521</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.029970818437473</v>
+        <v>-3.633720297486904</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.857819144954693</v>
+        <v>2.01631935333492</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4865383582383362</v>
+        <v>0.5241811999501673</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.762086911586431</v>
+        <v>3.78467261661353</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971073</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.260485314623062</v>
+        <v>-3.864234793672493</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.832319306070961</v>
+        <v>1.990819514451188</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2560238620527475</v>
+        <v>0.2936667037645786</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.690484173465582</v>
+        <v>3.71306987849268</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.6407642481998</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.517206132617886</v>
+        <v>-4.120955611667316</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.869942697874878</v>
+        <v>2.028442906255106</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.1852521296207638</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.76574714798114</v>
+        <v>3.788332853008238</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.66830316462223</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.671192550394027</v>
+        <v>-4.274942029443457</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.877328399910062</v>
+        <v>2.03582860829029</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.1852521296207638</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.83472741712678</v>
+        <v>3.857313122153878</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808523</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.620670646566361</v>
+        <v>-4.224420125615791</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.883588363561249</v>
+        <v>2.042088571941477</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.1852521296207638</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.820778619246901</v>
+        <v>3.843364324273999</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994888</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.873145800574085</v>
+        <v>-4.476895279623515</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.794468791013573</v>
+        <v>1.952968999393801</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.1852521296207638</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.832649108302315</v>
+        <v>3.855234813329413</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358292</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.142618602495793</v>
+        <v>-4.746368081545223</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.687890204763834</v>
+        <v>1.846390413144062</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1476092879089327</v>
+        <v>0.1852521296207638</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.833859642821258</v>
+        <v>3.856445347848357</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637081</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.300162674225235</v>
+        <v>-4.903912153274665</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.628994318299378</v>
+        <v>1.787494526679607</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08070748276865819</v>
+        <v>0.1183503244804893</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.797840301964415</v>
+        <v>3.820426006991513</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301338</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.578127069808509</v>
+        <v>-5.181876548857939</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.512886412802259</v>
+        <v>1.671386621182486</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.008912251516826064</v>
+        <v>0.02873059019500501</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.739146314129314</v>
+        <v>3.761732019156412</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215464</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.6950947624474</v>
+        <v>-5.29884424149683</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.628303392445746</v>
+        <v>1.786803600825974</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.008912251516826064</v>
+        <v>0.02873059019500501</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.901350370828358</v>
+        <v>3.923936075855456</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.696553628456686</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.779812704668353</v>
+        <v>-5.383562183717783</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.589262853521179</v>
+        <v>1.747763061901407</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.09402828044487244</v>
+        <v>-0.05638543873304136</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.845127391435344</v>
+        <v>3.867713096462443</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253281</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.861747522937236</v>
+        <v>-5.465497001986666</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.566718343782117</v>
+        <v>1.725218552162345</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1039630260319526</v>
+        <v>-0.06632018432012154</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.849395961651587</v>
+        <v>3.871981666678686</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.783647027717826</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.808009349536974</v>
+        <v>-5.411758828586404</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.597139251598124</v>
+        <v>1.755639459978352</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.05022485263169052</v>
+        <v>-0.01258201091985944</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.890564504147647</v>
+        <v>3.913150209174746</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616943</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.698003066059752</v>
+        <v>-5.301752545109182</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.633294652233188</v>
+        <v>1.791794860613416</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02702028071441531</v>
+        <v>0.01062256099741576</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.896640134542188</v>
+        <v>3.919225839569286</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.554943490318827</v>
+        <v>-5.158692969368257</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.694768493251533</v>
+        <v>1.853268701631761</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01900685412443603</v>
+        <v>0.01863598758739504</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.905698201218149</v>
+        <v>3.928283906245248</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436923</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.253496764846989</v>
+        <v>-4.857246243896419</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.822608066322803</v>
+        <v>1.981108274703032</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2824398713474012</v>
+        <v>0.3200827130592323</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.093827119383787</v>
+        <v>4.116412824410887</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064762</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.278087009082173</v>
+        <v>-4.881836488131603</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.81374314638144</v>
+        <v>1.972243354761668</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2824398713474012</v>
+        <v>0.3200827130592323</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.094798297136498</v>
+        <v>4.117384002163597</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859295</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.227048633075653</v>
+        <v>-4.830798112125083</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.835001401163804</v>
+        <v>1.993501609544032</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2824398713474012</v>
+        <v>0.3200827130592323</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.095641201516253</v>
+        <v>4.118226906543352</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354681</v>
+        <v>3.831748677354679</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.185909338209022</v>
+        <v>-4.789658817258452</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.870495217984601</v>
+        <v>2.02899542636483</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.323579166214032</v>
+        <v>0.3612220079258631</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.139362877310377</v>
+        <v>4.161948582337476</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085615</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.07530319812942</v>
+        <v>-4.67905267717885</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.730921670140377</v>
+        <v>1.889421878520605</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4341853062936341</v>
+        <v>0.4718281480054651</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.021910557482073</v>
+        <v>4.044496262509171</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.804703121462777</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.205883932660263</v>
+        <v>-4.809633411709693</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.682191420402004</v>
+        <v>1.840691628782232</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3036045717627915</v>
+        <v>0.3412474134746226</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.947064160837531</v>
+        <v>3.96964986586463</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218596</v>
+        <v>3.775043021218594</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.041387598469301</v>
+        <v>-4.645137077518731</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.732416773154471</v>
+        <v>1.890916981534699</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3036045717627915</v>
+        <v>0.3412474134746226</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.931490979913614</v>
+        <v>3.954076684940713</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.821044820462765</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.91690711774535</v>
+        <v>-4.52065659679478</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.781396675880481</v>
+        <v>1.939896884260709</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3036045717627915</v>
+        <v>0.3412474134746226</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.930678690350043</v>
+        <v>3.953264395377142</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83232118453305</v>
+        <v>3.832321184533051</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.927292312635239</v>
+        <v>-4.531041791684669</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.787111377049598</v>
+        <v>1.945611585429826</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2932193768729022</v>
+        <v>0.3308622185847333</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.934316352541183</v>
+        <v>3.956902057568281</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.463255670938917</v>
+        <v>3.80645021107204</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.540046617474293</v>
+        <v>3.697173450686591</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.927292312635239</v>
+        <v>-4.531041791684669</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.787111377049598</v>
+        <v>1.945611585429826</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2932193768729022</v>
+        <v>0.3308622185847333</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.533110414460661</v>
+        <v>3.690237247672958</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-639.1%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.4%</t>
+          <t>454.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.7%</t>
+          <t>-632.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-256.0%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.7%</t>
+          <t>-188.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-258.3%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-194.1%</t>
+          <t>-188.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-190.9%</t>
+          <t>-193.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-74.6%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.073588152288091</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.687288764722045</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.042227088974184</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.74241670333554</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.363719818893523</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.571102314678795</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.066308883714364</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.75673199677857</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.5717238772466</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.492792835891489</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.066308883714364</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.761624141332495</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.63390228840757</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.463002927765089</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.004130472553394</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.719398550973901</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.999971015552223</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.309659736213677</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6380617454087415</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.492841613993559</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.208461797003907</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.246601713371772</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4295709639570571</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.388085434861317</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.455662981769129</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.155819989874252</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4497243174558695</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.408276197369172</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.948048009793226</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.959972370708345</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.04266071056822723</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.113951572598447</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.333228400723298</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.804442753149179</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.04266071056822723</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.11249411141131</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.58309908073788</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.706263604597963</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.006397990737763981</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.136020866764204</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.789610857624901</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.619764952499412</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2129097676247855</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.008219859288249</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.108954932705403</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.493800249167471</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2129097676247855</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.009992785988509</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.540760725855191</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.30741081937496</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.3493272640660525</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.914475175591153</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.775454719987743</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.20181799672403</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3429909968367973</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.906561710930796</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.111117367218196</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.066133529487814</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4109219823257021</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.864383711293419</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.187561697421067</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.042043357640907</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3304764732320402</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.919138576983857</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.552689080059814</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8952469195912398</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6267872575310527</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.740606621410281</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.961277857240493</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7305729527337275</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.494214899116633</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.075038269263358</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.680254220396042</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.489400331588094</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.491430143550355</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5116915212901203</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.487394382196971</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.735701544277425</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4242416516679715</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.49765307286565</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.078960063920444</v>
+        <v>-7.133125570211944</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2830378089564589</v>
+        <v>0.2613716064398588</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.493752638011346</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.127162881162787</v>
+        <v>-7.181328387454288</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2621616021145226</v>
+        <v>0.2404953995979224</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.035376034711731</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.492157558066347</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.423824222972985</v>
+        <v>-7.477989729264485</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1472760413196519</v>
+        <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.10411917044561</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.454690652555227</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.610543931282288</v>
+        <v>-7.664709437573788</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.06856185346152754</v>
+        <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.10411917044561</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.450664348020824</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.993545320024919</v>
+        <v>-8.047710826316418</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.08474080335710887</v>
+        <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.10411917044561</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.45056224669924</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.998031765226307</v>
+        <v>-8.052197271517807</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.08396386546623447</v>
+        <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.108605615646998</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.450441895549837</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.35756208773031</v>
+        <v>-8.411727594021809</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2224256911697853</v>
+        <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.108605615646998</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.455792198847887</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.407911151184532</v>
+        <v>-8.462076657476031</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2346492965942963</v>
+        <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.15895467910122</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.433498780732532</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.505530428605928</v>
+        <v>-8.559695934897427</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2706552569410863</v>
+        <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.256573956522617</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.377968964901462</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.559601928114287</v>
+        <v>-8.613767434405785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2893903004228573</v>
+        <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.310645456030977</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.348419621518019</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.76386010344415</v>
+        <v>-8.818025609735649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3655803734361607</v>
+        <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.438284400644966</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.277349451868268</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.797512941952624</v>
+        <v>-8.851678448244122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.374558954355114</v>
+        <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.538697768562003</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.221583985602482</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.724043110285175</v>
+        <v>-8.778208616576674</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3297993201947129</v>
+        <v>-0.3514655227113126</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.465227936894554</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.281037586096372</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.899167527671718</v>
+        <v>-8.953333033963217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3852938664018137</v>
+        <v>-0.406960068918413</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.640352354281098</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.190518156411962</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.133619621686208</v>
+        <v>-9.187785127977707</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4862938689092053</v>
+        <v>-0.507960071425805</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.640352354281098</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.183298991510366</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.237994352712654</v>
+        <v>-9.292159859004153</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5347159520937601</v>
+        <v>-0.5563821546103598</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.744727085307544</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.114001962120523</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.290780508312981</v>
+        <v>-9.34494601460448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5547146244953347</v>
+        <v>-0.5763808270119339</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.840402571889941</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.057712460009641</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.41681730168127</v>
+        <v>-9.470982807972769</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6024356132135358</v>
+        <v>-0.624101815730135</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.815150949080199</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.075557162324601</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.359745529785339</v>
+        <v>-9.413911036076838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5756165687687624</v>
+        <v>-0.5972827712853621</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.815150949080199</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.079547498011002</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.50141737150946</v>
+        <v>-9.555582877800958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6337605323571522</v>
+        <v>-0.6554267348737519</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.815150949080199</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.07807227111226</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.451826527084625</v>
+        <v>-9.505992033376124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5988707844223464</v>
+        <v>-0.6205369869389457</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.765560104655365</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.122880187932032</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.302908192612769</v>
+        <v>-9.357073698904268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5523545842802866</v>
+        <v>-0.5740207867968863</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.734310513920192</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.128578808726453</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.077063039893357</v>
+        <v>-9.131228546184857</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4524374501563133</v>
+        <v>-0.4741036526729134</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.692383838333028</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.16331388711496</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.952484383555765</v>
+        <v>-9.006649889847266</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4014668430652177</v>
+        <v>-0.4231330455818179</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.692383838333028</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.164453031671019</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.005379671600052</v>
+        <v>-9.059545177891552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4199911841208248</v>
+        <v>-0.4416573866374249</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.687428492244582</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.170060013486195</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.93324649631217</v>
+        <v>-8.987412002603671</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3854042097670356</v>
+        <v>-0.4070704122836357</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.687428492244582</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.175793717724831</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.861880103702523</v>
+        <v>-8.916045609994024</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3665949151170418</v>
+        <v>-0.3882611176336423</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.616062099634934</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.208876290896755</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.768421069717299</v>
+        <v>-8.822586576008799</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3390947828358599</v>
+        <v>-0.36076098535246</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.616062099634934</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.198992809583847</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.501179268848901</v>
+        <v>-8.555344775140401</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2340326229878742</v>
+        <v>-0.2556988255044748</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.616062099634934</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.197158249084473</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.40327223017241</v>
+        <v>-8.457437736463911</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.195170122490739</v>
+        <v>-0.2168363250073391</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.548076349774378</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.237649384027346</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.379318689196452</v>
+        <v>-8.433484195487953</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.184920199954862</v>
+        <v>-0.2065864024714625</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.52412280879842</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.252690014758414</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.115258750873656</v>
+        <v>-8.169424257165156</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09255654078749576</v>
+        <v>-0.1142227433040959</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.260062870475624</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.39786566159034</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.408179127368817</v>
+        <v>-7.462344633660318</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1874882749541387</v>
+        <v>0.1658220724375385</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.260062870475624</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.395078627930039</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.367994829002627</v>
+        <v>-7.422160335294127</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2039056181884562</v>
+        <v>0.1822394156718561</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.219878572109433</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.419532830837595</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.204594958063264</v>
+        <v>-7.258760464354765</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2686323877849581</v>
+        <v>0.246966185268358</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.056478701170071</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.516939574621969</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.971113735833666</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3699493055146501</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8229974789404721</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.664952736797581</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.821447344826151</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4269236516046968</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7300939876979362</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.717802621230143</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.689171871195264</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4752013278040788</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5978185140670496</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.792535392155702</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.533433538635522</v>
+        <v>-6.587599044927023</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5403117215156121</v>
+        <v>0.518645518999012</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.442080181507308</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.888793452379184</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.284433739951941</v>
+        <v>-6.338599246243442</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6528179822127034</v>
+        <v>0.6311517796961028</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1930803828237273</v>
+        <v>-0.2472458891152278</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.051099672812991</v>
+        <v>3.018600369038091</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.390023729725046</v>
+        <v>-6.444189236016546</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4826060567042427</v>
+        <v>0.4609398541876426</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2986703725968317</v>
+        <v>-0.3528358788883322</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.85976974934991</v>
+        <v>2.827270445575009</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.408758631843643</v>
+        <v>-6.435012982690885</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5236564377338904</v>
+        <v>0.5131546973949934</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.304266382256963</v>
+        <v>-0.342123850411942</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.904956485430917</v>
+        <v>2.88224200453793</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.260818590436044</v>
+        <v>-6.287072941283285</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4629535316087625</v>
+        <v>0.4524517912698656</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2839454663484054</v>
+        <v>-0.3218029345033844</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.797270112287884</v>
+        <v>2.774555631394897</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.207849068182055</v>
+        <v>-6.234103419029297</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4754273542568797</v>
+        <v>0.4649256139179831</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.2688334122493956</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.820337839386799</v>
+        <v>2.797623358493812</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.164300661411365</v>
+        <v>-6.190555012258606</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4858861048700627</v>
+        <v>0.4753843645311662</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.2688334122493956</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.813377227291706</v>
+        <v>2.790662746398719</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.130937454932596</v>
+        <v>-6.157191805779838</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5136937418427134</v>
+        <v>0.5031920015038165</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.2688334122493956</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.827839581672849</v>
+        <v>2.805125100779862</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.022678317810074</v>
+        <v>-6.048932668657316</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5515295171509171</v>
+        <v>0.5410277768120202</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2309759440944165</v>
+        <v>-0.2688334122493956</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.822371702132044</v>
+        <v>2.799657221239057</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.899387182992943</v>
+        <v>-5.925641533840185</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5983440650883463</v>
+        <v>0.5878423247494498</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.107684809277286</v>
+        <v>-0.1455422774322651</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.893844477032899</v>
+        <v>2.871129996139912</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.8782379840895</v>
+        <v>-5.904492334936742</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6145047228870486</v>
+        <v>0.6040029825481521</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.08653561037384266</v>
+        <v>-0.1243930785288217</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.914234974612291</v>
+        <v>2.891520493719304</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.634472542106056</v>
+        <v>-5.660726892953297</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7077916080274771</v>
+        <v>0.6972898676885806</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.08653561037384266</v>
+        <v>-0.1243930785288217</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.910015682959342</v>
+        <v>2.887301202066354</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532709721828761</v>
+        <v>-5.558964072676003</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.750621050058411</v>
+        <v>0.7401193097195145</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.07331654198141396</v>
+        <v>-0.111174010136393</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.920071437914815</v>
+        <v>2.897356957021827</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282859327879686</v>
+        <v>-5.53717257051686</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.843303282621743</v>
+        <v>0.7415779855668738</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.07331654198141396</v>
+        <v>-0.111174010136393</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.912813512898517</v>
+        <v>2.89009903200553</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.106967235412254</v>
+        <v>-5.361280478049427</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9172592431293647</v>
+        <v>0.8155339460744959</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.07331654198141396</v>
+        <v>-0.111174010136393</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.916412636419166</v>
+        <v>2.893698155526178</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935520772389791</v>
+        <v>-5.189834015026963</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9991653343929037</v>
+        <v>0.8974400373380349</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.09812992104104917</v>
+        <v>0.06027245288607014</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.032608020287197</v>
+        <v>3.00989353939421</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.861231206651452</v>
+        <v>-5.115544449288624</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.027901638304536</v>
+        <v>0.9261763412496675</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1724194867793885</v>
+        <v>0.1345620186244094</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.076202237346497</v>
+        <v>3.05348775645351</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.797595464417517</v>
+        <v>-5.05190870705469</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.058050736252427</v>
+        <v>0.9563254391975584</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.236055229013323</v>
+        <v>0.198197760858344</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.119078483741176</v>
+        <v>3.096364002848188</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.686168705091597</v>
+        <v>-4.940481947728769</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.083815698766591</v>
+        <v>0.9820904017117222</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.236055229013323</v>
+        <v>0.198197760858344</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.100272742524971</v>
+        <v>3.077558261631984</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.445738208286737</v>
+        <v>-4.700051450923909</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.181730974113413</v>
+        <v>1.080005677058544</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4764857258181833</v>
+        <v>0.4386282576632042</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.246274117232765</v>
+        <v>3.223559636339777</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.373495640115542</v>
+        <v>-4.627808882752714</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.214557315216711</v>
+        <v>1.112832018161842</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4764857258181833</v>
+        <v>0.4386282576632042</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.250203431067585</v>
+        <v>3.227488950174598</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.355781953237677</v>
+        <v>-4.610095195874849</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.222321373885197</v>
+        <v>1.120596076830328</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4796670547151001</v>
+        <v>0.441809586560121</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.252790812323075</v>
+        <v>3.230076331430088</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.24697706775795</v>
+        <v>-4.501290310395122</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.262841399297081</v>
+        <v>1.161116102242212</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4796670547151001</v>
+        <v>0.441809586560121</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.249788883543069</v>
+        <v>3.227074402650081</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.026956269720939</v>
+        <v>-4.281269512358111</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.352428755522499</v>
+        <v>1.250703458467631</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6208868997830803</v>
+        <v>0.5830294316281013</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.336099827594471</v>
+        <v>3.313385346701483</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.894088580657661</v>
+        <v>-4.148401823294834</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.421470013949634</v>
+        <v>1.319744716894765</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6208868997830803</v>
+        <v>0.5830294316281013</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.351994010396294</v>
+        <v>3.329279529503307</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.773915497293162</v>
+        <v>-4.028228739930335</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.470685091735735</v>
+        <v>1.368959794680866</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7410599831475793</v>
+        <v>0.7032025149926002</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.425243704855296</v>
+        <v>3.402529223962308</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.629243352193424</v>
+        <v>-3.883556594830598</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.538642052337071</v>
+        <v>1.436916755282201</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8857321282473167</v>
+        <v>0.8478746600923377</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.522135094476578</v>
+        <v>3.49942061358359</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.689118179551117</v>
+        <v>-3.94343142218829</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.500729612795419</v>
+        <v>1.39900431574055</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8258573008896246</v>
+        <v>0.7879998327346456</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.472247689463388</v>
+        <v>3.449533208570401</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.569297948640279</v>
+        <v>-3.823611191277453</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.563946874393963</v>
+        <v>1.462221577339093</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8258573008896246</v>
+        <v>0.7879998327346456</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.487536858697597</v>
+        <v>3.46482237780461</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.571767655102085</v>
+        <v>-3.826080897739259</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.470603191131682</v>
+        <v>1.368877894076813</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8233875944278184</v>
+        <v>0.7855301262728394</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.393699234142955</v>
+        <v>3.370984753249967</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.640137841426095</v>
+        <v>-3.894451084063268</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.362516978087379</v>
+        <v>1.26079168103251</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7948058253090543</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.318526515049985</v>
+        <v>3.295812034156998</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.653925894273142</v>
+        <v>-3.908239136910315</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.347438465580452</v>
+        <v>1.245713168525583</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7948058253090543</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.308963223681876</v>
+        <v>3.286248742788889</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.709445970165731</v>
+        <v>-3.963759212802905</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.462261271915619</v>
+        <v>1.360535974860749</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7948058253090543</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.445994060374079</v>
+        <v>3.423279579481092</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.533971710373262</v>
+        <v>-3.788284953010435</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.537018207824394</v>
+        <v>1.435292910769525</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7948058253090543</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.450561292365867</v>
+        <v>3.427846811472879</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.644907963014511</v>
+        <v>-3.899221205651684</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.468385735529102</v>
+        <v>1.366660438474232</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8326632934640333</v>
+        <v>0.7948058253090543</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.426303321127074</v>
+        <v>3.403588840234086</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.611244417542229</v>
+        <v>-3.865557660179402</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.410389467119464</v>
+        <v>1.308664170064595</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8663268389363152</v>
+        <v>0.8284693707813362</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.375039761811892</v>
+        <v>3.352325280918905</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.551391798338506</v>
+        <v>-3.805705040975679</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.444502901233086</v>
+        <v>1.342777604178217</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8663268389363152</v>
+        <v>0.8284693707813362</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.385212148244025</v>
+        <v>3.362497667351037</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.465148335312128</v>
+        <v>-3.719461577949302</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.473946557017497</v>
+        <v>1.372221259962628</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8663268389363152</v>
+        <v>0.8284693707813362</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.380158418817885</v>
+        <v>3.357443937924898</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.510455154711108</v>
+        <v>-3.764768397348282</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.447599604702431</v>
+        <v>1.345874307647561</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8255166759270844</v>
+        <v>0.7876592077721054</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.347448096456872</v>
+        <v>3.324733615563885</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.53948825941341</v>
+        <v>-3.793801502050583</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.436538235854612</v>
+        <v>1.334812938799742</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8255166759270844</v>
+        <v>0.7876592077721054</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.347999969489974</v>
+        <v>3.325285488596986</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.446677777962551</v>
+        <v>-3.700991020599724</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.402935120326321</v>
+        <v>1.301209823271452</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9183271573779438</v>
+        <v>0.8804696892229648</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.332958950251855</v>
+        <v>3.310244469358868</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.491067247291978</v>
+        <v>-3.745380489929151</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.387052808519151</v>
+        <v>1.285327511464281</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8739376880485161</v>
+        <v>0.8360802198935371</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.308198744578799</v>
+        <v>3.285484263685812</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.607608852397321</v>
+        <v>-3.861922095034494</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.335511874988737</v>
+        <v>1.233786577933867</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7573960829431734</v>
+        <v>0.7195386147881944</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.233349490027317</v>
+        <v>3.210635009134329</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.495231851214649</v>
+        <v>-3.749545093851822</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.385953971292473</v>
+        <v>1.284228674237604</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7573960829431734</v>
+        <v>0.7195386147881944</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.238840785857984</v>
+        <v>3.216126304964996</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.523012249116002</v>
+        <v>-3.777325491753175</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.386339013900471</v>
+        <v>1.284613716845601</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7296156850418203</v>
+        <v>0.6917582168868412</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.233669748885711</v>
+        <v>3.210955267992724</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.64139292184614</v>
+        <v>-3.895706164483313</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.177342464809069</v>
+        <v>1.075617167754199</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6623978328908441</v>
+        <v>0.6245403647358651</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.031694757595778</v>
+        <v>3.008980276702791</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.750007000289471</v>
+        <v>-4.004320242926644</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.254046494150942</v>
+        <v>1.152321197096073</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6623978328908441</v>
+        <v>0.6245403647358651</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.151844418314984</v>
+        <v>3.129129937421997</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.714597962041328</v>
+        <v>-3.968911204678501</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.282723135552522</v>
+        <v>1.180997838497653</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6623978328908441</v>
+        <v>0.6245403647358651</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.166357444417307</v>
+        <v>3.14364296352432</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.676214299483177</v>
+        <v>-3.93052754212035</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.295496041918151</v>
+        <v>1.193770744863282</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7007814954489953</v>
+        <v>0.6629240272940162</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.186807083294567</v>
+        <v>3.164092602401579</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.499097969448011</v>
+        <v>-3.753411212085184</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.363071602777519</v>
+        <v>1.26134630572265</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7007814954489953</v>
+        <v>0.6629240272940162</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.183536112139869</v>
+        <v>3.160821631246881</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.544190214281556</v>
+        <v>-3.798503456918729</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.345718096606014</v>
+        <v>1.243992799551145</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6388854522796055</v>
+        <v>0.6010279841246264</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.147081878000148</v>
+        <v>3.12436739710716</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.364814793042789</v>
+        <v>-3.619128035679962</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.411255240407936</v>
+        <v>1.309529943353066</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7956622104503241</v>
+        <v>0.7578047422953451</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.234934908208993</v>
+        <v>3.212220427316006</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.409829006563395</v>
+        <v>-3.664142249200568</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.374057010331283</v>
+        <v>1.272331713276414</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7653133151357195</v>
+        <v>0.7274558469807405</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.19753302635182</v>
+        <v>3.174818545458833</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.67683351683583</v>
+        <v>-3.931146759473003</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.272946768561255</v>
+        <v>1.171221471506385</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.570950277092771</v>
+        <v>0.533092808937792</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.086606765864997</v>
+        <v>3.06389228497201</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.778031298273003</v>
+        <v>-4.032344540910175</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.231671577882887</v>
+        <v>1.129946280828018</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5025414635474519</v>
+        <v>0.4646839953924728</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.044765399634307</v>
+        <v>3.02205091874132</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.77152033165869</v>
+        <v>-4.025833574295863</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.231875926082929</v>
+        <v>1.130150629028059</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5025414635474519</v>
+        <v>0.4646839953924728</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.042365361188624</v>
+        <v>3.019650880295636</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.752482203951393</v>
+        <v>-4.006795446588566</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.236015896374093</v>
+        <v>1.134290599319223</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4443578522162573</v>
+        <v>0.4065003840612783</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.003979913598152</v>
+        <v>2.981265432705165</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.783608835102011</v>
+        <v>-4.037922077739184</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.342859645548036</v>
+        <v>1.241134348493166</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4443578522162573</v>
+        <v>0.4065003840612783</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.123274315232342</v>
+        <v>3.100559834339355</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.937917782735934</v>
+        <v>-4.051788839073102</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.2819693954806</v>
+        <v>1.236420972945733</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3899772709027647</v>
+        <v>0.3686424673274553</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.09147929543038</v>
+        <v>3.078678413285195</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.893113611196004</v>
+        <v>-4.006984667533172</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.305899594493498</v>
+        <v>1.260351171958631</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3899772709027647</v>
+        <v>0.3686424673274553</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.097487825827306</v>
+        <v>3.08468694368212</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.745370640961001</v>
+        <v>-3.85924169729817</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.262947003864699</v>
+        <v>1.217398581329831</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5577846281376478</v>
+        <v>0.5364498245623385</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.096122461445435</v>
+        <v>3.08332157930025</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.847385323492222</v>
+        <v>-3.961256379829391</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.224934752383691</v>
+        <v>1.179386329848824</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5577846281376478</v>
+        <v>0.5364498245623385</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.098916082976916</v>
+        <v>3.086115200831731</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.841232617439438</v>
+        <v>-3.955103673776606</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.228058183196463</v>
+        <v>1.182509760661596</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5639373341904321</v>
+        <v>0.5426025306151228</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.103270055000245</v>
+        <v>3.09046917285506</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.858041915589939</v>
+        <v>-3.971912971927108</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.220414940676373</v>
+        <v>1.174866518141505</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5471280360399304</v>
+        <v>0.5257932324646211</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.092264952850055</v>
+        <v>3.079464070704869</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.795743916813818</v>
+        <v>-3.909614973150986</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.311669693983643</v>
+        <v>1.266121271448775</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5471280360399304</v>
+        <v>0.5257932324646211</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.158600506646875</v>
+        <v>3.14579962450169</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.59395371914866</v>
+        <v>-3.707824775485828</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.194677774763833</v>
+        <v>1.149129352228965</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7451462282090848</v>
+        <v>0.7238114246337755</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.079703423662495</v>
+        <v>3.066902541517309</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.644840431834854</v>
+        <v>-3.758711488172023</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.24461332201153</v>
+        <v>1.199064899476663</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6942595155228903</v>
+        <v>0.672924711947581</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.119461628372954</v>
+        <v>3.106660746227768</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.742580976459829</v>
+        <v>-3.856452032796997</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.220144840277584</v>
+        <v>1.174596417742716</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6783702373899101</v>
+        <v>0.6570354338146007</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.124555797609209</v>
+        <v>3.111754915464024</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.802790274465113</v>
+        <v>-3.916661330802282</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.194597101900142</v>
+        <v>1.149048679365274</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6181609393846256</v>
+        <v>0.5968261358093162</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.08696619963071</v>
+        <v>3.074165317485524</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.726368228033186</v>
+        <v>-3.840239284370355</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.223657538512841</v>
+        <v>1.178109115977974</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6181609393846256</v>
+        <v>0.5968261358093162</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.085457817670639</v>
+        <v>3.072656935525453</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.681995096394618</v>
+        <v>-3.795866152731786</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.241269658603705</v>
+        <v>1.195721236068837</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6625340710231942</v>
+        <v>0.6411992674478848</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.111944564089216</v>
+        <v>3.09914368194403</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.704475447253503</v>
+        <v>-3.818346503590671</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.226671312398742</v>
+        <v>1.181122889863874</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6625340710231942</v>
+        <v>0.6411992674478848</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.106338358227807</v>
+        <v>3.093537476082621</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.656819716692447</v>
+        <v>-3.770690773029616</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.252115361650968</v>
+        <v>1.206566939116101</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7101898015842498</v>
+        <v>0.6888549980089405</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.141313553592245</v>
+        <v>3.128512671447059</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.556301558193693</v>
+        <v>-3.670172614530861</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.297214998425195</v>
+        <v>1.251666575890327</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8107079600830044</v>
+        <v>0.789373156507695</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.206516822066222</v>
+        <v>3.193715939921037</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.616968148596082</v>
+        <v>-3.73083920493325</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.259703034740112</v>
+        <v>1.214154612205244</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7290096433644707</v>
+        <v>0.7076748397891613</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.144252504510974</v>
+        <v>3.131451622365788</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.572129746987684</v>
+        <v>-3.686000803324852</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.281736097994099</v>
+        <v>1.236187675459232</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7335530763093402</v>
+        <v>0.7122182727340308</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.151076266888524</v>
+        <v>3.138275384743339</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.591628203229692</v>
+        <v>-3.70549925956686</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.278097655128374</v>
+        <v>1.232549232593506</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6854684350294359</v>
+        <v>0.6641336314541265</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.12638642175166</v>
+        <v>3.113585539606474</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.547425366143791</v>
+        <v>-3.66129642248096</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.301658392490571</v>
+        <v>1.256109969955704</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7296712721153363</v>
+        <v>0.708336468540027</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.158787726531037</v>
+        <v>3.145986844385852</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.584404393807235</v>
+        <v>-3.698275450144403</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.285276781894442</v>
+        <v>1.239728359359574</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7666451739066669</v>
+        <v>0.7453103703313575</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.179382068075083</v>
+        <v>3.166581185929898</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.426112976267962</v>
+        <v>-3.539984032605131</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.39984111409319</v>
+        <v>1.354292691558323</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7666451739066669</v>
+        <v>0.7453103703313575</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.230629833258123</v>
+        <v>3.217828951112937</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321016</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.218470972633486</v>
+        <v>-3.332342028970654</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.481338620141234</v>
+        <v>1.435790197606366</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.974287177541143</v>
+        <v>0.9529523739658337</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.353655740033062</v>
+        <v>3.340854857887876</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.167438879910958</v>
+        <v>-3.281309936248126</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.496699685468515</v>
+        <v>1.451151262933647</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.025319270263671</v>
+        <v>1.003984466688362</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.379223223904849</v>
+        <v>3.366422341759663</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.102214698783753</v>
+        <v>-3.216085755120921</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.539976762012102</v>
+        <v>1.494428339477234</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.090543451390877</v>
+        <v>1.069208647815567</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.435545136673877</v>
+        <v>3.422744254528691</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.064787678712619</v>
+        <v>-3.178658735049787</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.550908542339836</v>
+        <v>1.505360119804968</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.095794989420058</v>
+        <v>1.074460185844749</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.434657031790666</v>
+        <v>3.42185614964548</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.084899334747327</v>
+        <v>-3.198770391084496</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.544120672257193</v>
+        <v>1.498572249722325</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.106822334417478</v>
+        <v>1.085487530842168</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.442530231120358</v>
+        <v>3.429729348975172</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563628</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.031154520320122</v>
+        <v>-3.145025576657291</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.726176369049286</v>
+        <v>1.680627946514418</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.11688564385794</v>
+        <v>1.09555084028263</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.609125987805846</v>
+        <v>3.59632510566066</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957619</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.95637225929511</v>
+        <v>-3.070243315632278</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.876202182677108</v>
+        <v>1.83065376014224</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.191667904882952</v>
+        <v>1.170333101307643</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.774108253638671</v>
+        <v>3.761307371493485</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.930288175031302</v>
+        <v>-3.04415923136847</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.87834379239649</v>
+        <v>1.832795369861622</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.191667904882952</v>
+        <v>1.170333101307643</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.76581622965253</v>
+        <v>3.753015347507344</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896923</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.852156994182355</v>
+        <v>-2.966028050519523</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.907789460319848</v>
+        <v>1.862241037784981</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.265844715766637</v>
+        <v>1.244509912191328</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.80851551176652</v>
+        <v>3.795714629621334</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.843264532789072</v>
+        <v>-2.95713558912624</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.928900850603953</v>
+        <v>1.883352428069085</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.265844715766637</v>
+        <v>1.244509912191328</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.826069917493311</v>
+        <v>3.813269035348126</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.01174064975895</v>
+        <v>-3.125611706096118</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.853365451220586</v>
+        <v>1.807817028685718</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.237896880050056</v>
+        <v>1.216562076474747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.801156263467947</v>
+        <v>3.788355381322762</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782701</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.313941120897367</v>
+        <v>-2.427812177234535</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.113754959953081</v>
+        <v>2.068206537418213</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.167548820679646</v>
+        <v>1.146214017104336</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.740217125033563</v>
+        <v>3.727416242888377</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.291220017214214</v>
+        <v>-2.405091073551382</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.113507423923247</v>
+        <v>2.067959001388379</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.167548820679646</v>
+        <v>1.146214017104336</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.730881147530467</v>
+        <v>3.718080265385281</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.420421830508257</v>
+        <v>-2.534292886845425</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.220732824456799</v>
+        <v>2.175184401921931</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.038347007385603</v>
+        <v>1.017012203810294</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.81226618540521</v>
+        <v>3.799465303260025</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.575202837286512</v>
+        <v>-2.68907389362368</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.195898244239143</v>
+        <v>2.150349821704275</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.004979333331127</v>
+        <v>0.9836445297558178</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.829323403466172</v>
+        <v>3.816522521320986</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799958</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.568148147071339</v>
+        <v>-2.682019203408507</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.195395476314757</v>
+        <v>2.14984705377989</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.012034023546301</v>
+        <v>0.9906992199709916</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.830231573584821</v>
+        <v>3.817430691439635</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.541196922744851</v>
+        <v>-2.655067979082019</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.216182119690094</v>
+        <v>2.170633697155226</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.02691436957402</v>
+        <v>1.005579565998711</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.849165934846194</v>
+        <v>3.836365052701008</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.677149930801167</v>
+        <v>-2.791020987138335</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.345904048612527</v>
+        <v>2.30035562607766</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.02691436957402</v>
+        <v>1.005579565998711</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.033269066991154</v>
+        <v>4.020468184845968</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.699558048606039</v>
+        <v>-2.813429104943207</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.329057496393572</v>
+        <v>2.283509073858704</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.02691436957402</v>
+        <v>1.005579565998711</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.025385761894147</v>
+        <v>4.012584879748961</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.847563816085438</v>
+        <v>-2.961434872422607</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.271909188951449</v>
+        <v>2.226360766416581</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9401873607104787</v>
+        <v>0.9188525571351693</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.975403556125659</v>
+        <v>3.962602673980474</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.857004741973968</v>
+        <v>-2.970875798311137</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.324386536317885</v>
+        <v>2.278838113783017</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.06261447825387</v>
+        <v>1.041279674678561</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.105113544373541</v>
+        <v>4.092312662228355</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.90927834930961</v>
+        <v>-3.023149405646778</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.306368187928929</v>
+        <v>2.260819765394061</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.010340870918229</v>
+        <v>0.9890060673429195</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.076640474517458</v>
+        <v>4.063839592372272</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.985608326910516</v>
+        <v>-3.099479383247684</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.273948009782342</v>
+        <v>2.228399587247474</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.010340870918229</v>
+        <v>0.9890060673429195</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.074752287411233</v>
+        <v>4.061951405266047</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.187862047234869</v>
+        <v>-3.301733103572037</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.187866751255463</v>
+        <v>2.142318328720595</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8080871505938754</v>
+        <v>0.786752347018566</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.948220284819483</v>
+        <v>3.935419402674297</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343059</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.349430472762124</v>
+        <v>-3.463301529099292</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.121673391254713</v>
+        <v>2.076124968719845</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.681304226795996</v>
+        <v>0.6599694232206866</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.870584540750908</v>
+        <v>3.857783658605722</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647099</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.481731764859677</v>
+        <v>-3.595602821196846</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.08182628128161</v>
+        <v>2.036277858746742</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.681304226795996</v>
+        <v>0.6599694232206866</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.883657947616826</v>
+        <v>3.870857065471641</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763527</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.483293407674537</v>
+        <v>-3.597164464011706</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.081201624155666</v>
+        <v>2.035653201620798</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.681304226795996</v>
+        <v>0.6599694232206866</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.883657947616826</v>
+        <v>3.870857065471641</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392114</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.51119419478401</v>
+        <v>-3.625065251121179</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.068565350438879</v>
+        <v>2.023016927904012</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6467073026530612</v>
+        <v>0.6253724990777518</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.861423834258067</v>
+        <v>3.848622952112882</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172521</v>
+        <v>3.684909939172525</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.633720297486904</v>
+        <v>-3.747591353824073</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.01631935333492</v>
+        <v>1.970770930800053</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5241811999501673</v>
+        <v>0.502846396374858</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.78467261661353</v>
+        <v>3.771871734468344</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971073</v>
+        <v>3.619362241971076</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.864234793672493</v>
+        <v>-3.978105850009661</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.990819514451188</v>
+        <v>1.945271091916321</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2936667037645786</v>
+        <v>0.2723319001892692</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.71306987849268</v>
+        <v>3.700268996347495</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.6407642481998</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.120955611667316</v>
+        <v>-4.234826668004485</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.028442906255106</v>
+        <v>1.982894483720238</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1852521296207638</v>
+        <v>0.1639173260454544</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.788332853008238</v>
+        <v>3.775531970863053</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66830316462223</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.274942029443457</v>
+        <v>-4.388813085780625</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.03582860829029</v>
+        <v>1.990280185755422</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1852521296207638</v>
+        <v>0.1639173260454544</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.857313122153878</v>
+        <v>3.844512240008693</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808523</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.224420125615791</v>
+        <v>-4.338291181952959</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.042088571941477</v>
+        <v>1.996540149406609</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1852521296207638</v>
+        <v>0.1639173260454544</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.843364324273999</v>
+        <v>3.830563442128814</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994888</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.476895279623515</v>
+        <v>-4.590766335960684</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.952968999393801</v>
+        <v>1.907420576858934</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1852521296207638</v>
+        <v>0.1639173260454544</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.855234813329413</v>
+        <v>3.842433931184228</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358292</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.746368081545223</v>
+        <v>-4.860239137882392</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.846390413144062</v>
+        <v>1.800841990609194</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1852521296207638</v>
+        <v>0.1639173260454544</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.856445347848357</v>
+        <v>3.843644465703171</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637081</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.903912153274665</v>
+        <v>-5.017783209611833</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.787494526679607</v>
+        <v>1.741946104144739</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1183503244804893</v>
+        <v>0.0970155209051799</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.820426006991513</v>
+        <v>3.807625124846328</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301338</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.181876548857939</v>
+        <v>-5.295747605195107</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.671386621182486</v>
+        <v>1.625838198647619</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.02873059019500501</v>
+        <v>0.007395786619695643</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.761732019156412</v>
+        <v>3.748931137011227</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215464</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.29884424149683</v>
+        <v>-5.412715297833998</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.786803600825974</v>
+        <v>1.741255178291107</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.02873059019500501</v>
+        <v>0.007395786619695643</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923936075855456</v>
+        <v>3.911135193710271</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456686</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.383562183717783</v>
+        <v>-5.497433240054951</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.747763061901407</v>
+        <v>1.702214639366539</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.05638543873304136</v>
+        <v>-0.07772024230835073</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.867713096462443</v>
+        <v>3.854912214317257</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253281</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.465497001986666</v>
+        <v>-5.579368058323834</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.725218552162345</v>
+        <v>1.679670129627477</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.06632018432012154</v>
+        <v>-0.08765498789543091</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.871981666678686</v>
+        <v>3.8591807845335</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717826</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.411758828586404</v>
+        <v>-5.525629884923572</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.755639459978352</v>
+        <v>1.710091037443485</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.01258201091985944</v>
+        <v>-0.03391681449516881</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.913150209174746</v>
+        <v>3.90034932702956</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616943</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.301752545109182</v>
+        <v>-5.415623601446351</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.791794860613416</v>
+        <v>1.746246438078549</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01062256099741576</v>
+        <v>-0.0107122425778936</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.919225839569286</v>
+        <v>3.9064249574241</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.158692969368257</v>
+        <v>-5.272564025705425</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.853268701631761</v>
+        <v>1.807720279096893</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.01863598758739504</v>
+        <v>-0.002698815987914327</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.928283906245248</v>
+        <v>3.915483024100062</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436923</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.857246243896419</v>
+        <v>-4.971117300233588</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.981108274703032</v>
+        <v>1.935559852168164</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3200827130592323</v>
+        <v>0.2987479094839229</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.116412824410887</v>
+        <v>4.103611942265701</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064762</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.881836488131603</v>
+        <v>-4.995707544468772</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.972243354761668</v>
+        <v>1.926694932226801</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3200827130592323</v>
+        <v>0.2987479094839229</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.117384002163597</v>
+        <v>4.104583120018411</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859295</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.830798112125083</v>
+        <v>-5.00885640385705</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.993501609544032</v>
+        <v>1.922278292851245</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3200827130592323</v>
+        <v>0.2987479094839229</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.118226906543352</v>
+        <v>4.105426024398167</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354679</v>
+        <v>3.831748677354683</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.789658817258452</v>
+        <v>-4.967717108990419</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.02899542636483</v>
+        <v>1.957772109672042</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3612220079258631</v>
+        <v>0.3398872043505538</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.161948582337476</v>
+        <v>4.14914770019229</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085615</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.67905267717885</v>
+        <v>-4.857110968910817</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.889421878520605</v>
+        <v>1.818198561827818</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4718281480054651</v>
+        <v>0.4504933444301558</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.044496262509171</v>
+        <v>4.031695380363987</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462777</v>
+        <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.809633411709693</v>
+        <v>-4.987691703441659</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.840691628782232</v>
+        <v>1.769468312089445</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3412474134746226</v>
+        <v>0.3199126098993132</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.96964986586463</v>
+        <v>3.956848983719444</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218594</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.645137077518731</v>
+        <v>-4.823195369250698</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.890916981534699</v>
+        <v>1.819693664841912</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3412474134746226</v>
+        <v>0.3199126098993132</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.954076684940713</v>
+        <v>3.941275802795527</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462765</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.52065659679478</v>
+        <v>-4.698714888526746</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.939896884260709</v>
+        <v>1.868673567567922</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3412474134746226</v>
+        <v>0.3199126098993132</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.953264395377142</v>
+        <v>3.940463513231957</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533051</v>
+        <v>3.832321184533057</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.531041791684669</v>
+        <v>-4.709100083416636</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.945611585429826</v>
+        <v>1.874388268737039</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3308622185847333</v>
+        <v>0.3095274150094239</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.956902057568281</v>
+        <v>3.944101175423095</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.80645021107204</v>
+        <v>3.733984935921557</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.697173450686591</v>
+        <v>3.721537833460863</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.531041791684669</v>
+        <v>-4.709100083416636</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.945611585429826</v>
+        <v>1.874388268737039</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3308622185847333</v>
+        <v>0.3095274150094239</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.690237247672958</v>
+        <v>3.714601630447231</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>126.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.4%</t>
+          <t>455.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.5%</t>
+          <t>-633.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-188.8%</t>
+          <t>-189.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-188.7%</t>
+          <t>-185.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-193.0%</t>
+          <t>-194.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-67.4%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.059545177891552</v>
+        <v>-9.048567729753833</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4416573866374249</v>
+        <v>-0.4372664073823369</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.73704908697911</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.140287656645477</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.987412002603671</v>
+        <v>-8.976434554465952</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4070704122836357</v>
+        <v>-0.4026794330285481</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.73704908697911</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.146021360884114</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.916045609994024</v>
+        <v>-8.905068161856304</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3882611176336423</v>
+        <v>-0.3838701383785543</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.665682694369462</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.179103934056037</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.822586576008799</v>
+        <v>-8.81160912787108</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.36076098535246</v>
+        <v>-0.356370006097372</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.665682694369462</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.16922045274313</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.555344775140401</v>
+        <v>-8.544367327002682</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2556988255044748</v>
+        <v>-0.2513078462493867</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.665682694369462</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.167385892243756</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.457437736463911</v>
+        <v>-8.446460288326191</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2168363250073391</v>
+        <v>-0.2124453457522515</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.597696944508906</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.207877027186629</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.433484195487953</v>
+        <v>-8.422506747350234</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2065864024714625</v>
+        <v>-0.2021954232163745</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.573743403532949</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.222917657917697</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.169424257165156</v>
+        <v>-8.158446809027437</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1142227433040959</v>
+        <v>-0.1098317640490079</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.309683465210152</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.368093304749623</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.462344633660318</v>
+        <v>-7.451367185522598</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1658220724375385</v>
+        <v>0.1702130516926266</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.309683465210152</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.365306271089322</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.422160335294127</v>
+        <v>-7.411182887156408</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1822394156718561</v>
+        <v>0.1866303949269441</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.269499166843961</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.389760473996878</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.258760464354765</v>
+        <v>-7.247783016217046</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.246966185268358</v>
+        <v>0.251357164523446</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.106099295904599</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.487167217781252</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-7.014301793987447</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.3526740822531376</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8726180736750004</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.635180379956864</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-6.864635402979932</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.4096484283431847</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7797145824324645</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.688030264389426</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-6.732359929349045</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.4579261045425662</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6474391088015778</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.762763035314985</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.576621596789304</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.5230364982540996</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4917007762418363</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.859021095538467</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.327621798105723</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.6355427589511908</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2472458891152278</v>
+        <v>-0.2427009775582556</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.018600369038091</v>
+        <v>3.021327315972274</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.433211787878827</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.4653308334427302</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3528358788883322</v>
+        <v>-0.3482909673313599</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.827270445575009</v>
+        <v>2.829997392509193</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.435012982690885</v>
+        <v>-6.451946689997424</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5131546973949934</v>
+        <v>0.5063812144723778</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.342123850411942</v>
+        <v>-0.3538869769914912</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.88224200453793</v>
+        <v>2.8751841285902</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.287072941283285</v>
+        <v>-6.304006648589825</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4524517912698656</v>
+        <v>0.44567830834725</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3218029345033844</v>
+        <v>-0.3335660610829337</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.774555631394897</v>
+        <v>2.767497755447167</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.234103419029297</v>
+        <v>-6.251037126335836</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4649256139179831</v>
+        <v>0.4581521309953671</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2688334122493956</v>
+        <v>-0.2805965388289448</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.797623358493812</v>
+        <v>2.790565482546083</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.190555012258606</v>
+        <v>-6.207488719565146</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4753843645311662</v>
+        <v>0.4686108816085501</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2688334122493956</v>
+        <v>-0.2805965388289448</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.790662746398719</v>
+        <v>2.783604870450989</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.157191805779838</v>
+        <v>-6.174125513086377</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5031920015038165</v>
+        <v>0.4964185185812009</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2688334122493956</v>
+        <v>-0.2805965388289448</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.805125100779862</v>
+        <v>2.798067224832133</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.048932668657316</v>
+        <v>-6.065866375963855</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5410277768120202</v>
+        <v>0.5342542938894046</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2688334122493956</v>
+        <v>-0.2805965388289448</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.799657221239057</v>
+        <v>2.792599345291328</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.925641533840185</v>
+        <v>-5.942575241146725</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5878423247494498</v>
+        <v>0.5810688418268337</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1455422774322651</v>
+        <v>-0.1573054040118143</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.871129996139912</v>
+        <v>2.864072120192183</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.904492334936742</v>
+        <v>-5.921426042243281</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6040029825481521</v>
+        <v>0.5972294996255365</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1243930785288217</v>
+        <v>-0.136156205108371</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.891520493719304</v>
+        <v>2.884462617771574</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.660726892953297</v>
+        <v>-5.677660600259837</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6972898676885806</v>
+        <v>0.6905163847659646</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1243930785288217</v>
+        <v>-0.136156205108371</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.887301202066354</v>
+        <v>2.880243326118625</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.558964072676003</v>
+        <v>-5.575897779982542</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7401193097195145</v>
+        <v>0.7333458267968989</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.111174010136393</v>
+        <v>-0.1229371367159423</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.897356957021827</v>
+        <v>2.890299081074098</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.53717257051686</v>
+        <v>-5.326047386033467</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7415779855668738</v>
+        <v>0.8260280593602305</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.111174010136393</v>
+        <v>-0.1229371367159423</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.89009903200553</v>
+        <v>2.8830411560578</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.361280478049427</v>
+        <v>-5.150155293566035</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8155339460744959</v>
+        <v>0.8999840198678521</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.111174010136393</v>
+        <v>-0.1229371367159423</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.893698155526178</v>
+        <v>2.886640279578449</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.189834015026963</v>
+        <v>-4.978708830543572</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8974400373380349</v>
+        <v>0.9818901111313914</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.06027245288607014</v>
+        <v>0.04850932630652088</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.00989353939421</v>
+        <v>3.00283566344648</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.115544449288624</v>
+        <v>-4.904419264805233</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9261763412496675</v>
+        <v>1.010626415043024</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1345620186244094</v>
+        <v>0.1227988920448602</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.05348775645351</v>
+        <v>3.046429880505781</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.05190870705469</v>
+        <v>-4.840783522571298</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9563254391975584</v>
+        <v>1.040775512990915</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.198197760858344</v>
+        <v>0.1864346342787947</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.096364002848188</v>
+        <v>3.089306126900459</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.940481947728769</v>
+        <v>-4.729356763245378</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9820904017117222</v>
+        <v>1.066540475505079</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.198197760858344</v>
+        <v>0.1864346342787947</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.077558261631984</v>
+        <v>3.070500385684254</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.700051450923909</v>
+        <v>-4.488926266440518</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.080005677058544</v>
+        <v>1.1644557508519</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4386282576632042</v>
+        <v>0.426865131083655</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.223559636339777</v>
+        <v>3.216501760392048</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.627808882752714</v>
+        <v>-4.416683698269323</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.112832018161842</v>
+        <v>1.197282091955198</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4386282576632042</v>
+        <v>0.426865131083655</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.227488950174598</v>
+        <v>3.220431074226868</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.610095195874849</v>
+        <v>-4.398970011391458</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.120596076830328</v>
+        <v>1.205046150623684</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.441809586560121</v>
+        <v>0.4300464599805718</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.230076331430088</v>
+        <v>3.223018455482358</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.501290310395122</v>
+        <v>-4.290165125911731</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.161116102242212</v>
+        <v>1.245566176035569</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.441809586560121</v>
+        <v>0.4300464599805718</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.227074402650081</v>
+        <v>3.220016526702352</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.281269512358111</v>
+        <v>-4.07014432787472</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.250703458467631</v>
+        <v>1.335153532260987</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5830294316281013</v>
+        <v>0.571266305048552</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.313385346701483</v>
+        <v>3.306327470753754</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.148401823294834</v>
+        <v>-3.937276638811442</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.319744716894765</v>
+        <v>1.404194790688122</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5830294316281013</v>
+        <v>0.571266305048552</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.329279529503307</v>
+        <v>3.322221653555577</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.028228739930335</v>
+        <v>-3.817103555446943</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.368959794680866</v>
+        <v>1.453409868474223</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7032025149926002</v>
+        <v>0.691439388413051</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.402529223962308</v>
+        <v>3.395471348014579</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.883556594830598</v>
+        <v>-3.672431410347206</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.436916755282201</v>
+        <v>1.521366829075558</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8478746600923377</v>
+        <v>0.8361115335127884</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.49942061358359</v>
+        <v>3.492362737635861</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.94343142218829</v>
+        <v>-3.732306237704898</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.39900431574055</v>
+        <v>1.483454389533907</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7879998327346456</v>
+        <v>0.7762367061550963</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.449533208570401</v>
+        <v>3.442475332622672</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.823611191277453</v>
+        <v>-3.612486006794061</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.462221577339093</v>
+        <v>1.54667165113245</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7879998327346456</v>
+        <v>0.7762367061550963</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.46482237780461</v>
+        <v>3.45776450185688</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.826080897739259</v>
+        <v>-3.614955713255867</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.368877894076813</v>
+        <v>1.45332796787017</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7855301262728394</v>
+        <v>0.7737669996932901</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.370984753249967</v>
+        <v>3.363926877302238</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.894451084063268</v>
+        <v>-3.683325899579876</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.26079168103251</v>
+        <v>1.345241754825867</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7948058253090543</v>
+        <v>0.783042698729505</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.295812034156998</v>
+        <v>3.288754158209268</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.908239136910315</v>
+        <v>-3.845443447525637</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.245713168525583</v>
+        <v>1.270831444279454</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7948058253090543</v>
+        <v>0.783042698729505</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.286248742788889</v>
+        <v>3.27919086684116</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.963759212802905</v>
+        <v>-3.900963523418226</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.360535974860749</v>
+        <v>1.385654250614621</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7948058253090543</v>
+        <v>0.783042698729505</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.423279579481092</v>
+        <v>3.416221703533362</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.788284953010435</v>
+        <v>-3.725489263625757</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.435292910769525</v>
+        <v>1.460411186523396</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7948058253090543</v>
+        <v>0.783042698729505</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.427846811472879</v>
+        <v>3.42078893552515</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.899221205651684</v>
+        <v>-3.836425516267006</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.366660438474232</v>
+        <v>1.391778714228104</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7948058253090543</v>
+        <v>0.783042698729505</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.403588840234086</v>
+        <v>3.396530964286357</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.865557660179402</v>
+        <v>-3.802761970794724</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.308664170064595</v>
+        <v>1.333782445818466</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8284693707813362</v>
+        <v>0.8167062442017869</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.352325280918905</v>
+        <v>3.345267404971175</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.805705040975679</v>
+        <v>-3.742909351591001</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.342777604178217</v>
+        <v>1.367895879932088</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8284693707813362</v>
+        <v>0.8167062442017869</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.362497667351037</v>
+        <v>3.355439791403308</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.719461577949302</v>
+        <v>-3.656665888564623</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.372221259962628</v>
+        <v>1.397339535716499</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8284693707813362</v>
+        <v>0.8167062442017869</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.357443937924898</v>
+        <v>3.350386061977168</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.764768397348282</v>
+        <v>-3.701972707963603</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.345874307647561</v>
+        <v>1.370992583401433</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7876592077721054</v>
+        <v>0.7758960811925562</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.324733615563885</v>
+        <v>3.317675739616155</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.793801502050583</v>
+        <v>-3.731005812665904</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.334812938799742</v>
+        <v>1.359931214553614</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7876592077721054</v>
+        <v>0.7758960811925562</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.325285488596986</v>
+        <v>3.318227612649257</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.700991020599724</v>
+        <v>-3.638195331215045</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.301209823271452</v>
+        <v>1.326328099025323</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8804696892229648</v>
+        <v>0.8687065626434155</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.310244469358868</v>
+        <v>3.303186593411138</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.745380489929151</v>
+        <v>-3.682584800544473</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.285327511464281</v>
+        <v>1.310445787218153</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8360802198935371</v>
+        <v>0.8243170933139878</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.285484263685812</v>
+        <v>3.278426387738082</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.861922095034494</v>
+        <v>-3.799126405649816</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.233786577933867</v>
+        <v>1.258904853687739</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7195386147881944</v>
+        <v>0.7077754882086451</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.210635009134329</v>
+        <v>3.2035771331866</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.749545093851822</v>
+        <v>-3.686749404467143</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.284228674237604</v>
+        <v>1.309346949991475</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7195386147881944</v>
+        <v>0.7077754882086451</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.216126304964996</v>
+        <v>3.209068429017267</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777325491753175</v>
+        <v>-3.714529802368496</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.284613716845601</v>
+        <v>1.309731992599473</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6917582168868412</v>
+        <v>0.679995090307292</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.210955267992724</v>
+        <v>3.203897392044994</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.895706164483313</v>
+        <v>-3.832910475098635</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.075617167754199</v>
+        <v>1.100735443508071</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6245403647358651</v>
+        <v>0.6127772381563158</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.008980276702791</v>
+        <v>3.001922400755062</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.004320242926644</v>
+        <v>-3.941524553541966</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.152321197096073</v>
+        <v>1.177439472849944</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6245403647358651</v>
+        <v>0.6127772381563158</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.129129937421997</v>
+        <v>3.122072061474267</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.968911204678501</v>
+        <v>-3.906115515293823</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.180997838497653</v>
+        <v>1.206116114251524</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6245403647358651</v>
+        <v>0.6127772381563158</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.14364296352432</v>
+        <v>3.13658508757659</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.93052754212035</v>
+        <v>-3.867731852735672</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.193770744863282</v>
+        <v>1.218889020617153</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6629240272940162</v>
+        <v>0.651160900714467</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.164092602401579</v>
+        <v>3.15703472645385</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.753411212085184</v>
+        <v>-3.690615522700506</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.26134630572265</v>
+        <v>1.286464581476522</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6629240272940162</v>
+        <v>0.651160900714467</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.160821631246881</v>
+        <v>3.153763755299152</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.798503456918729</v>
+        <v>-3.735707767534051</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.243992799551145</v>
+        <v>1.269111075305017</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6010279841246264</v>
+        <v>0.5892648575450772</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.12436739710716</v>
+        <v>3.117309521159431</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.619128035679962</v>
+        <v>-3.556332346295283</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.309529943353066</v>
+        <v>1.334648219106938</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7578047422953451</v>
+        <v>0.7460416157157959</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.212220427316006</v>
+        <v>3.205162551368276</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.664142249200568</v>
+        <v>-3.60134655981589</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.272331713276414</v>
+        <v>1.297449989030285</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7274558469807405</v>
+        <v>0.7156927204011913</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.174818545458833</v>
+        <v>3.167760669511103</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.931146759473003</v>
+        <v>-3.868351070088325</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.171221471506385</v>
+        <v>1.196339747260257</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.533092808937792</v>
+        <v>0.5213296823582427</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.06389228497201</v>
+        <v>3.05683440902428</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.032344540910175</v>
+        <v>-3.969548851525498</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.129946280828018</v>
+        <v>1.155064556581889</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4646839953924728</v>
+        <v>0.4529208688129235</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.02205091874132</v>
+        <v>3.01499304279359</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.025833574295863</v>
+        <v>-3.963037884911185</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.130150629028059</v>
+        <v>1.155268904781931</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4646839953924728</v>
+        <v>0.4529208688129235</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.019650880295636</v>
+        <v>3.012593004347907</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.006795446588566</v>
+        <v>-3.943999757203888</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.134290599319223</v>
+        <v>1.159408875073095</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4065003840612783</v>
+        <v>0.394737257481729</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.981265432705165</v>
+        <v>2.974207556757435</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.037922077739184</v>
+        <v>-3.975126388354506</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.241134348493166</v>
+        <v>1.266252624247038</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4065003840612783</v>
+        <v>0.394737257481729</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.100559834339355</v>
+        <v>3.093501958391625</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.051788839073102</v>
+        <v>-3.988993149688423</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.236420972945733</v>
+        <v>1.261539248699604</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3686424673274553</v>
+        <v>0.3568793407479061</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.078678413285195</v>
+        <v>3.071620537337465</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.006984667533172</v>
+        <v>-4.082857639744916</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.260351171958631</v>
+        <v>1.230001983073933</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3686424673274553</v>
+        <v>0.3568793407479061</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.08468694368212</v>
+        <v>3.077629067734391</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.85924169729817</v>
+        <v>-3.935114669509914</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.217398581329831</v>
+        <v>1.187049392445134</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5364498245623385</v>
+        <v>0.5246866979827892</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.08332157930025</v>
+        <v>3.07626370335252</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.961256379829391</v>
+        <v>-4.037129352041135</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.179386329848824</v>
+        <v>1.149037140964126</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5364498245623385</v>
+        <v>0.5246866979827892</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.086115200831731</v>
+        <v>3.079057324884001</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.955103673776606</v>
+        <v>-4.030976645988351</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.182509760661596</v>
+        <v>1.152160571776898</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5426025306151228</v>
+        <v>0.5308394040355735</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.09046917285506</v>
+        <v>3.08341129690733</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.971912971927108</v>
+        <v>-4.047785944138853</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.174866518141505</v>
+        <v>1.144517329256808</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5257932324646211</v>
+        <v>0.5140301058850718</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.079464070704869</v>
+        <v>3.072406194757139</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.909614973150986</v>
+        <v>-3.985487945362731</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.266121271448775</v>
+        <v>1.235772082564077</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5257932324646211</v>
+        <v>0.5140301058850718</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.14579962450169</v>
+        <v>3.13874174855396</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.707824775485828</v>
+        <v>-3.783697747697573</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.149129352228965</v>
+        <v>1.118780163344268</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7238114246337755</v>
+        <v>0.7120482980542262</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.066902541517309</v>
+        <v>3.05984466556958</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.758711488172023</v>
+        <v>-3.834584460383768</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.199064899476663</v>
+        <v>1.168715710591965</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.672924711947581</v>
+        <v>0.6611615853680317</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.106660746227768</v>
+        <v>3.099602870280039</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.856452032796997</v>
+        <v>-3.932325005008742</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.174596417742716</v>
+        <v>1.144247228858019</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6570354338146007</v>
+        <v>0.6452723072350515</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.111754915464024</v>
+        <v>3.104697039516294</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.916661330802282</v>
+        <v>-3.992534303014026</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.149048679365274</v>
+        <v>1.118699490480577</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5968261358093162</v>
+        <v>0.585063009229767</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.074165317485524</v>
+        <v>3.067107441537795</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.840239284370355</v>
+        <v>-3.9161122565821</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.178109115977974</v>
+        <v>1.147759927093276</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5968261358093162</v>
+        <v>0.585063009229767</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.072656935525453</v>
+        <v>3.065599059577723</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.795866152731786</v>
+        <v>-3.871739124943531</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.195721236068837</v>
+        <v>1.16537204718414</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6411992674478848</v>
+        <v>0.6294361408683355</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.09914368194403</v>
+        <v>3.092085805996301</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.818346503590671</v>
+        <v>-3.894219475802416</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.181122889863874</v>
+        <v>1.150773700979176</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6411992674478848</v>
+        <v>0.6294361408683355</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.093537476082621</v>
+        <v>3.086479600134891</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.770690773029616</v>
+        <v>-3.84656374524136</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.206566939116101</v>
+        <v>1.176217750231403</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6888549980089405</v>
+        <v>0.6770918714293912</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.128512671447059</v>
+        <v>3.121454795499329</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.670172614530861</v>
+        <v>-3.746045586742605</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.251666575890327</v>
+        <v>1.22131738700563</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.789373156507695</v>
+        <v>0.7776100299281458</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.193715939921037</v>
+        <v>3.186658063973307</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.73083920493325</v>
+        <v>-3.806712177144994</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.214154612205244</v>
+        <v>1.183805423320547</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7076748397891613</v>
+        <v>0.6959117132096121</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.131451622365788</v>
+        <v>3.124393746418059</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.686000803324852</v>
+        <v>-3.761873775536596</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.236187675459232</v>
+        <v>1.205838486574534</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7122182727340308</v>
+        <v>0.7004551461544816</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.138275384743339</v>
+        <v>3.131217508795609</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.70549925956686</v>
+        <v>-3.781372231778604</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.232549232593506</v>
+        <v>1.202200043708809</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6641336314541265</v>
+        <v>0.6523705048745773</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.113585539606474</v>
+        <v>3.106527663658745</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.66129642248096</v>
+        <v>-3.737169394692704</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.256109969955704</v>
+        <v>1.225760781071006</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.708336468540027</v>
+        <v>0.6965733419604777</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.145986844385852</v>
+        <v>3.138928968438122</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.698275450144403</v>
+        <v>-3.774148422356147</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.239728359359574</v>
+        <v>1.209379170474877</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7453103703313575</v>
+        <v>0.7335472437518082</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.166581185929898</v>
+        <v>3.159523309982168</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.539984032605131</v>
+        <v>-3.615857004816875</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.354292691558323</v>
+        <v>1.323943502673625</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7453103703313575</v>
+        <v>0.7335472437518082</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.217828951112937</v>
+        <v>3.210771075165208</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.332342028970654</v>
+        <v>-3.408215001182399</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.435790197606366</v>
+        <v>1.405441008721669</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9529523739658337</v>
+        <v>0.9411892473862844</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.340854857887876</v>
+        <v>3.333796981940147</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.281309936248126</v>
+        <v>-3.357182908459871</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.451151262933647</v>
+        <v>1.42080207404895</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.003984466688362</v>
+        <v>0.9922213401088125</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.366422341759663</v>
+        <v>3.359364465811933</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.216085755120921</v>
+        <v>-3.291958727332665</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.494428339477234</v>
+        <v>1.464079150592537</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.069208647815567</v>
+        <v>1.057445521236018</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.422744254528691</v>
+        <v>3.415686378580962</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.178658735049787</v>
+        <v>-3.254531707261532</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.505360119804968</v>
+        <v>1.475010930920271</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.074460185844749</v>
+        <v>1.0626970592652</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.42185614964548</v>
+        <v>3.414798273697751</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.198770391084496</v>
+        <v>-3.27464336329624</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.498572249722325</v>
+        <v>1.468223060837628</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.085487530842168</v>
+        <v>1.073724404262619</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.429729348975172</v>
+        <v>3.422671473027443</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.145025576657291</v>
+        <v>-3.220898548869035</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.680627946514418</v>
+        <v>1.650278757629721</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.09555084028263</v>
+        <v>1.083787713703081</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.59632510566066</v>
+        <v>3.589267229712931</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.070243315632278</v>
+        <v>-3.146116287844023</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.83065376014224</v>
+        <v>1.800304571257543</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.170333101307643</v>
+        <v>1.158569974728094</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.761307371493485</v>
+        <v>3.754249495545756</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.04415923136847</v>
+        <v>-3.120032203580215</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.832795369861622</v>
+        <v>1.802446180976925</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.170333101307643</v>
+        <v>1.158569974728094</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.753015347507344</v>
+        <v>3.745957471559615</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.966028050519523</v>
+        <v>-3.041901022731268</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.862241037784981</v>
+        <v>1.831891848900283</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.244509912191328</v>
+        <v>1.232746785611778</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.795714629621334</v>
+        <v>3.788656753673605</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.95713558912624</v>
+        <v>-3.033008561337985</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.883352428069085</v>
+        <v>1.853003239184388</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.244509912191328</v>
+        <v>1.232746785611778</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.813269035348126</v>
+        <v>3.806211159400396</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.125611706096118</v>
+        <v>-3.201484678307863</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.807817028685718</v>
+        <v>1.777467839801021</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.216562076474747</v>
+        <v>1.204798949895198</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.788355381322762</v>
+        <v>3.781297505375032</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.427812177234535</v>
+        <v>-2.503685149446279</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.068206537418213</v>
+        <v>2.037857348533516</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.146214017104336</v>
+        <v>1.134450890524787</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.727416242888377</v>
+        <v>3.720358366940647</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.405091073551382</v>
+        <v>-2.480964045763127</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.067959001388379</v>
+        <v>2.037609812503681</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.146214017104336</v>
+        <v>1.134450890524787</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.718080265385281</v>
+        <v>3.711022389437552</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.534292886845425</v>
+        <v>-2.610165859057169</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.175184401921931</v>
+        <v>2.144835213037234</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.017012203810294</v>
+        <v>1.005249077230745</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.799465303260025</v>
+        <v>3.792407427312296</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.68907389362368</v>
+        <v>-2.764946865835425</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.150349821704275</v>
+        <v>2.120000632819578</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9836445297558178</v>
+        <v>0.9718814031762686</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.816522521320986</v>
+        <v>3.809464645373256</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.682019203408507</v>
+        <v>-2.757892175620251</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.14984705377989</v>
+        <v>2.119497864895192</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9906992199709916</v>
+        <v>0.9789360933914424</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.817430691439635</v>
+        <v>3.810372815491906</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.655067979082019</v>
+        <v>-2.730940951293763</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.170633697155226</v>
+        <v>2.140284508270529</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.005579565998711</v>
+        <v>0.9938164394191615</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.836365052701008</v>
+        <v>3.829307176753279</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.791020987138335</v>
+        <v>-2.86689395935008</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.30035562607766</v>
+        <v>2.270006437192962</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.005579565998711</v>
+        <v>0.9938164394191615</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.020468184845968</v>
+        <v>4.013410308898239</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.813429104943207</v>
+        <v>-2.889302077154952</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.283509073858704</v>
+        <v>2.253159884974007</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.005579565998711</v>
+        <v>0.9938164394191615</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.012584879748961</v>
+        <v>4.005527003801232</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.961434872422607</v>
+        <v>-3.037307844634351</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.226360766416581</v>
+        <v>2.196011577531884</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9188525571351693</v>
+        <v>0.9070894305556201</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.962602673980474</v>
+        <v>3.955544798032745</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.970875798311137</v>
+        <v>-3.046748770522881</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.278838113783017</v>
+        <v>2.248488924898319</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.041279674678561</v>
+        <v>1.029516548099012</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.092312662228355</v>
+        <v>4.085254786280626</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.023149405646778</v>
+        <v>-3.099022377858522</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.260819765394061</v>
+        <v>2.230470576509364</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9890060673429195</v>
+        <v>0.9772429407633704</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.063839592372272</v>
+        <v>4.056781716424543</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.099479383247684</v>
+        <v>-3.175352355459428</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.228399587247474</v>
+        <v>2.198050398362777</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9890060673429195</v>
+        <v>0.9772429407633704</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.061951405266047</v>
+        <v>4.054893529318318</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.301733103572037</v>
+        <v>-3.377606075783782</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.142318328720595</v>
+        <v>2.111969139835898</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.786752347018566</v>
+        <v>0.774989220439017</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.935419402674297</v>
+        <v>3.928361526726568</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.463301529099292</v>
+        <v>-3.539174501311037</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.076124968719845</v>
+        <v>2.045775779835148</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6599694232206866</v>
+        <v>0.6482062966411376</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.857783658605722</v>
+        <v>3.850725782657992</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.595602821196846</v>
+        <v>-3.67147579340859</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.036277858746742</v>
+        <v>2.005928669862045</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6599694232206866</v>
+        <v>0.6482062966411376</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.870857065471641</v>
+        <v>3.863799189523911</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763534</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.597164464011706</v>
+        <v>-3.67303743622345</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.035653201620798</v>
+        <v>2.005304012736101</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6599694232206866</v>
+        <v>0.6482062966411376</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.870857065471641</v>
+        <v>3.863799189523911</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715834055392118</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.625065251121179</v>
+        <v>-3.700938223332923</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.023016927904012</v>
+        <v>1.992667739019314</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6253724990777518</v>
+        <v>0.6136093724982028</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.848622952112882</v>
+        <v>3.841565076165153</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.747591353824073</v>
+        <v>-3.823464326035817</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.970770930800053</v>
+        <v>1.940421741915355</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.502846396374858</v>
+        <v>0.4910832697953089</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.771871734468344</v>
+        <v>3.764813858520615</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.61936224197108</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.978105850009661</v>
+        <v>-4.053978822221405</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.945271091916321</v>
+        <v>1.914921903031623</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2723319001892692</v>
+        <v>0.2605687736097202</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.700268996347495</v>
+        <v>3.693211120399766</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.234826668004485</v>
+        <v>-4.31069964021623</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.982894483720238</v>
+        <v>1.952545294835541</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1639173260454544</v>
+        <v>0.1521541994659054</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.775531970863053</v>
+        <v>3.768474094915323</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.388813085780625</v>
+        <v>-4.46468605799237</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.990280185755422</v>
+        <v>1.959930996870725</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1639173260454544</v>
+        <v>0.1521541994659054</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.844512240008693</v>
+        <v>3.837454364060963</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.338291181952959</v>
+        <v>-4.414164154164705</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.996540149406609</v>
+        <v>1.966190960521911</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1639173260454544</v>
+        <v>0.1521541994659054</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.830563442128814</v>
+        <v>3.823505566181084</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994895</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.590766335960684</v>
+        <v>-4.666639308172429</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.907420576858934</v>
+        <v>1.877071387974236</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1639173260454544</v>
+        <v>0.1521541994659054</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.842433931184228</v>
+        <v>3.835376055236498</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.860239137882392</v>
+        <v>-4.936112110094137</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.800841990609194</v>
+        <v>1.770492801724496</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1639173260454544</v>
+        <v>0.1521541994659054</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.843644465703171</v>
+        <v>3.836586589755442</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637088</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.017783209611833</v>
+        <v>-5.093656181823579</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.741946104144739</v>
+        <v>1.711596915260041</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.0970155209051799</v>
+        <v>0.08525239432563086</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.807625124846328</v>
+        <v>3.800567248898599</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301345</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.295747605195107</v>
+        <v>-5.371620577406852</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.625838198647619</v>
+        <v>1.595489009762921</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.007395786619695643</v>
+        <v>-0.004367339959853389</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.748931137011227</v>
+        <v>3.741873261063497</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215471</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.412715297833998</v>
+        <v>-5.488588270045743</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.741255178291107</v>
+        <v>1.710905989406409</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.007395786619695643</v>
+        <v>-0.004367339959853389</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.911135193710271</v>
+        <v>3.904077317762542</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456693</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.497433240054951</v>
+        <v>-5.573306212266696</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.702214639366539</v>
+        <v>1.671865450481842</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.07772024230835073</v>
+        <v>-0.08948336888789976</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.854912214317257</v>
+        <v>3.847854338369528</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.579368058323834</v>
+        <v>-5.65524103053558</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.679670129627477</v>
+        <v>1.64932094074278</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.08765498789543091</v>
+        <v>-0.09941811447497995</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.8591807845335</v>
+        <v>3.852122908585771</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717833</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.525629884923572</v>
+        <v>-5.601502857135317</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.710091037443485</v>
+        <v>1.679741848558787</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.03391681449516881</v>
+        <v>-0.04567994107471784</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.90034932702956</v>
+        <v>3.893291451081831</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.79831094461695</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.415623601446351</v>
+        <v>-5.491496573658096</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.746246438078549</v>
+        <v>1.715897249193851</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.0107122425778936</v>
+        <v>-0.02247536915744264</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.9064249574241</v>
+        <v>3.899367081476371</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203665</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.272564025705425</v>
+        <v>-5.348436997917171</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.807720279096893</v>
+        <v>1.777371090212195</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.002698815987914327</v>
+        <v>-0.01446194256746336</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.915483024100062</v>
+        <v>3.908425148152333</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.971117300233588</v>
+        <v>-5.046990272445333</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.935559852168164</v>
+        <v>1.905210663283466</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2987479094839229</v>
+        <v>0.2869847829043739</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.103611942265701</v>
+        <v>4.096554066317971</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064769</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.995707544468772</v>
+        <v>-5.071580516680517</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.926694932226801</v>
+        <v>1.896345743342103</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2987479094839229</v>
+        <v>0.2869847829043739</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.104583120018411</v>
+        <v>4.097525244070681</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859303</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.00885640385705</v>
+        <v>-5.020542140673997</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.922278292851245</v>
+        <v>1.917603998124466</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2987479094839229</v>
+        <v>0.2869847829043739</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.105426024398167</v>
+        <v>4.098368148450437</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>3.831748677354685</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.967717108990419</v>
+        <v>-4.979402845807366</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.957772109672042</v>
+        <v>1.953097814945264</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3398872043505538</v>
+        <v>0.3281240777710047</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.14914770019229</v>
+        <v>4.142089824244561</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085621</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.857110968910817</v>
+        <v>-4.868796705727764</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.818198561827818</v>
+        <v>1.81352426710104</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4504933444301558</v>
+        <v>0.4387302178506067</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.031695380363987</v>
+        <v>4.024637504416257</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462783</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.987691703441659</v>
+        <v>-4.999377440258606</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.769468312089445</v>
+        <v>1.764794017362666</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3199126098993132</v>
+        <v>0.3081494833197642</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.956848983719444</v>
+        <v>3.949791107771714</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.7750430212186</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.823195369250698</v>
+        <v>-4.834881106067645</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.819693664841912</v>
+        <v>1.815019370115134</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3199126098993132</v>
+        <v>0.3081494833197642</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.941275802795527</v>
+        <v>3.934217926847797</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462771</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.698714888526746</v>
+        <v>-4.710400625343693</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.868673567567922</v>
+        <v>1.863999272841144</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3199126098993132</v>
+        <v>0.3081494833197642</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.940463513231957</v>
+        <v>3.933405637284227</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533057</v>
+        <v>3.832321184533059</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.709100083416636</v>
+        <v>-4.720785820233583</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.874388268737039</v>
+        <v>1.86971397401026</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3095274150094239</v>
+        <v>0.2977642884298749</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.944101175423095</v>
+        <v>3.937043299475366</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.733984935921557</v>
+        <v>3.859634973629163</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.721537833460863</v>
+        <v>3.792911118815379</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.709100083416636</v>
+        <v>-4.720785820233583</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.874388268737039</v>
+        <v>1.86971397401026</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3095274150094239</v>
+        <v>0.2977642884298749</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.714601630447231</v>
+        <v>3.785974915801747</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.3%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-639.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.3%</t>
+          <t>455.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-633.7%</t>
+          <t>-609.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-256.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-189.3%</t>
+          <t>-181.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-258.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-185.5%</t>
+          <t>-217.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-194.2%</t>
+          <t>-189.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-155.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-50.8%</t>
         </is>
       </c>
     </row>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.544971950862044</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.305726329372219</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.3500768343639406</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.91402543341242</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.779665944994596</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.200133506721289</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.3437405671346854</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.906111968752064</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.115328592225048</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.064449039485073</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.4116715526235902</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.863933969114686</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.19177292242792</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>1.040358867638166</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.3312260435299283</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.918688834805125</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.556900305066667</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.8935624295884987</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.6275368278289408</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.740156879231548</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.965489082247345</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7288884627309864</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.036125605009619</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.4937651569379</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.07924949427021</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6785697303933009</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.036125605009619</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.488950589409361</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.495641368557207</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.5100070312873797</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.036125605009619</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.486944640018238</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.739912769284277</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4225571616652308</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.036125605009619</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.497203330686917</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.133125570211944</v>
+        <v>-7.083171288927296</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2613716064398588</v>
+        <v>0.2813533189537183</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.036125605009619</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.493302895832612</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.181328387454288</v>
+        <v>-7.131374106169639</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2404953995979224</v>
+        <v>0.2604771121117815</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.036125605009619</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.491707815887613</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.477989729264485</v>
+        <v>-7.428035447979837</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1256098388030513</v>
+        <v>0.1455915513169108</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.104868740743498</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.454240910376495</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.664709437573788</v>
+        <v>-7.61475515628914</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04689565094492743</v>
+        <v>0.06687736345878648</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.104868740743498</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.450214605842091</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.047710826316418</v>
+        <v>-7.997756545031771</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.106407005873709</v>
+        <v>-0.08642529335984994</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.104868740743498</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.450112504520507</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.052197271517807</v>
+        <v>-8.00224299023316</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1056300679828341</v>
+        <v>-0.08564835546897509</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.109355185944886</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.449992153371104</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.411727594021809</v>
+        <v>-8.361773312737164</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2440918936863845</v>
+        <v>-0.2241101811725259</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.109355185944886</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.455342456669154</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.462076657476031</v>
+        <v>-8.412122376191386</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.256315499110896</v>
+        <v>-0.2363337865970374</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.159704249399109</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.433049038553799</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.559695934897427</v>
+        <v>-8.509741653612782</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2923214594576855</v>
+        <v>-0.2723397469438269</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.257323526820505</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.37751922272273</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.613767434405785</v>
+        <v>-8.56381315312114</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.311056502939457</v>
+        <v>-0.2910747904255984</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.311395026328865</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.347969879339286</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.818025609735649</v>
+        <v>-8.768071328451004</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3872465759527599</v>
+        <v>-0.3672648634389013</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.439033970942853</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.276899709689535</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.851678448244122</v>
+        <v>-8.801724166959477</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3962251568717132</v>
+        <v>-0.3762434443578546</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.539447338859891</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.221134243423749</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.778208616576674</v>
+        <v>-8.728254335292029</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3514655227113126</v>
+        <v>-0.331483810197454</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.465977507192442</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.280587843917639</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.953333033963217</v>
+        <v>-8.903378752678572</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.406960068918413</v>
+        <v>-0.3869783564045544</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.641101924578986</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.19006841423323</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.187785127977707</v>
+        <v>-9.137830846693062</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.507960071425805</v>
+        <v>-0.4879783589119464</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.641101924578986</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.182849249331634</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.292159859004153</v>
+        <v>-9.242205577719508</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5563821546103598</v>
+        <v>-0.5364004420965012</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.745476655605432</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.11355221994179</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.34494601460448</v>
+        <v>-9.294991733319835</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5763808270119339</v>
+        <v>-0.5563991144980753</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.841152142187829</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.057262717830908</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.470982807972769</v>
+        <v>-9.421028526688124</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.624101815730135</v>
+        <v>-0.6041201032162764</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815900519378087</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.075107420145868</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.413911036076838</v>
+        <v>-9.363956754792193</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5972827712853621</v>
+        <v>-0.5773010587715035</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815900519378087</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.079097755832269</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.555582877800958</v>
+        <v>-9.505628596516313</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6554267348737519</v>
+        <v>-0.6354450223598933</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.815900519378087</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.077622528933527</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.505992033376124</v>
+        <v>-9.456037752091479</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6205369869389457</v>
+        <v>-0.600555274425087</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.766309674953253</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.1224304457533</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.357073698904268</v>
+        <v>-9.307119417619623</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5740207867968863</v>
+        <v>-0.5540390742830277</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.73506008421808</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.128129066547721</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.131228546184857</v>
+        <v>-9.081274264900211</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4741036526729134</v>
+        <v>-0.4541219401590539</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.693133408630916</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.162864144936227</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.006649889847266</v>
+        <v>-8.956695608562619</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4231330455818179</v>
+        <v>-0.4031513330679584</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.693133408630916</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.164003289492286</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.048567729753833</v>
+        <v>-9.009590896606905</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4372664073823369</v>
+        <v>-0.4216756741235654</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.73704908697911</v>
+        <v>-1.68817806254247</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.140287656645477</v>
+        <v>2.169610271307461</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.976434554465952</v>
+        <v>-8.937457721319024</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4026794330285481</v>
+        <v>-0.3870886997697767</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.73704908697911</v>
+        <v>-1.68817806254247</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.146021360884114</v>
+        <v>2.175343975546098</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.905068161856304</v>
+        <v>-8.866091328709377</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3838701383785543</v>
+        <v>-0.3682794051197829</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.665682694369462</v>
+        <v>-1.616811669932822</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.179103934056037</v>
+        <v>2.208426548718021</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.81160912787108</v>
+        <v>-8.772632294724152</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.356370006097372</v>
+        <v>-0.3407792728386005</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.665682694369462</v>
+        <v>-1.616811669932822</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.16922045274313</v>
+        <v>2.198543067405114</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.544367327002682</v>
+        <v>-8.505390493855755</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2513078462493867</v>
+        <v>-0.2357171129906153</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.665682694369462</v>
+        <v>-1.616811669932822</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.167385892243756</v>
+        <v>2.196708506905741</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.446460288326191</v>
+        <v>-8.407483455179264</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2124453457522515</v>
+        <v>-0.1968546124934796</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.597696944508906</v>
+        <v>-1.548825920072266</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.207877027186629</v>
+        <v>2.237199641848613</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.422506747350234</v>
+        <v>-8.383529914203306</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2021954232163745</v>
+        <v>-0.186604689957603</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.573743403532949</v>
+        <v>-1.524872379096308</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.222917657917697</v>
+        <v>2.252240272579682</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.158446809027437</v>
+        <v>-8.119469975880509</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1098317640490079</v>
+        <v>-0.09424103079023638</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.309683465210152</v>
+        <v>-1.260812440773512</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.368093304749623</v>
+        <v>2.397415919411607</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.451367185522598</v>
+        <v>-7.412390352375671</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1702130516926266</v>
+        <v>0.185803784951398</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.309683465210152</v>
+        <v>-1.260812440773512</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.365306271089322</v>
+        <v>2.394628885751306</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.411182887156408</v>
+        <v>-7.372206054009481</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1866303949269441</v>
+        <v>0.2022211281857156</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.269499166843961</v>
+        <v>-1.220628142407321</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.389760473996878</v>
+        <v>2.419083088658862</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.247783016217046</v>
+        <v>-7.208806183070118</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.251357164523446</v>
+        <v>0.2669478977822175</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.106099295904599</v>
+        <v>-1.057228271467959</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.487167217781252</v>
+        <v>2.516489832443237</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.014301793987447</v>
+        <v>-6.97532496084052</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3526740822531376</v>
+        <v>0.3682648155119095</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8726180736750004</v>
+        <v>-0.8237470492383601</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.635180379956864</v>
+        <v>2.664502994618848</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.864635402979932</v>
+        <v>-6.825658569833005</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4096484283431847</v>
+        <v>0.4252391616019562</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7797145824324645</v>
+        <v>-0.7308435579958241</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.688030264389426</v>
+        <v>2.71735287905141</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.732359929349045</v>
+        <v>-6.693383096202118</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4579261045425662</v>
+        <v>0.4735168378013377</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6474391088015778</v>
+        <v>-0.5985680843649375</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.762763035314985</v>
+        <v>2.792085649976969</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.576621596789304</v>
+        <v>-6.537644763642376</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5230364982540996</v>
+        <v>0.5386272315128711</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4917007762418363</v>
+        <v>-0.4428297518051959</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.859021095538467</v>
+        <v>2.888343710200451</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.327621798105723</v>
+        <v>-6.288644964958795</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6355427589511908</v>
+        <v>0.6511334922099623</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2427009775582556</v>
+        <v>-0.1938299531216152</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.021327315972274</v>
+        <v>3.050649930634258</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.433211787878827</v>
+        <v>-6.3942349547319</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4653308334427302</v>
+        <v>0.4809215667015021</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3482909673313599</v>
+        <v>-0.2994199428947196</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.829997392509193</v>
+        <v>2.859320007171177</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.451946689997424</v>
+        <v>-6.412969856850497</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5063812144723778</v>
+        <v>0.5219719477311493</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3538869769914912</v>
+        <v>-0.3050159525548509</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.8751841285902</v>
+        <v>2.904506743252185</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.304006648589825</v>
+        <v>-6.265029815442897</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.44567830834725</v>
+        <v>0.4612690416060214</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3335660610829337</v>
+        <v>-0.2846950366462933</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.767497755447167</v>
+        <v>2.796820370109152</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.251037126335836</v>
+        <v>-6.212060293188909</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4581521309953671</v>
+        <v>0.473742864254139</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2805965388289448</v>
+        <v>-0.2317255143923044</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.790565482546083</v>
+        <v>2.819888097208067</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.207488719565146</v>
+        <v>-6.168511886418218</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4686108816085501</v>
+        <v>0.484201614867322</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2805965388289448</v>
+        <v>-0.2317255143923044</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.783604870450989</v>
+        <v>2.812927485112974</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.174125513086377</v>
+        <v>-6.13514867993945</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4964185185812009</v>
+        <v>0.5120092518399724</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2805965388289448</v>
+        <v>-0.2317255143923044</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.798067224832133</v>
+        <v>2.827389839494117</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.065866375963855</v>
+        <v>-6.026889542816928</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5342542938894046</v>
+        <v>0.5498450271481761</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2805965388289448</v>
+        <v>-0.2317255143923044</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.792599345291328</v>
+        <v>2.821921959953312</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.942575241146725</v>
+        <v>-5.903598407999797</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5810688418268337</v>
+        <v>0.5966595750856056</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1573054040118143</v>
+        <v>-0.1084343795751739</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.864072120192183</v>
+        <v>2.893394734854167</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.921426042243281</v>
+        <v>-5.882449209096354</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5972294996255365</v>
+        <v>0.612820232884308</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.136156205108371</v>
+        <v>-0.08728518067173058</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.884462617771574</v>
+        <v>2.913785232433558</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.677660600259837</v>
+        <v>-5.63868376711291</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6905163847659646</v>
+        <v>0.7061071180247365</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.136156205108371</v>
+        <v>-0.08728518067173058</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.880243326118625</v>
+        <v>2.909565940780609</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.575897779982542</v>
+        <v>-5.536920946835615</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7333458267968989</v>
+        <v>0.7489365600556703</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1229371367159423</v>
+        <v>-0.07406611227930188</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.890299081074098</v>
+        <v>2.919621695736082</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.326047386033467</v>
+        <v>-5.28707055288654</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8260280593602305</v>
+        <v>0.8416187926190024</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1229371367159423</v>
+        <v>-0.07406611227930188</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.8830411560578</v>
+        <v>2.912363770719784</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.150155293566035</v>
+        <v>-5.111178460419108</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8999840198678521</v>
+        <v>0.9155747531266241</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1229371367159423</v>
+        <v>-0.07406611227930188</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.886640279578449</v>
+        <v>2.915962894240433</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.978708830543572</v>
+        <v>-4.939731997396644</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9818901111313914</v>
+        <v>0.997480844390163</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04850932630652088</v>
+        <v>0.09738035074316126</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.00283566344648</v>
+        <v>3.032158278108464</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.904419264805233</v>
+        <v>-4.865442431658305</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.010626415043024</v>
+        <v>1.026217148301796</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1227988920448602</v>
+        <v>0.1716699164815005</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.046429880505781</v>
+        <v>3.075752495167765</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.840783522571298</v>
+        <v>-4.801806689424371</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.040775512990915</v>
+        <v>1.056366246249687</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1864346342787947</v>
+        <v>0.2353056587154351</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.089306126900459</v>
+        <v>3.118628741562443</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.729356763245378</v>
+        <v>-4.690379930098451</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.066540475505079</v>
+        <v>1.08213120876385</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1864346342787947</v>
+        <v>0.2353056587154351</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.070500385684254</v>
+        <v>3.099823000346238</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.488926266440518</v>
+        <v>-4.44994943329359</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.1644557508519</v>
+        <v>1.180046484110672</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.426865131083655</v>
+        <v>0.4757361555202954</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.216501760392048</v>
+        <v>3.245824375054032</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.416683698269323</v>
+        <v>-4.377706865122396</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.197282091955198</v>
+        <v>1.21287282521397</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.426865131083655</v>
+        <v>0.4757361555202954</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.220431074226868</v>
+        <v>3.249753688888852</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.398970011391458</v>
+        <v>-4.35999317824453</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.205046150623684</v>
+        <v>1.220636883882456</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4300464599805718</v>
+        <v>0.4789174844172122</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.223018455482358</v>
+        <v>3.252341070144342</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.290165125911731</v>
+        <v>-4.251188292764803</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.245566176035569</v>
+        <v>1.26115690929434</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4300464599805718</v>
+        <v>0.4789174844172122</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.220016526702352</v>
+        <v>3.249339141364336</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.07014432787472</v>
+        <v>-4.031167494727793</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.335153532260987</v>
+        <v>1.350744265519759</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.571266305048552</v>
+        <v>0.6201373294851924</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.306327470753754</v>
+        <v>3.335650085415738</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.937276638811442</v>
+        <v>-3.898299805664515</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.404194790688122</v>
+        <v>1.419785523946893</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.571266305048552</v>
+        <v>0.6201373294851924</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.322221653555577</v>
+        <v>3.351544268217562</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.817103555446943</v>
+        <v>-3.778126722300016</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.453409868474223</v>
+        <v>1.469000601732995</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.691439388413051</v>
+        <v>0.7403104128496913</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.395471348014579</v>
+        <v>3.424793962676563</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.672431410347206</v>
+        <v>-3.633454577200278</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.521366829075558</v>
+        <v>1.53695756233433</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8361115335127884</v>
+        <v>0.8849825579494288</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.492362737635861</v>
+        <v>3.521685352297845</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.732306237704898</v>
+        <v>-3.693329404557971</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.483454389533907</v>
+        <v>1.499045122792678</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7762367061550963</v>
+        <v>0.8251077305917367</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.442475332622672</v>
+        <v>3.471797947284656</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.612486006794061</v>
+        <v>-3.573509173647133</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.54667165113245</v>
+        <v>1.562262384391222</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7762367061550963</v>
+        <v>0.8251077305917367</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.45776450185688</v>
+        <v>3.487087116518864</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.614955713255867</v>
+        <v>-3.575978880108939</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.45332796787017</v>
+        <v>1.468918701128941</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7737669996932901</v>
+        <v>0.8226380241299305</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.363926877302238</v>
+        <v>3.393249491964222</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.683325899579876</v>
+        <v>-3.644349066432949</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.345241754825867</v>
+        <v>1.360832488084639</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.783042698729505</v>
+        <v>0.8319137231661454</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.288754158209268</v>
+        <v>3.318076772871252</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.845443447525637</v>
+        <v>-3.658137119279996</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.270831444279454</v>
+        <v>1.345753975577711</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.783042698729505</v>
+        <v>0.8319137231661454</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.27919086684116</v>
+        <v>3.308513481503144</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.900963523418226</v>
+        <v>-3.713657195172585</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.385654250614621</v>
+        <v>1.460576781912878</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.783042698729505</v>
+        <v>0.8319137231661454</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.416221703533362</v>
+        <v>3.445544318195346</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.725489263625757</v>
+        <v>-3.538182935380116</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.460411186523396</v>
+        <v>1.535333717821653</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.783042698729505</v>
+        <v>0.8319137231661454</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.42078893552515</v>
+        <v>3.450111550187134</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.836425516267006</v>
+        <v>-3.649119188021364</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.391778714228104</v>
+        <v>1.466701245526361</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.783042698729505</v>
+        <v>0.8319137231661454</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.396530964286357</v>
+        <v>3.425853578948341</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.802761970794724</v>
+        <v>-3.615455642549083</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.333782445818466</v>
+        <v>1.408704977116723</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8167062442017869</v>
+        <v>0.8655772686384273</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.345267404971175</v>
+        <v>3.37459001963316</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.742909351591001</v>
+        <v>-3.555603023345359</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.367895879932088</v>
+        <v>1.442818411230345</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8167062442017869</v>
+        <v>0.8655772686384273</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.355439791403308</v>
+        <v>3.384762406065292</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.656665888564623</v>
+        <v>-3.469359560318982</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.397339535716499</v>
+        <v>1.472262067014756</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8167062442017869</v>
+        <v>0.8655772686384273</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.350386061977168</v>
+        <v>3.379708676639153</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.701972707963603</v>
+        <v>-3.514666379717962</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.370992583401433</v>
+        <v>1.44591511469969</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7758960811925562</v>
+        <v>0.8247671056291965</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.317675739616155</v>
+        <v>3.346998354278139</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.731005812665904</v>
+        <v>-3.543699484420264</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.359931214553614</v>
+        <v>1.434853745851871</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7758960811925562</v>
+        <v>0.8247671056291965</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.318227612649257</v>
+        <v>3.347550227311241</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.638195331215045</v>
+        <v>-3.450889002969404</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.326328099025323</v>
+        <v>1.40125063032358</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8687065626434155</v>
+        <v>0.9175775870800559</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.303186593411138</v>
+        <v>3.332509208073122</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.682584800544473</v>
+        <v>-3.495278472298832</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.310445787218153</v>
+        <v>1.38536831851641</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8243170933139878</v>
+        <v>0.8731881177506282</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.278426387738082</v>
+        <v>3.307749002400067</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.799126405649816</v>
+        <v>-3.611820077404175</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.258904853687739</v>
+        <v>1.333827384985996</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7077754882086451</v>
+        <v>0.7566465126452855</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.2035771331866</v>
+        <v>3.232899747848584</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.686749404467143</v>
+        <v>-3.499443076221502</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.309346949991475</v>
+        <v>1.384269481289732</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7077754882086451</v>
+        <v>0.7566465126452855</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.209068429017267</v>
+        <v>3.238391043679251</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.714529802368496</v>
+        <v>-3.527223474122855</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.309731992599473</v>
+        <v>1.38465452389773</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.679995090307292</v>
+        <v>0.7288661147439324</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.203897392044994</v>
+        <v>3.233220006706978</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.832910475098635</v>
+        <v>-3.645604146852994</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.100735443508071</v>
+        <v>1.175657974806328</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6127772381563158</v>
+        <v>0.6616482625929562</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.001922400755062</v>
+        <v>3.031245015417046</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.941524553541966</v>
+        <v>-3.754218225296325</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.177439472849944</v>
+        <v>1.252362004148201</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6127772381563158</v>
+        <v>0.6616482625929562</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.122072061474267</v>
+        <v>3.151394676136252</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.906115515293823</v>
+        <v>-3.718809187048182</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.206116114251524</v>
+        <v>1.281038645549781</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6127772381563158</v>
+        <v>0.6616482625929562</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.13658508757659</v>
+        <v>3.165907702238575</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.867731852735672</v>
+        <v>-3.680425524490031</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.218889020617153</v>
+        <v>1.29381155191541</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.651160900714467</v>
+        <v>0.7000319251511073</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.15703472645385</v>
+        <v>3.186357341115834</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.690615522700506</v>
+        <v>-3.503309194454865</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.286464581476522</v>
+        <v>1.361387112774779</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.651160900714467</v>
+        <v>0.7000319251511073</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.153763755299152</v>
+        <v>3.183086369961136</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.735707767534051</v>
+        <v>-3.54840143928841</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.269111075305017</v>
+        <v>1.344033606603274</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5892648575450772</v>
+        <v>0.6381358819817176</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.117309521159431</v>
+        <v>3.146632135821415</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.556332346295283</v>
+        <v>-3.369026018049643</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.334648219106938</v>
+        <v>1.409570750405195</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7460416157157959</v>
+        <v>0.7949126401524362</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.205162551368276</v>
+        <v>3.23448516603026</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.60134655981589</v>
+        <v>-3.414040231570249</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.297449989030285</v>
+        <v>1.372372520328542</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7156927204011913</v>
+        <v>0.7645637448378316</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.167760669511103</v>
+        <v>3.197083284173087</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.868351070088325</v>
+        <v>-3.681044741842684</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.196339747260257</v>
+        <v>1.271262278558514</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5213296823582427</v>
+        <v>0.5702007067948831</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.05683440902428</v>
+        <v>3.086157023686264</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.969548851525498</v>
+        <v>-3.782242523279857</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.155064556581889</v>
+        <v>1.229987087880146</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4529208688129235</v>
+        <v>0.501791893249564</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.01499304279359</v>
+        <v>3.044315657455574</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.963037884911185</v>
+        <v>-3.775731556665544</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.155268904781931</v>
+        <v>1.230191436080188</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4529208688129235</v>
+        <v>0.501791893249564</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.012593004347907</v>
+        <v>3.041915619009891</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.943999757203888</v>
+        <v>-3.756693428958247</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.159408875073095</v>
+        <v>1.234331406371352</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.394737257481729</v>
+        <v>0.4436082819183694</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.974207556757435</v>
+        <v>3.003530171419419</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.975126388354506</v>
+        <v>-3.787820060108865</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.266252624247038</v>
+        <v>1.341175155545295</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.394737257481729</v>
+        <v>0.4436082819183694</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.093501958391625</v>
+        <v>3.122824573053609</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.988993149688423</v>
+        <v>-3.801686821442782</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.261539248699604</v>
+        <v>1.336461779997862</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3568793407479061</v>
+        <v>0.4057503651845465</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.071620537337465</v>
+        <v>3.100943151999449</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.082857639744916</v>
+        <v>-3.756882649902852</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.230001983073933</v>
+        <v>1.360391979010759</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3568793407479061</v>
+        <v>0.4057503651845465</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.077629067734391</v>
+        <v>3.106951682396375</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.935114669509914</v>
+        <v>-3.60913967966785</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.187049392445134</v>
+        <v>1.31743938838196</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5246866979827892</v>
+        <v>0.5735577224194297</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.07626370335252</v>
+        <v>3.105586318014505</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.037129352041135</v>
+        <v>-3.711154362199071</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.149037140964126</v>
+        <v>1.279427136900952</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5246866979827892</v>
+        <v>0.5735577224194297</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.079057324884001</v>
+        <v>3.108379939545986</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.030976645988351</v>
+        <v>-3.705001656146287</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.152160571776898</v>
+        <v>1.282550567713725</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5308394040355735</v>
+        <v>0.579710428472214</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.08341129690733</v>
+        <v>3.112733911569315</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.047785944138853</v>
+        <v>-3.721810954296788</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.144517329256808</v>
+        <v>1.274907325193634</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5140301058850718</v>
+        <v>0.5629011303217124</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.072406194757139</v>
+        <v>3.101728809419124</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.985487945362731</v>
+        <v>-3.659512955520666</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.235772082564077</v>
+        <v>1.366162078500904</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5140301058850718</v>
+        <v>0.5629011303217124</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.13874174855396</v>
+        <v>3.168064363215945</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.783697747697573</v>
+        <v>-3.457722757855509</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.118780163344268</v>
+        <v>1.249170159281094</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7120482980542262</v>
+        <v>0.7609193224908668</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.05984466556958</v>
+        <v>3.089167280231564</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.834584460383768</v>
+        <v>-3.508609470541703</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.168715710591965</v>
+        <v>1.299105706528791</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6611615853680317</v>
+        <v>0.7100326098046723</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.099602870280039</v>
+        <v>3.128925484942023</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.932325005008742</v>
+        <v>-3.606350015166678</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.144247228858019</v>
+        <v>1.274637224794845</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6452723072350515</v>
+        <v>0.6941433316716921</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.104697039516294</v>
+        <v>3.134019654178279</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.992534303014026</v>
+        <v>-3.666559313171962</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.118699490480577</v>
+        <v>1.249089486417403</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.585063009229767</v>
+        <v>0.6339340336664075</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.067107441537795</v>
+        <v>3.096430056199779</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.9161122565821</v>
+        <v>-3.590137266740035</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.147759927093276</v>
+        <v>1.278149923030103</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.585063009229767</v>
+        <v>0.6339340336664075</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.065599059577723</v>
+        <v>3.094921674239708</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.871739124943531</v>
+        <v>-3.545764135101467</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.16537204718414</v>
+        <v>1.295762043120966</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6294361408683355</v>
+        <v>0.6783071653049761</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.092085805996301</v>
+        <v>3.121408420658285</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.894219475802416</v>
+        <v>-3.568244485960351</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.150773700979176</v>
+        <v>1.281163696916003</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6294361408683355</v>
+        <v>0.6783071653049761</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.086479600134891</v>
+        <v>3.115802214796876</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.84656374524136</v>
+        <v>-3.520588755399296</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.176217750231403</v>
+        <v>1.30660774616823</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6770918714293912</v>
+        <v>0.7259628958660318</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.121454795499329</v>
+        <v>3.150777410161314</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.746045586742605</v>
+        <v>-3.420070596900541</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.22131738700563</v>
+        <v>1.351707382942456</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7776100299281458</v>
+        <v>0.8264810543647864</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.186658063973307</v>
+        <v>3.215980678635291</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.806712177144994</v>
+        <v>-3.48073718730293</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.183805423320547</v>
+        <v>1.314195419257373</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6959117132096121</v>
+        <v>0.7447827376462527</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.124393746418059</v>
+        <v>3.153716361080043</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.761873775536596</v>
+        <v>-3.435898785694532</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.205838486574534</v>
+        <v>1.336228482511361</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7004551461544816</v>
+        <v>0.7493261705911222</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.131217508795609</v>
+        <v>3.160540123457594</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.781372231778604</v>
+        <v>-3.455397241936541</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.202200043708809</v>
+        <v>1.332590039645635</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6523705048745773</v>
+        <v>0.7012415293112179</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.106527663658745</v>
+        <v>3.135850278320729</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.737169394692704</v>
+        <v>-3.41119440485064</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.225760781071006</v>
+        <v>1.356150777007833</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6965733419604777</v>
+        <v>0.7454443663971183</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.138928968438122</v>
+        <v>3.168251583100107</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.774148422356147</v>
+        <v>-3.448173432514083</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.209379170474877</v>
+        <v>1.339769166411703</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7335472437518082</v>
+        <v>0.7824182681884488</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.159523309982168</v>
+        <v>3.188845924644153</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.615857004816875</v>
+        <v>-3.289882014974811</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.323943502673625</v>
+        <v>1.454333498610451</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7335472437518082</v>
+        <v>0.7824182681884488</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.210771075165208</v>
+        <v>3.240093689827192</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.408215001182399</v>
+        <v>-3.082240011340335</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.405441008721669</v>
+        <v>1.535831004658495</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9411892473862844</v>
+        <v>0.990060271822925</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.333796981940147</v>
+        <v>3.363119596602131</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.357182908459871</v>
+        <v>-3.031207918617807</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.42080207404895</v>
+        <v>1.551192069985776</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9922213401088125</v>
+        <v>1.041092364545453</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.359364465811933</v>
+        <v>3.388687080473917</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.291958727332665</v>
+        <v>-2.965983737490602</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.464079150592537</v>
+        <v>1.594469146529363</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.057445521236018</v>
+        <v>1.106316545672658</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.415686378580962</v>
+        <v>3.445008993242946</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.254531707261532</v>
+        <v>-2.928556717419468</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.475010930920271</v>
+        <v>1.605400926857097</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.0626970592652</v>
+        <v>1.11156808370184</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.414798273697751</v>
+        <v>3.444120888359735</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.27464336329624</v>
+        <v>-2.948668373454176</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.468223060837628</v>
+        <v>1.598613056774454</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.073724404262619</v>
+        <v>1.122595428699259</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.422671473027443</v>
+        <v>3.451994087689427</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.220898548869035</v>
+        <v>-2.894923559026971</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.650278757629721</v>
+        <v>1.780668753566547</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.083787713703081</v>
+        <v>1.132658738139722</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.589267229712931</v>
+        <v>3.618589844374915</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.146116287844023</v>
+        <v>-2.820141298001959</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.800304571257543</v>
+        <v>1.930694567194369</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.158569974728094</v>
+        <v>1.207440999164734</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.754249495545756</v>
+        <v>3.78357211020774</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.120032203580215</v>
+        <v>-2.794057213738151</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.802446180976925</v>
+        <v>1.932836176913751</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.158569974728094</v>
+        <v>1.207440999164734</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.745957471559615</v>
+        <v>3.775280086221599</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.041901022731268</v>
+        <v>-2.715926032889204</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.831891848900283</v>
+        <v>1.96228184483711</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.232746785611778</v>
+        <v>1.281617810048419</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.788656753673605</v>
+        <v>3.817979368335589</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.033008561337985</v>
+        <v>-2.707033571495921</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.853003239184388</v>
+        <v>1.983393235121214</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.232746785611778</v>
+        <v>1.281617810048419</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.806211159400396</v>
+        <v>3.83553377406238</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.201484678307863</v>
+        <v>-2.875509688465799</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.777467839801021</v>
+        <v>1.907857835737847</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.204798949895198</v>
+        <v>1.253669974331838</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.781297505375032</v>
+        <v>3.810620120037016</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.503685149446279</v>
+        <v>-2.177710159604215</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.037857348533516</v>
+        <v>2.168247344470342</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.134450890524787</v>
+        <v>1.183321914961427</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.720358366940647</v>
+        <v>3.749680981602631</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.480964045763127</v>
+        <v>-2.154989055921063</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.037609812503681</v>
+        <v>2.167999808440507</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.134450890524787</v>
+        <v>1.183321914961427</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.711022389437552</v>
+        <v>3.740345004099536</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.610165859057169</v>
+        <v>-2.284190869215105</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.144835213037234</v>
+        <v>2.27522520897406</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.005249077230745</v>
+        <v>1.054120101667385</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.792407427312296</v>
+        <v>3.82173004197428</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.764946865835425</v>
+        <v>-2.438971875993361</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.120000632819578</v>
+        <v>2.250390628756404</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9718814031762686</v>
+        <v>1.020752427612909</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.809464645373256</v>
+        <v>3.83878726003524</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.757892175620251</v>
+        <v>-2.431917185778187</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.119497864895192</v>
+        <v>2.249887860832019</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9789360933914424</v>
+        <v>1.027807117828083</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.810372815491906</v>
+        <v>3.83969543015389</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.730940951293763</v>
+        <v>-2.404965961451699</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.140284508270529</v>
+        <v>2.270674504207356</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9938164394191615</v>
+        <v>1.042687463855802</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.829307176753279</v>
+        <v>3.858629791415263</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.86689395935008</v>
+        <v>-2.553699096186526</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.270006437192962</v>
+        <v>2.395284382458384</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9938164394191615</v>
+        <v>1.042687463855802</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.013410308898239</v>
+        <v>4.042732923560223</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.889302077154952</v>
+        <v>-2.576107213991398</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.253159884974007</v>
+        <v>2.378437830239429</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9938164394191615</v>
+        <v>1.042687463855802</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.005527003801232</v>
+        <v>4.034849618463216</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.037307844634351</v>
+        <v>-2.724112981470797</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.196011577531884</v>
+        <v>2.321289522797307</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9070894305556201</v>
+        <v>0.9559604549922605</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.955544798032745</v>
+        <v>3.984867412694729</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.046748770522881</v>
+        <v>-2.733553907359327</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.248488924898319</v>
+        <v>2.373766870163742</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.029516548099012</v>
+        <v>1.078387572535652</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.085254786280626</v>
+        <v>4.11457740094261</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.099022377858522</v>
+        <v>-2.785827514694968</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.230470576509364</v>
+        <v>2.355748521774786</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9772429407633704</v>
+        <v>1.026113965200011</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.056781716424543</v>
+        <v>4.086104331086527</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.175352355459428</v>
+        <v>-2.862157492295874</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.198050398362777</v>
+        <v>2.323328343628199</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9772429407633704</v>
+        <v>1.026113965200011</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.054893529318318</v>
+        <v>4.084216143980302</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.377606075783782</v>
+        <v>-3.064411212620227</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.111969139835898</v>
+        <v>2.23724708510132</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.774989220439017</v>
+        <v>0.8238602448756571</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.928361526726568</v>
+        <v>3.957684141388552</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.539174501311037</v>
+        <v>-3.225979638147483</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.045775779835148</v>
+        <v>2.17105372510057</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6482062966411376</v>
+        <v>0.6970773210777778</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.850725782657992</v>
+        <v>3.880048397319977</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.7549119076471</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.67147579340859</v>
+        <v>-3.358280930245036</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.005928669862045</v>
+        <v>2.131206615127468</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6482062966411376</v>
+        <v>0.6970773210777778</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.863799189523911</v>
+        <v>3.893121804185895</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763534</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.67303743622345</v>
+        <v>-3.359842573059896</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.005304012736101</v>
+        <v>2.130581958001524</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6482062966411376</v>
+        <v>0.6970773210777778</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.863799189523911</v>
+        <v>3.893121804185895</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392118</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.700938223332923</v>
+        <v>-3.387743360169369</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.992667739019314</v>
+        <v>2.117945684284736</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6136093724982028</v>
+        <v>0.662480396934843</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.841565076165153</v>
+        <v>3.870887690827137</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.823464326035817</v>
+        <v>-3.510269462872263</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.940421741915355</v>
+        <v>2.065699687180778</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4910832697953089</v>
+        <v>0.5399542942319491</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.764813858520615</v>
+        <v>3.794136473182599</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61936224197108</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.053978822221405</v>
+        <v>-3.740783959057851</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.914921903031623</v>
+        <v>2.040199848297046</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2605687736097202</v>
+        <v>0.3094397980463603</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.693211120399766</v>
+        <v>3.72253373506175</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.31069964021623</v>
+        <v>-3.997504777052675</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.952545294835541</v>
+        <v>2.077823240100964</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1521541994659054</v>
+        <v>0.2010252239025455</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.768474094915323</v>
+        <v>3.797796709577308</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.46468605799237</v>
+        <v>-4.151491194828816</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.959930996870725</v>
+        <v>2.085208942136147</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1521541994659054</v>
+        <v>0.2010252239025455</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.837454364060963</v>
+        <v>3.866776978722947</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.414164154164705</v>
+        <v>-4.10096929100115</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.966190960521911</v>
+        <v>2.091468905787334</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1521541994659054</v>
+        <v>0.2010252239025455</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.823505566181084</v>
+        <v>3.852828180843068</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994895</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.666639308172429</v>
+        <v>-4.392643690857105</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.877071387974236</v>
+        <v>1.986669634900366</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1521541994659054</v>
+        <v>0.2010252239025455</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.835376055236498</v>
+        <v>3.864698669898482</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.936112110094137</v>
+        <v>-4.662116492778813</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.770492801724496</v>
+        <v>1.880091048650626</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1521541994659054</v>
+        <v>0.2010252239025455</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.836586589755442</v>
+        <v>3.865909204417426</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637088</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.093656181823579</v>
+        <v>-4.819660564508255</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.711596915260041</v>
+        <v>1.821195162186171</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08525239432563086</v>
+        <v>0.134123418762271</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.800567248898599</v>
+        <v>3.829889863560583</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301345</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.371620577406852</v>
+        <v>-5.097624960091529</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.595489009762921</v>
+        <v>1.705087256689051</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.004367339959853389</v>
+        <v>0.04450368447678676</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.741873261063497</v>
+        <v>3.771195875725482</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215471</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.488588270045743</v>
+        <v>-5.21459265273042</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.710905989406409</v>
+        <v>1.820504236332539</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.004367339959853389</v>
+        <v>0.04450368447678676</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.904077317762542</v>
+        <v>3.933399932424526</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456693</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.573306212266696</v>
+        <v>-5.299310594951373</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.671865450481842</v>
+        <v>1.781463697407972</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08948336888789976</v>
+        <v>-0.04061234445125961</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.847854338369528</v>
+        <v>3.877176953031512</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.65524103053558</v>
+        <v>-5.381245413220256</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.64932094074278</v>
+        <v>1.758919187668909</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.09941811447497995</v>
+        <v>-0.05054709003833979</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.852122908585771</v>
+        <v>3.881445523247755</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717833</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.601502857135317</v>
+        <v>-5.327507239819994</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.679741848558787</v>
+        <v>1.789340095484917</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04567994107471784</v>
+        <v>0.003191083361922309</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.893291451081831</v>
+        <v>3.922614065743815</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79831094461695</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.491496573658096</v>
+        <v>-5.217500956342772</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.715897249193851</v>
+        <v>1.825495496119981</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02247536915744264</v>
+        <v>0.02639565527919752</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.899367081476371</v>
+        <v>3.928689696138355</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203665</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.348436997917171</v>
+        <v>-5.074441380601847</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.777371090212195</v>
+        <v>1.886969337138325</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01446194256746336</v>
+        <v>0.03440908186917679</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.908425148152333</v>
+        <v>3.937747762814317</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.046990272445333</v>
+        <v>-4.77299465513001</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.905210663283466</v>
+        <v>2.014808910209596</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2869847829043739</v>
+        <v>0.3358558073410141</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.096554066317971</v>
+        <v>4.125876680979955</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064769</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.071580516680517</v>
+        <v>-4.797584899365194</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.896345743342103</v>
+        <v>2.005943990268233</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2869847829043739</v>
+        <v>0.3358558073410141</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.097525244070681</v>
+        <v>4.126847858732665</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859303</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.020542140673997</v>
+        <v>-4.746546523358673</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.917603998124466</v>
+        <v>2.027202245050597</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2869847829043739</v>
+        <v>0.3358558073410141</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.098368148450437</v>
+        <v>4.127690763112421</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354685</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.979402845807366</v>
+        <v>-4.705407228492042</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.953097814945264</v>
+        <v>2.062696061871394</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3281240777710047</v>
+        <v>0.3769951022076449</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.142089824244561</v>
+        <v>4.171412438906545</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085621</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.868796705727764</v>
+        <v>-4.59480108841244</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.81352426710104</v>
+        <v>1.923122514027169</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4387302178506067</v>
+        <v>0.4876012422872469</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.024637504416257</v>
+        <v>4.053960119078241</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462783</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.999377440258606</v>
+        <v>-4.725381822943283</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.764794017362666</v>
+        <v>1.874392264288796</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3081494833197642</v>
+        <v>0.3570205077564044</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.949791107771714</v>
+        <v>3.979113722433699</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.7750430212186</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.834881106067645</v>
+        <v>-4.560885488752321</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.815019370115134</v>
+        <v>1.924617617041264</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3081494833197642</v>
+        <v>0.3570205077564044</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.934217926847797</v>
+        <v>3.963540541509781</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462771</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.710400625343693</v>
+        <v>-4.43640500802837</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.863999272841144</v>
+        <v>1.973597519767274</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3081494833197642</v>
+        <v>0.3570205077564044</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.933405637284227</v>
+        <v>3.962728251946212</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533059</v>
+        <v>3.83232118453305</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.720785820233583</v>
+        <v>-4.446790202918259</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.86971397401026</v>
+        <v>1.979312220936391</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2977642884298749</v>
+        <v>0.3466353128665151</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.937043299475366</v>
+        <v>3.96636591413735</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.859634973629163</v>
+        <v>3.83892492013052</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.792911118815379</v>
+        <v>3.743082388853192</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.720785820233583</v>
+        <v>-4.483399054129496</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.86971397401026</v>
+        <v>1.949366342887647</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2977642884298749</v>
+        <v>0.3493335902362247</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.785974915801747</v>
+        <v>3.952682542994927</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240727.xlsx
+++ b/tame_output/ON/bt/strategyON_20240727.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-639.5%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.1%</t>
+          <t>455.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-609.9%</t>
+          <t>-610.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-256.2%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.3%</t>
+          <t>-179.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-258.4%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-217.1%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-189.1%</t>
+          <t>-197.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-54.4%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.544971950862044</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.305726329372219</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.3500768343639406</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.91402543341242</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.779665944994596</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.200133506721289</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3437405671346854</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.906111968752064</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.115328592225048</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.064449039485073</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4116715526235902</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.863933969114686</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.19177292242792</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.040358867638166</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3312260435299283</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.918688834805125</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.556900305066667</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8935624295884987</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6275368278289408</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.740156879231548</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.965489082247345</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7288884627309864</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.036125605009619</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.4937651569379</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.07924949427021</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6785697303933009</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.036125605009619</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.488950589409361</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.495641368557207</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5100070312873797</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.036125605009619</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.486944640018238</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.739912769284277</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4225571616652308</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.036125605009619</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.497203330686917</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.083171288927296</v>
+        <v>-7.133125570211944</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2813533189537183</v>
+        <v>0.2613716064398588</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.036125605009619</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.493302895832612</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.131374106169639</v>
+        <v>-7.181328387454288</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2604771121117815</v>
+        <v>0.2404953995979224</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.036125605009619</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.491707815887613</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.428035447979837</v>
+        <v>-7.477989729264485</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1455915513169108</v>
+        <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.104868740743498</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.454240910376495</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.61475515628914</v>
+        <v>-7.664709437573788</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.06687736345878648</v>
+        <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.104868740743498</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.450214605842091</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.997756545031771</v>
+        <v>-8.047710826316418</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.08642529335984994</v>
+        <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.104868740743498</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.450112504520507</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.00224299023316</v>
+        <v>-8.052197271517807</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.08564835546897509</v>
+        <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.109355185944886</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.449992153371104</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.361773312737164</v>
+        <v>-8.411727594021809</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2241101811725259</v>
+        <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.109355185944886</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.455342456669154</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.412122376191386</v>
+        <v>-8.462076657476031</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2363337865970374</v>
+        <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.159704249399109</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.433049038553799</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.509741653612782</v>
+        <v>-8.559695934897427</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2723397469438269</v>
+        <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.257323526820505</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.37751922272273</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.56381315312114</v>
+        <v>-8.613767434405785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2910747904255984</v>
+        <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.311395026328865</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.347969879339286</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.768071328451004</v>
+        <v>-8.818025609735649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3672648634389013</v>
+        <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.439033970942853</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.276899709689535</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.801724166959477</v>
+        <v>-8.851678448244122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3762434443578546</v>
+        <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.539447338859891</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.221134243423749</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.728254335292029</v>
+        <v>-8.778208616576674</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.331483810197454</v>
+        <v>-0.3514655227113126</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.465977507192442</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.280587843917639</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.903378752678572</v>
+        <v>-8.953333033963217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3869783564045544</v>
+        <v>-0.406960068918413</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.641101924578986</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.19006841423323</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.137830846693062</v>
+        <v>-9.187785127977707</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4879783589119464</v>
+        <v>-0.507960071425805</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.641101924578986</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.182849249331634</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.242205577719508</v>
+        <v>-9.292159859004153</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5364004420965012</v>
+        <v>-0.5563821546103598</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.745476655605432</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.11355221994179</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.294991733319835</v>
+        <v>-9.34494601460448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5563991144980753</v>
+        <v>-0.5763808270119339</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.841152142187829</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.057262717830908</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.421028526688124</v>
+        <v>-9.470982807972769</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6041201032162764</v>
+        <v>-0.624101815730135</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.815900519378087</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.075107420145868</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.363956754792193</v>
+        <v>-9.413911036076838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5773010587715035</v>
+        <v>-0.5972827712853621</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.815900519378087</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.079097755832269</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.505628596516313</v>
+        <v>-9.555582877800958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6354450223598933</v>
+        <v>-0.6554267348737519</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.815900519378087</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.077622528933527</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.456037752091479</v>
+        <v>-9.505992033376124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.600555274425087</v>
+        <v>-0.6205369869389457</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.766309674953253</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.1224304457533</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.307119417619623</v>
+        <v>-9.357073698904268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5540390742830277</v>
+        <v>-0.5740207867968863</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.73506008421808</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.128129066547721</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.081274264900211</v>
+        <v>-9.131228546184857</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4541219401590539</v>
+        <v>-0.4741036526729134</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.693133408630916</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.162864144936227</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.956695608562619</v>
+        <v>-9.006649889847266</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4031513330679584</v>
+        <v>-0.4231330455818179</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.693133408630916</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.164003289492286</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.009590896606905</v>
+        <v>-9.059545177891552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4216756741235654</v>
+        <v>-0.4416573866374249</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.68817806254247</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.169610271307461</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611563</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.937457721319024</v>
+        <v>-8.987412002603671</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3870886997697767</v>
+        <v>-0.4070704122836357</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.68817806254247</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.175343975546098</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.866091328709377</v>
+        <v>-8.916045609994024</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3682794051197829</v>
+        <v>-0.3882611176336423</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.616811669932822</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.208426548718021</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.772632294724152</v>
+        <v>-8.822586576008799</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3407792728386005</v>
+        <v>-0.36076098535246</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.616811669932822</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.198543067405114</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.505390493855755</v>
+        <v>-8.555344775140401</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2357171129906153</v>
+        <v>-0.2556988255044748</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.616811669932822</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.196708506905741</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.407483455179264</v>
+        <v>-8.457437736463911</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1968546124934796</v>
+        <v>-0.2168363250073391</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.548825920072266</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.237199641848613</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.383529914203306</v>
+        <v>-8.433484195487953</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.186604689957603</v>
+        <v>-0.2065864024714625</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.524872379096308</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.252240272579682</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.119469975880509</v>
+        <v>-8.169424257165156</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09424103079023638</v>
+        <v>-0.1142227433040959</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.260812440773512</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.397415919411607</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.412390352375671</v>
+        <v>-7.462344633660318</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.185803784951398</v>
+        <v>0.1658220724375385</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.260812440773512</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.394628885751306</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.372206054009481</v>
+        <v>-7.422160335294127</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2022211281857156</v>
+        <v>0.1822394156718561</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.220628142407321</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.419083088658862</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.208806183070118</v>
+        <v>-7.258760464354765</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2669478977822175</v>
+        <v>0.246966185268358</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.057228271467959</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.516489832443237</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.97532496084052</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3682648155119095</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8237470492383601</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.664502994618848</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.825658569833005</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4252391616019562</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7308435579958241</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.71735287905141</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.693383096202118</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4735168378013377</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5985680843649375</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.792085649976969</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.537644763642376</v>
+        <v>-6.587599044927023</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5386272315128711</v>
+        <v>0.518645518999012</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4428297518051959</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.888343710200451</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.288644964958795</v>
+        <v>-6.338599246243442</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6511334922099623</v>
+        <v>0.6311517796961028</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1938299531216152</v>
+        <v>-0.2472458891152278</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.050649930634258</v>
+        <v>3.018600369038091</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.3942349547319</v>
+        <v>-6.444189236016546</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4809215667015021</v>
+        <v>0.4609398541876426</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2994199428947196</v>
+        <v>-0.3528358788883322</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.859320007171177</v>
+        <v>2.827270445575009</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.412969856850497</v>
+        <v>-6.462924138135143</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5219719477311493</v>
+        <v>0.5019902352172902</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3050159525548509</v>
+        <v>-0.3584318885484635</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.904506743252185</v>
+        <v>2.872457181656017</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.265029815442897</v>
+        <v>-6.314984096727544</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4612690416060214</v>
+        <v>0.4412873290921624</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2846950366462933</v>
+        <v>-0.3381109726399059</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.796820370109152</v>
+        <v>2.764770808512984</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.212060293188909</v>
+        <v>-6.262014574473556</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.473742864254139</v>
+        <v>0.4537611517402795</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2317255143923044</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.819888097208067</v>
+        <v>2.787838535611899</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.168511886418218</v>
+        <v>-6.218466167702865</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.484201614867322</v>
+        <v>0.4642199023534626</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2317255143923044</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.812927485112974</v>
+        <v>2.780877923516806</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.13514867993945</v>
+        <v>-6.185102961224096</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5120092518399724</v>
+        <v>0.4920275393261129</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2317255143923044</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.827389839494117</v>
+        <v>2.795340277897949</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.026889542816928</v>
+        <v>-6.076843824101575</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5498450271481761</v>
+        <v>0.5298633146343166</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2317255143923044</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.821921959953312</v>
+        <v>2.789872398357144</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.903598407999797</v>
+        <v>-5.953552689284444</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5966595750856056</v>
+        <v>0.5766778625717461</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1084343795751739</v>
+        <v>-0.1618503155687865</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.893394734854167</v>
+        <v>2.861345173257999</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.882449209096354</v>
+        <v>-5.932403490381001</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.612820232884308</v>
+        <v>0.5928385203704485</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.08728518067173058</v>
+        <v>-0.1407011166653432</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.913785232433558</v>
+        <v>2.88173567083739</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.63868376711291</v>
+        <v>-5.688638048397556</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7061071180247365</v>
+        <v>0.686125405510877</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.08728518067173058</v>
+        <v>-0.1407011166653432</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.909565940780609</v>
+        <v>2.877516379184441</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.536920946835615</v>
+        <v>-5.586875228120261</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7489365600556703</v>
+        <v>0.7289548475418108</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.07406611227930188</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.919621695736082</v>
+        <v>2.887572134139914</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.28707055288654</v>
+        <v>-5.337024834171187</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8416187926190024</v>
+        <v>0.8216370801051429</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.07406611227930188</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.912363770719784</v>
+        <v>2.880314209123616</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.111178460419108</v>
+        <v>-5.161132741703755</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9155747531266241</v>
+        <v>0.8955930406127646</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.07406611227930188</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.915962894240433</v>
+        <v>2.883913332644265</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.939731997396644</v>
+        <v>-4.989686278681291</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.997480844390163</v>
+        <v>0.9774991318763036</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.09738035074316126</v>
+        <v>0.04396441474954865</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.032158278108464</v>
+        <v>3.000108716512297</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.865442431658305</v>
+        <v>-4.915396712942952</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.026217148301796</v>
+        <v>1.006235435787936</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1716699164815005</v>
+        <v>0.1182539804878879</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.075752495167765</v>
+        <v>3.043702933571597</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.801806689424371</v>
+        <v>-4.851760970709018</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.056366246249687</v>
+        <v>1.036384533735827</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2353056587154351</v>
+        <v>0.1818897227218225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.118628741562443</v>
+        <v>3.086579179966275</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.690379930098451</v>
+        <v>-4.740334211383098</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.08213120876385</v>
+        <v>1.062149496249991</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2353056587154351</v>
+        <v>0.1818897227218225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.099823000346238</v>
+        <v>3.067773438750071</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.44994943329359</v>
+        <v>-4.499903714578237</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.180046484110672</v>
+        <v>1.160064771596812</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4757361555202954</v>
+        <v>0.4223202195266827</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.245824375054032</v>
+        <v>3.213774813457865</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.377706865122396</v>
+        <v>-4.427661146407043</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.21287282521397</v>
+        <v>1.192891112700111</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4757361555202954</v>
+        <v>0.4223202195266827</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.249753688888852</v>
+        <v>3.217704127292685</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.35999317824453</v>
+        <v>-4.409947459529177</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.220636883882456</v>
+        <v>1.200655171368597</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4789174844172122</v>
+        <v>0.4255015484235996</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.252341070144342</v>
+        <v>3.220291508548175</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.251188292764803</v>
+        <v>-4.30114257404945</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.26115690929434</v>
+        <v>1.241175196780481</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4789174844172122</v>
+        <v>0.4255015484235996</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.249339141364336</v>
+        <v>3.217289579768168</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.031167494727793</v>
+        <v>-4.08112177601244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.350744265519759</v>
+        <v>1.330762553005899</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6201373294851924</v>
+        <v>0.5667213934915798</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.335650085415738</v>
+        <v>3.303600523819571</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.898299805664515</v>
+        <v>-3.948254086949162</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.419785523946893</v>
+        <v>1.399803811433034</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6201373294851924</v>
+        <v>0.5667213934915798</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.351544268217562</v>
+        <v>3.319494706621394</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.778126722300016</v>
+        <v>-3.828081003584662</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.469000601732995</v>
+        <v>1.449018889219135</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7403104128496913</v>
+        <v>0.6868944768560787</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.424793962676563</v>
+        <v>3.392744401080395</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.633454577200278</v>
+        <v>-3.683408858484925</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.53695756233433</v>
+        <v>1.51697584982047</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8849825579494288</v>
+        <v>0.8315666219558162</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.521685352297845</v>
+        <v>3.489635790701677</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.693329404557971</v>
+        <v>-3.743283685842617</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.499045122792678</v>
+        <v>1.479063410278819</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8251077305917367</v>
+        <v>0.7716917945981241</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.471797947284656</v>
+        <v>3.439748385688488</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.573509173647133</v>
+        <v>-3.62346345493178</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.562262384391222</v>
+        <v>1.542280671877363</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8251077305917367</v>
+        <v>0.7716917945981241</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.487087116518864</v>
+        <v>3.455037554922697</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.575978880108939</v>
+        <v>-3.625933161393586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.468918701128941</v>
+        <v>1.448936988615082</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8226380241299305</v>
+        <v>0.7692220881363179</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.393249491964222</v>
+        <v>3.361199930368054</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.644349066432949</v>
+        <v>-3.694303347717596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.360832488084639</v>
+        <v>1.340850775570779</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8319137231661454</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.318076772871252</v>
+        <v>3.286027211275085</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.658137119279996</v>
+        <v>-3.708091400564642</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.345753975577711</v>
+        <v>1.325772263063852</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8319137231661454</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.308513481503144</v>
+        <v>3.276463919906976</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.713657195172585</v>
+        <v>-3.763611476457232</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.460576781912878</v>
+        <v>1.440595069399018</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8319137231661454</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.445544318195346</v>
+        <v>3.413494756599178</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.538182935380116</v>
+        <v>-3.588137216664763</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.535333717821653</v>
+        <v>1.515352005307794</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8319137231661454</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.450111550187134</v>
+        <v>3.418061988590966</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.649119188021364</v>
+        <v>-3.699073469306011</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.466701245526361</v>
+        <v>1.446719533012502</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8319137231661454</v>
+        <v>0.7784977871725328</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.425853578948341</v>
+        <v>3.393804017352173</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.615455642549083</v>
+        <v>-3.665409923833729</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.408704977116723</v>
+        <v>1.388723264602864</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8655772686384273</v>
+        <v>0.8121613326448147</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.37459001963316</v>
+        <v>3.342540458036992</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.555603023345359</v>
+        <v>-3.605557304630006</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.442818411230345</v>
+        <v>1.422836698716486</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8655772686384273</v>
+        <v>0.8121613326448147</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.384762406065292</v>
+        <v>3.352712844469124</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.469359560318982</v>
+        <v>-3.519313841603629</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.472262067014756</v>
+        <v>1.452280354500897</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8655772686384273</v>
+        <v>0.8121613326448147</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.379708676639153</v>
+        <v>3.347659115042985</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.514666379717962</v>
+        <v>-3.564620661002609</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.44591511469969</v>
+        <v>1.425933402185831</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8247671056291965</v>
+        <v>0.7713511696355839</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.346998354278139</v>
+        <v>3.314948792681972</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.543699484420264</v>
+        <v>-3.59365376570491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.434853745851871</v>
+        <v>1.414872033338011</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8247671056291965</v>
+        <v>0.7713511696355839</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.347550227311241</v>
+        <v>3.315500665715073</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.450889002969404</v>
+        <v>-3.500843284254051</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.40125063032358</v>
+        <v>1.381268917809721</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9175775870800559</v>
+        <v>0.8641616510864433</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.332509208073122</v>
+        <v>3.300459646476955</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.495278472298832</v>
+        <v>-3.545232753583479</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.38536831851641</v>
+        <v>1.365386606002551</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8731881177506282</v>
+        <v>0.8197721817570156</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.307749002400067</v>
+        <v>3.275699440803899</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.611820077404175</v>
+        <v>-3.661774358688822</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.333827384985996</v>
+        <v>1.313845672472136</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7566465126452855</v>
+        <v>0.7032305766516729</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.232899747848584</v>
+        <v>3.200850186252416</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.499443076221502</v>
+        <v>-3.549397357506149</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.384269481289732</v>
+        <v>1.364287768775873</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7566465126452855</v>
+        <v>0.7032305766516729</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.238391043679251</v>
+        <v>3.206341482083084</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.527223474122855</v>
+        <v>-3.577177755407502</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.38465452389773</v>
+        <v>1.36467281138387</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7288661147439324</v>
+        <v>0.6754501787503198</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.233220006706978</v>
+        <v>3.201170445110811</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.645604146852994</v>
+        <v>-3.695558428137641</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.175657974806328</v>
+        <v>1.155676262292468</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6616482625929562</v>
+        <v>0.6082323265993436</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.031245015417046</v>
+        <v>2.999195453820878</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.754218225296325</v>
+        <v>-3.804172506580972</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.252362004148201</v>
+        <v>1.232380291634342</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6616482625929562</v>
+        <v>0.6082323265993436</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.151394676136252</v>
+        <v>3.119345114540084</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.718809187048182</v>
+        <v>-3.768763468332829</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.281038645549781</v>
+        <v>1.261056933035922</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6616482625929562</v>
+        <v>0.6082323265993436</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.165907702238575</v>
+        <v>3.133858140642407</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.680425524490031</v>
+        <v>-3.730379805774678</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.29381155191541</v>
+        <v>1.273829839401551</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7000319251511073</v>
+        <v>0.6466159891574947</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.186357341115834</v>
+        <v>3.154307779519666</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.503309194454865</v>
+        <v>-3.553263475739512</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.361387112774779</v>
+        <v>1.341405400260919</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7000319251511073</v>
+        <v>0.6466159891574947</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.183086369961136</v>
+        <v>3.151036808364968</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.54840143928841</v>
+        <v>-3.598355720573057</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.344033606603274</v>
+        <v>1.324051894089414</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6381358819817176</v>
+        <v>0.5847199459881049</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.146632135821415</v>
+        <v>3.114582574225247</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.369026018049643</v>
+        <v>-3.418980299334289</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.409570750405195</v>
+        <v>1.389589037891336</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7949126401524362</v>
+        <v>0.7414967041588236</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.23448516603026</v>
+        <v>3.202435604434093</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.414040231570249</v>
+        <v>-3.463994512854895</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.372372520328542</v>
+        <v>1.352390807814683</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7645637448378316</v>
+        <v>0.711147808844219</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.197083284173087</v>
+        <v>3.16503372257692</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.681044741842684</v>
+        <v>-3.730999023127331</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.271262278558514</v>
+        <v>1.251280566044654</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5702007067948831</v>
+        <v>0.5167847708012705</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.086157023686264</v>
+        <v>3.054107462090097</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.782242523279857</v>
+        <v>-3.832196804564504</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.229987087880146</v>
+        <v>1.210005375366287</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.501791893249564</v>
+        <v>0.4483759572559513</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.044315657455574</v>
+        <v>3.012266095859407</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.775731556665544</v>
+        <v>-3.825685837950191</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.230191436080188</v>
+        <v>1.210209723566328</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.501791893249564</v>
+        <v>0.4483759572559513</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.041915619009891</v>
+        <v>3.009866057413723</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.756693428958247</v>
+        <v>-3.806647710242894</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.234331406371352</v>
+        <v>1.214349693857492</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4436082819183694</v>
+        <v>0.3901923459247568</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.003530171419419</v>
+        <v>2.971480609823252</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.787820060108865</v>
+        <v>-3.837774341393512</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.341175155545295</v>
+        <v>1.321193443031436</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4436082819183694</v>
+        <v>0.3901923459247568</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.122824573053609</v>
+        <v>3.090775011457442</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.801686821442782</v>
+        <v>-3.851641102727429</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.336461779997862</v>
+        <v>1.316480067484002</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4057503651845465</v>
+        <v>0.3523344291909338</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.100943151999449</v>
+        <v>3.068893590403281</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.756882649902852</v>
+        <v>-3.806836931187499</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.360391979010759</v>
+        <v>1.3404102664969</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4057503651845465</v>
+        <v>0.3523344291909338</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.106951682396375</v>
+        <v>3.074902120800207</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.60913967966785</v>
+        <v>-3.659093960952497</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.31743938838196</v>
+        <v>1.2974576758681</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5735577224194297</v>
+        <v>0.520141786425817</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.105586318014505</v>
+        <v>3.073536756418337</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.711154362199071</v>
+        <v>-3.761108643483718</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.279427136900952</v>
+        <v>1.259445424387093</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5735577224194297</v>
+        <v>0.520141786425817</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.108379939545986</v>
+        <v>3.076330377949818</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.705001656146287</v>
+        <v>-3.754955937430934</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.282550567713725</v>
+        <v>1.262568855199865</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.579710428472214</v>
+        <v>0.5262944924786013</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.112733911569315</v>
+        <v>3.080684349973147</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.721810954296788</v>
+        <v>-3.771765235581435</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.274907325193634</v>
+        <v>1.254925612679775</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5629011303217124</v>
+        <v>0.5094851943280996</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.101728809419124</v>
+        <v>3.069679247822956</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.659512955520666</v>
+        <v>-3.709467236805313</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.366162078500904</v>
+        <v>1.346180365987044</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5629011303217124</v>
+        <v>0.5094851943280996</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.168064363215945</v>
+        <v>3.136014801619777</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.457722757855509</v>
+        <v>-3.507677039140155</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.249170159281094</v>
+        <v>1.229188446767235</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7609193224908668</v>
+        <v>0.707503386497254</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.089167280231564</v>
+        <v>3.057117718635397</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.508609470541703</v>
+        <v>-3.55856375182635</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.299105706528791</v>
+        <v>1.279123994014932</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7100326098046723</v>
+        <v>0.6566166738110595</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.128925484942023</v>
+        <v>3.096875923345855</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.606350015166678</v>
+        <v>-3.656304296451324</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.274637224794845</v>
+        <v>1.254655512280986</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6941433316716921</v>
+        <v>0.6407273956780792</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.134019654178279</v>
+        <v>3.101970092582111</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.666559313171962</v>
+        <v>-3.716513594456609</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.249089486417403</v>
+        <v>1.229107773903544</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6339340336664075</v>
+        <v>0.5805180976727947</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.096430056199779</v>
+        <v>3.064380494603612</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.590137266740035</v>
+        <v>-3.640091548024682</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.278149923030103</v>
+        <v>1.258168210516243</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6339340336664075</v>
+        <v>0.5805180976727947</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.094921674239708</v>
+        <v>3.06287211264354</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.545764135101467</v>
+        <v>-3.595718416386113</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.295762043120966</v>
+        <v>1.275780330607107</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6783071653049761</v>
+        <v>0.6248912293113633</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.121408420658285</v>
+        <v>3.089358859062118</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.568244485960351</v>
+        <v>-3.618198767244998</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.281163696916003</v>
+        <v>1.261181984402143</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6783071653049761</v>
+        <v>0.6248912293113633</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.115802214796876</v>
+        <v>3.083752653200708</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.520588755399296</v>
+        <v>-3.570543036683943</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.30660774616823</v>
+        <v>1.28662603365437</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7259628958660318</v>
+        <v>0.672546959872419</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.150777410161314</v>
+        <v>3.118727848565146</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.420070596900541</v>
+        <v>-3.470024878185188</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.351707382942456</v>
+        <v>1.331725670428597</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8264810543647864</v>
+        <v>0.7730651183711735</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.215980678635291</v>
+        <v>3.183931117039124</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.48073718730293</v>
+        <v>-3.530691468587577</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.314195419257373</v>
+        <v>1.294213706743513</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7447827376462527</v>
+        <v>0.6913668016526399</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.153716361080043</v>
+        <v>3.121666799483876</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.435898785694532</v>
+        <v>-3.485853066979179</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.336228482511361</v>
+        <v>1.316246769997501</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7493261705911222</v>
+        <v>0.6959102345975093</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.160540123457594</v>
+        <v>3.128490561861426</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.455397241936541</v>
+        <v>-3.505351523221187</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.332590039645635</v>
+        <v>1.312608327131776</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7012415293112179</v>
+        <v>0.647825593317605</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.135850278320729</v>
+        <v>3.103800716724561</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.41119440485064</v>
+        <v>-3.461148686135287</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.356150777007833</v>
+        <v>1.336169064493973</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7454443663971183</v>
+        <v>0.6920284304035055</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.168251583100107</v>
+        <v>3.136202021503939</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.448173432514083</v>
+        <v>-3.49812771379873</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.339769166411703</v>
+        <v>1.319787453897844</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7824182681884488</v>
+        <v>0.729002332194836</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.188845924644153</v>
+        <v>3.156796363047984</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.289882014974811</v>
+        <v>-3.339836296259458</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.454333498610451</v>
+        <v>1.434351786096592</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7824182681884488</v>
+        <v>0.729002332194836</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.240093689827192</v>
+        <v>3.208044128231024</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.082240011340335</v>
+        <v>-3.132194292624982</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.535831004658495</v>
+        <v>1.515849292144636</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.990060271822925</v>
+        <v>0.9366443358293122</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.363119596602131</v>
+        <v>3.331070035005963</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.031207918617807</v>
+        <v>-3.081162199902454</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.551192069985776</v>
+        <v>1.531210357471917</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.041092364545453</v>
+        <v>0.9876764285518401</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.388687080473917</v>
+        <v>3.35663751887775</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.965983737490602</v>
+        <v>-3.015938018775248</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.594469146529363</v>
+        <v>1.574487434015504</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.106316545672658</v>
+        <v>1.052900609679046</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.445008993242946</v>
+        <v>3.412959431646778</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.928556717419468</v>
+        <v>-2.978510998704115</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.605400926857097</v>
+        <v>1.585419214343238</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.11156808370184</v>
+        <v>1.058152147708227</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.444120888359735</v>
+        <v>3.412071326763567</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.948668373454176</v>
+        <v>-2.998622654738823</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.598613056774454</v>
+        <v>1.578631344260595</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.122595428699259</v>
+        <v>1.069179492705646</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.451994087689427</v>
+        <v>3.419944526093259</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.894923559026971</v>
+        <v>-2.944877840311618</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.780668753566547</v>
+        <v>1.760687041052688</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.132658738139722</v>
+        <v>1.079242802146108</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.618589844374915</v>
+        <v>3.586540282778747</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.820141298001959</v>
+        <v>-2.870095579286605</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.930694567194369</v>
+        <v>1.91071285468051</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.207440999164734</v>
+        <v>1.154025063171121</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.78357211020774</v>
+        <v>3.751522548611572</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.794057213738151</v>
+        <v>-2.844011495022797</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.932836176913751</v>
+        <v>1.912854464399892</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.207440999164734</v>
+        <v>1.154025063171121</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.775280086221599</v>
+        <v>3.743230524625431</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.715926032889204</v>
+        <v>-2.765880314173851</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.96228184483711</v>
+        <v>1.94230013232325</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.281617810048419</v>
+        <v>1.228201874054806</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.817979368335589</v>
+        <v>3.785929806739421</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.707033571495921</v>
+        <v>-2.756987852780568</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.983393235121214</v>
+        <v>1.963411522607355</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.281617810048419</v>
+        <v>1.228201874054806</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.83553377406238</v>
+        <v>3.803484212466213</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.875509688465799</v>
+        <v>-2.925463969750445</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.907857835737847</v>
+        <v>1.887876123223988</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.253669974331838</v>
+        <v>1.200254038338225</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.810620120037016</v>
+        <v>3.778570558440848</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.177710159604215</v>
+        <v>-2.227664440888862</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.168247344470342</v>
+        <v>2.148265631956483</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.183321914961427</v>
+        <v>1.129905978967814</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.749680981602631</v>
+        <v>3.717631420006464</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.154989055921063</v>
+        <v>-2.20494333720571</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.167999808440507</v>
+        <v>2.148018095926648</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.183321914961427</v>
+        <v>1.129905978967814</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.740345004099536</v>
+        <v>3.708295442503368</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.284190869215105</v>
+        <v>-2.334145150499752</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.27522520897406</v>
+        <v>2.2552434964602</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.054120101667385</v>
+        <v>1.000704165673772</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.82173004197428</v>
+        <v>3.789680480378112</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.438971875993361</v>
+        <v>-2.488926157278008</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.250390628756404</v>
+        <v>2.230408916242545</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.020752427612909</v>
+        <v>0.9673364916192959</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.83878726003524</v>
+        <v>3.806737698439073</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.431917185778187</v>
+        <v>-2.481871467062834</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.249887860832019</v>
+        <v>2.229906148318159</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.027807117828083</v>
+        <v>0.9743911818344697</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.83969543015389</v>
+        <v>3.807645868557722</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.404965961451699</v>
+        <v>-2.454920242736346</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.270674504207356</v>
+        <v>2.250692791693496</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.042687463855802</v>
+        <v>0.9892715278621889</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.858629791415263</v>
+        <v>3.826580229819095</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.553699096186526</v>
+        <v>-2.590873250792662</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.395284382458384</v>
+        <v>2.380414720615929</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.042687463855802</v>
+        <v>0.9892715278621889</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.042732923560223</v>
+        <v>4.010683361964055</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.576107213991398</v>
+        <v>-2.613281368597534</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.378437830239429</v>
+        <v>2.363568168396974</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.042687463855802</v>
+        <v>0.9892715278621889</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.034849618463216</v>
+        <v>4.002800056867049</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.724112981470797</v>
+        <v>-2.761287136076934</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.321289522797307</v>
+        <v>2.306419860954851</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9559604549922605</v>
+        <v>0.9025445189986474</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.984867412694729</v>
+        <v>3.952817851098561</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.733553907359327</v>
+        <v>-2.770728061965464</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.373766870163742</v>
+        <v>2.358897208321286</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.078387572535652</v>
+        <v>1.024971636542039</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.11457740094261</v>
+        <v>4.082527839346443</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.785827514694968</v>
+        <v>-2.823001669301105</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.355748521774786</v>
+        <v>2.340878859932331</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.026113965200011</v>
+        <v>0.9726980292063977</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.086104331086527</v>
+        <v>4.054054769490358</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.862157492295874</v>
+        <v>-2.899331646902011</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.323328343628199</v>
+        <v>2.308458681785743</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.026113965200011</v>
+        <v>0.9726980292063977</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.084216143980302</v>
+        <v>4.052166582384134</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.064411212620227</v>
+        <v>-3.101585367226364</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.23724708510132</v>
+        <v>2.222377423258864</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8238602448756571</v>
+        <v>0.7704443088820443</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.957684141388552</v>
+        <v>3.925634579792384</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.225979638147483</v>
+        <v>-3.26315379275362</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.17105372510057</v>
+        <v>2.156184063258115</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6970773210777778</v>
+        <v>0.6436613850841649</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.880048397319977</v>
+        <v>3.847998835723809</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.358280930245036</v>
+        <v>-3.395455084851173</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.131206615127468</v>
+        <v>2.116336953285012</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6970773210777778</v>
+        <v>0.6436613850841649</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.893121804185895</v>
+        <v>3.861072242589727</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.359842573059896</v>
+        <v>-3.397016727666033</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.130581958001524</v>
+        <v>2.115712296159068</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6970773210777778</v>
+        <v>0.6436613850841649</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.893121804185895</v>
+        <v>3.861072242589727</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.387743360169369</v>
+        <v>-3.424917514775506</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.117945684284736</v>
+        <v>2.103076022442281</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.662480396934843</v>
+        <v>0.6090644609412301</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.870887690827137</v>
+        <v>3.838838129230969</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.510269462872263</v>
+        <v>-3.5474436174784</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.065699687180778</v>
+        <v>2.050830025338322</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5399542942319491</v>
+        <v>0.4865383582383362</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.794136473182599</v>
+        <v>3.762086911586431</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.740783959057851</v>
+        <v>-3.777958113663988</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.040199848297046</v>
+        <v>2.02533018645459</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3094397980463603</v>
+        <v>0.2560238620527475</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.72253373506175</v>
+        <v>3.690484173465582</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.997504777052675</v>
+        <v>-4.034678931658812</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.077823240100964</v>
+        <v>2.062953578258508</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2010252239025455</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.797796709577308</v>
+        <v>3.76574714798114</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.151491194828816</v>
+        <v>-4.188665349434952</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.085208942136147</v>
+        <v>2.070339280293692</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2010252239025455</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.866776978722947</v>
+        <v>3.83472741712678</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.10096929100115</v>
+        <v>-4.138143445607287</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.091468905787334</v>
+        <v>2.076599243944879</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2010252239025455</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.852828180843068</v>
+        <v>3.820778619246901</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.392643690857105</v>
+        <v>-4.390618599615011</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.986669634900366</v>
+        <v>1.987479671397203</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2010252239025455</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.864698669898482</v>
+        <v>3.832649108302315</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.662116492778813</v>
+        <v>-4.668249235976743</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.880091048650626</v>
+        <v>1.877637951371454</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2010252239025455</v>
+        <v>0.1476092879089327</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.865909204417426</v>
+        <v>3.833859642821258</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.819660564508255</v>
+        <v>-4.825793307706185</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.821195162186171</v>
+        <v>1.818742064906999</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.134123418762271</v>
+        <v>0.08070748276865819</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.829889863560583</v>
+        <v>3.797840301964415</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.097624960091529</v>
+        <v>-5.103757703289459</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.705087256689051</v>
+        <v>1.702634159409878</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.04450368447678676</v>
+        <v>-0.008912251516826064</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.771195875725482</v>
+        <v>3.739146314129314</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.21459265273042</v>
+        <v>-5.220725395928349</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.820504236332539</v>
+        <v>1.818051139053366</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.04450368447678676</v>
+        <v>-0.008912251516826064</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.933399932424526</v>
+        <v>3.901350370828358</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.299310594951373</v>
+        <v>-5.305443338149303</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.781463697407972</v>
+        <v>1.779010600128799</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04061234445125961</v>
+        <v>-0.09402828044487244</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.877176953031512</v>
+        <v>3.845127391435344</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.381245413220256</v>
+        <v>-5.387378156418186</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.758919187668909</v>
+        <v>1.756466090389737</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.05054709003833979</v>
+        <v>-0.1039630260319526</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.881445523247755</v>
+        <v>3.849395961651587</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.327507239819994</v>
+        <v>-5.333639983017924</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.789340095484917</v>
+        <v>1.786886998205744</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.003191083361922309</v>
+        <v>-0.05022485263169052</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.922614065743815</v>
+        <v>3.890564504147647</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.217500956342772</v>
+        <v>-5.223633699540702</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.825495496119981</v>
+        <v>1.823042398840808</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02639565527919752</v>
+        <v>-0.02702028071441531</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.928689696138355</v>
+        <v>3.896640134542188</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.074441380601847</v>
+        <v>-5.080574123799776</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.886969337138325</v>
+        <v>1.884516239859153</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.03440908186917679</v>
+        <v>-0.01900685412443603</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.937747762814317</v>
+        <v>3.905698201218149</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.77299465513001</v>
+        <v>-4.779127398327939</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.014808910209596</v>
+        <v>2.012355812930424</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3358558073410141</v>
+        <v>0.2824398713474012</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.125876680979955</v>
+        <v>4.093827119383787</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.797584899365194</v>
+        <v>-4.803717642563123</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.005943990268233</v>
+        <v>2.003490892989061</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3358558073410141</v>
+        <v>0.2824398713474012</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.126847858732665</v>
+        <v>4.094798297136498</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.746546523358673</v>
+        <v>-4.752679266556602</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.027202245050597</v>
+        <v>2.024749147771424</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3358558073410141</v>
+        <v>0.2824398713474012</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.127690763112421</v>
+        <v>4.095641201516253</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.705407228492042</v>
+        <v>-4.752477782459296</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.062696061871394</v>
+        <v>2.043867840284492</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3769951022076449</v>
+        <v>0.2826413554447075</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.171412438906545</v>
+        <v>4.114800190848783</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.59480108841244</v>
+        <v>-4.641871642379694</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.923122514027169</v>
+        <v>1.904294292440267</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4876012422872469</v>
+        <v>0.3932474955243095</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.053960119078241</v>
+        <v>3.997347871020478</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.725381822943283</v>
+        <v>-4.772452376910537</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.874392264288796</v>
+        <v>1.855564042701894</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3570205077564044</v>
+        <v>0.262666760993467</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.979113722433699</v>
+        <v>3.922501474375936</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.560885488752321</v>
+        <v>-4.607956042719575</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.924617617041264</v>
+        <v>1.905789395454361</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3570205077564044</v>
+        <v>0.262666760993467</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.963540541509781</v>
+        <v>3.906928293452019</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.43640500802837</v>
+        <v>-4.483475561995624</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.973597519767274</v>
+        <v>1.954769298180372</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3570205077564044</v>
+        <v>0.262666760993467</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.962728251946212</v>
+        <v>3.906116003888449</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83232118453305</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.446790202918259</v>
+        <v>-4.493860756885513</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.979312220936391</v>
+        <v>1.960483999349488</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3466353128665151</v>
+        <v>0.2522815661035777</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.96636591413735</v>
+        <v>3.909753666079588</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83892492013052</v>
+        <v>3.806893439551228</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.743082388853192</v>
+        <v>3.759364651566908</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.483399054129496</v>
+        <v>-4.48491396222097</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.949366342887647</v>
+        <v>1.965042642364772</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3493335902362247</v>
+        <v>0.2612283607681206</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.952682542994927</v>
+        <v>3.91610166802778</v>
       </c>
     </row>
   </sheetData>
